--- a/Sustainability_Frameworks_Tool_COMPLETE.xlsx
+++ b/Sustainability_Frameworks_Tool_COMPLETE.xlsx
@@ -12702,10 +12702,12 @@
       </c>
       <c r="R63" s="128" t="inlineStr">
         <is>
-          <t>• Defined benefit obligation data must align with IFRS/GAAP disclosures
-• Applies only if legal actions have occurred — disclose zero if none
+          <t>• Legal register must be current, signed off by General Counsel, and auditable
+• Applies only if legal actions have occurred — disclose zero if none with explanation
 • Material competition law cases may already be disclosed in financial statements
-• Assurers will cross-reference with legal register and financial disclosures</t>
+• Assurers will cross-reference with legal register and financial statement footnotes
+• Case descriptions must be consistent between sustainability report and annual report
+• Settlement terms and confidentiality constraints should be noted if limiting disclosure</t>
         </is>
       </c>
       <c r="S63" s="129" t="inlineStr">
@@ -18442,7 +18444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T69"/>
+  <dimension ref="A1:T95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" style="116" min="1" max="1"/>
@@ -22574,7 +22576,7 @@
     <row r="38" ht="22" customHeight="1" s="42">
       <c r="A38" s="132" t="inlineStr">
         <is>
-          <t xml:space="preserve">   GRI 12: Coal Sector 2022 — Additional Topics</t>
+          <t xml:space="preserve">   GRI 12: Coal Sector 2022 — Additional Topics (12.1–12.13)</t>
         </is>
       </c>
     </row>
@@ -23786,67 +23788,1243 @@
     <row r="49" ht="22" customHeight="1" s="42">
       <c r="A49" s="132" t="inlineStr">
         <is>
-          <t xml:space="preserve">   GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 — Additional Topics</t>
+          <t xml:space="preserve">   GRI 12: Coal Sector 2022 — Additional Topics (12.14–12.22)</t>
         </is>
       </c>
     </row>
     <row r="50" ht="130" customHeight="1" s="42">
       <c r="A50" s="122" t="inlineStr">
         <is>
+          <t>GRI 12: Coal Sector 2022</t>
+        </is>
+      </c>
+      <c r="B50" s="122" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C50" s="122" t="inlineStr">
+        <is>
+          <t>Social Topics — Local Communities</t>
+        </is>
+      </c>
+      <c r="D50" s="123" t="inlineStr">
+        <is>
+          <t>GRI 12 — Topic 12.14</t>
+        </is>
+      </c>
+      <c r="E50" s="122" t="inlineStr">
+        <is>
+          <t>Local Communities</t>
+        </is>
+      </c>
+      <c r="F50" s="122" t="inlineStr">
+        <is>
+          <t>Coal sector entities must report on their impacts on local communities, including social and economic contributions and adverse impacts from operations.</t>
+        </is>
+      </c>
+      <c r="G50" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H50" s="122" t="inlineStr">
+        <is>
+          <t>All coal mining and coal power generation entities</t>
+        </is>
+      </c>
+      <c r="I50" s="122" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 12</t>
+        </is>
+      </c>
+      <c r="J50" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K50" s="122" t="inlineStr">
+        <is>
+          <t>Report using GRI 413 (Local Communities). Sector-specific considerations include: (a) community impacts from noise, dust, vibration, and water disruption from coal mining; (b) economic dependency of local communities on coal operations; (c) impacts on community health from air and water pollution; (d) resettlement and land displacement from mine development; (e) social investment and community development activities in mining-affected communities; (f) just transition planning impacts on local communities.</t>
+        </is>
+      </c>
+      <c r="L50" s="124" t="inlineStr">
+        <is>
+          <t>• Community engagement programme documentation and records
+• Social impact assessment (SIA) for operational sites
+• Community development fund records and project documentation
+• Resettlement action plan (RAP) and progress reports
+• Health impact assessment (HIA) records
+• Local procurement and employment data by community
+• Stakeholder grievance register and resolution records
+• Community consultation records for new projects or expansions
+• Environmental monitoring data shared with communities (dust, noise, water quality)</t>
+        </is>
+      </c>
+      <c r="M50" s="125" t="inlineStr">
+        <is>
+          <t>• Community meeting minutes and consultation records
+• Independent social audit reports
+• Government-approved environmental and social impact assessments
+• Resettlement completion certificates
+• Community satisfaction survey results
+• Regulatory compliance records for community notification
+• Third-party community welfare monitoring reports</t>
+        </is>
+      </c>
+      <c r="N50" s="126" t="inlineStr">
+        <is>
+          <t>• Number of communities in areas of influence of operations
+• Number of community engagement events held
+• Total community investment ($) by type and location
+• Number of community complaints or grievances received and resolved
+• Number of workers resettled (if applicable)
+• Compensation paid to affected community members ($)
+• Local employment rate (% of employees from local community)
+• Local procurement spend (% of total procurement)
+• Community health impact metrics (dust, water quality exceedances)</t>
+        </is>
+      </c>
+      <c r="O50" s="127" t="inlineStr">
+        <is>
+          <t>Local employment % = Employees hired from local community / Total site employees × 100. Community investment intensity = Community investment / Revenue × 100. Grievance resolution rate = Grievances resolved / Grievances received × 100. Resettlement completion rate = RAP milestones completed / Total RAP milestones × 100.</t>
+        </is>
+      </c>
+      <c r="P50" s="122" t="inlineStr">
+        <is>
+          <t>Community Affairs / Operations / Sustainability / Human Rights / ESG</t>
+        </is>
+      </c>
+      <c r="Q50" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R50" s="128" t="inlineStr">
+        <is>
+          <t>• RAP implementation quality is a primary assurance focus for coal operators with displaced communities
+• Community health impacts (respiratory, water quality) require quantitative monitoring data
+• Just transition plans must address community economic impacts explicitly
+• Assurers will assess consistency between community claims and community feedback
+• Independent social audits strengthen credibility of community impact claims</t>
+        </is>
+      </c>
+      <c r="S50" s="129" t="inlineStr">
+        <is>
+          <t>• Is there a current social impact assessment for each operational site affecting communities?
+• Are resettlement action plans independently monitored and verified?
+• Does the organisation have documented plans for community transitions in closure scenarios?
+• Are community health impacts from dust, noise, and water quality systematically monitored and reported?</t>
+        </is>
+      </c>
+      <c r="T50" s="122" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022 | Topic 12.14 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="130" customHeight="1" s="42">
+      <c r="A51" s="133" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022</t>
+        </is>
+      </c>
+      <c r="B51" s="133" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C51" s="133" t="inlineStr">
+        <is>
+          <t>Social Topics — Indigenous Peoples</t>
+        </is>
+      </c>
+      <c r="D51" s="134" t="inlineStr">
+        <is>
+          <t>GRI 12 — Topic 12.15</t>
+        </is>
+      </c>
+      <c r="E51" s="133" t="inlineStr">
+        <is>
+          <t>Rights of Indigenous Peoples</t>
+        </is>
+      </c>
+      <c r="F51" s="133" t="inlineStr">
+        <is>
+          <t>Coal entities must report on respect for the rights of indigenous peoples in areas affected by coal mining, including free, prior and informed consent (FPIC).</t>
+        </is>
+      </c>
+      <c r="G51" s="133" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H51" s="133" t="inlineStr">
+        <is>
+          <t>Coal entities operating in or near indigenous territories</t>
+        </is>
+      </c>
+      <c r="I51" s="133" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 12</t>
+        </is>
+      </c>
+      <c r="J51" s="133" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K51" s="133" t="inlineStr">
+        <is>
+          <t>Report using GRI 411 (Rights of Indigenous Peoples). Sector-specific considerations include: (a) identification of indigenous peoples in the area of influence of coal operations; (b) FPIC processes for new projects, expansions, or significant operational changes; (c) land, water, and cultural heritage rights of indigenous peoples; (d) indigenous peoples' involvement in environmental monitoring; (e) joint management and benefit-sharing agreements.</t>
+        </is>
+      </c>
+      <c r="L51" s="124" t="inlineStr">
+        <is>
+          <t>• Indigenous peoples identification and mapping records
+• FPIC process documentation and consent records
+• Land rights and cultural heritage assessment records
+• Indigenous community engagement programme documentation
+• Benefit-sharing agreement documentation
+• Cultural heritage site register and protection protocols
+• Joint management committee records
+• ILO Convention 169 compliance assessment
+• Indigenous liaison officer programme records</t>
+        </is>
+      </c>
+      <c r="M51" s="125" t="inlineStr">
+        <is>
+          <t>• Documented consent records for FPIC processes
+• Cultural heritage site survey reports
+• Benefit-sharing agreement signed copies
+• Government-approved FPIC compliance records
+• Independent FPIC assessment reports
+• Legal counsel opinion on ILO 169 obligations
+• Indigenous community satisfaction and feedback records</t>
+        </is>
+      </c>
+      <c r="N51" s="126" t="inlineStr">
+        <is>
+          <t>• Number of indigenous communities in area of influence
+• Number of FPIC processes conducted
+• Number of consent agreements reached vs. rejected
+• Cultural heritage sites identified and protected
+• Value of benefit-sharing agreements ($)
+• Number of indigenous peoples employed by operation
+• Number of indigenous community engagement events
+• Legal actions related to indigenous rights (count and outcomes)</t>
+        </is>
+      </c>
+      <c r="O51" s="127" t="inlineStr">
+        <is>
+          <t>FPIC compliance rate = Projects with documented FPIC / Projects affecting indigenous territories × 100. Indigenous employment % = Indigenous workers / Total site employees × 100. Cultural heritage site protection rate = Sites with protection protocols / Total identified sites × 100.</t>
+        </is>
+      </c>
+      <c r="P51" s="133" t="inlineStr">
+        <is>
+          <t>Community Affairs / Legal / Human Rights / Operations / Sustainability</t>
+        </is>
+      </c>
+      <c r="Q51" s="133" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R51" s="128" t="inlineStr">
+        <is>
+          <t>• FPIC must be free (no coercion), prior (before decisions), and informed (full information provided)
+• Assurers will scrutinise FPIC documentation for all three elements
+• Cultural heritage protection requires formal site surveys — undocumented sites are a risk
+• ILO 169 obligations apply in signatory countries — legal counsel must confirm compliance
+• Benefit-sharing must be fair and documented in legally binding agreements</t>
+        </is>
+      </c>
+      <c r="S51" s="129" t="inlineStr">
+        <is>
+          <t>• Are FPIC processes in place for all projects affecting indigenous territories?
+• Is cultural heritage assessed and protected at all operational sites?
+• Are benefit-sharing agreements in place and independently monitored?
+• Are there any pending or completed legal actions regarding indigenous peoples' rights?</t>
+        </is>
+      </c>
+      <c r="T51" s="133" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022 | Topic 12.15 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="130" customHeight="1" s="42">
+      <c r="A52" s="122" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022</t>
+        </is>
+      </c>
+      <c r="B52" s="122" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C52" s="122" t="inlineStr">
+        <is>
+          <t>Social Topics — Conflict and Security</t>
+        </is>
+      </c>
+      <c r="D52" s="123" t="inlineStr">
+        <is>
+          <t>GRI 12 — Topic 12.16</t>
+        </is>
+      </c>
+      <c r="E52" s="122" t="inlineStr">
+        <is>
+          <t>Conflict and Security</t>
+        </is>
+      </c>
+      <c r="F52" s="122" t="inlineStr">
+        <is>
+          <t>Report on the security arrangements in coal operations and their potential for contributing to or being associated with human rights abuses in conflict-affected areas.</t>
+        </is>
+      </c>
+      <c r="G52" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H52" s="122" t="inlineStr">
+        <is>
+          <t>Coal entities operating in conflict-affected or high-risk areas</t>
+        </is>
+      </c>
+      <c r="I52" s="122" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 12</t>
+        </is>
+      </c>
+      <c r="J52" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K52" s="122" t="inlineStr">
+        <is>
+          <t>Report using GRI 410 (Security Practices). Sector-specific considerations include: (a) security arrangements at coal mines, ports, and infrastructure; (b) use of private security forces and their conduct; (c) operating in conflict-affected or high-risk areas (CAHRAs); (d) Voluntary Principles on Security and Human Rights (VPSHR) implementation; (e) incidents involving security personnel and third parties.</t>
+        </is>
+      </c>
+      <c r="L52" s="124" t="inlineStr">
+        <is>
+          <t>• Security risk assessment and management plan
+• Security provider contracts and terms of reference
+• Voluntary Principles on Security and Human Rights (VPSHR) implementation records
+• Security incident register (including use of force incidents)
+• Human rights training records for security personnel
+• Complaints mechanism records specific to security incidents
+• Country risk assessments for CAHRA operations
+• OECD Due Diligence Guidance compliance documentation
+• Background check records for security personnel</t>
+        </is>
+      </c>
+      <c r="M52" s="125" t="inlineStr">
+        <is>
+          <t>• Security incident investigation reports
+• VPSHR compliance assessment reports
+• Security personnel human rights training completion records
+• Legal records of any security-related human rights incidents
+• Regulatory compliance records in conflict-affected jurisdictions
+• Independent security audit reports</t>
+        </is>
+      </c>
+      <c r="N52" s="126" t="inlineStr">
+        <is>
+          <t>• Number of security personnel (private and public) engaged at operations
+• Number of security incidents involving injury or fatality
+• Percentage of security personnel trained on human rights (%)
+• Number of complaints received regarding security conduct
+• Operations in conflict-affected or high-risk areas (count)
+• VPSHR adherence status (committed, implementing, reporting)
+• Legal actions related to security conduct (count and outcomes)</t>
+        </is>
+      </c>
+      <c r="O52" s="127" t="inlineStr">
+        <is>
+          <t>Security incident rate = Security incidents / Total security personnel × 100. Training coverage = Security personnel trained on human rights / Total security personnel × 100. Complaint resolution rate = Complaints resolved / Complaints received × 100.</t>
+        </is>
+      </c>
+      <c r="P52" s="122" t="inlineStr">
+        <is>
+          <t>Security / Legal / Human Rights / Operations / Risk Management</t>
+        </is>
+      </c>
+      <c r="Q52" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R52" s="128" t="inlineStr">
+        <is>
+          <t>• VPSHR is the primary international framework — coal companies should formally commit
+• All security incidents involving force must be investigated and documented
+• Public security forces under company influence require the same human rights standards
+• CAHRA operations require enhanced due diligence per OECD guidance
+• Assurers will cross-check incident records with local reporting and media</t>
+        </is>
+      </c>
+      <c r="S52" s="129" t="inlineStr">
+        <is>
+          <t>• Has the organisation formally committed to the Voluntary Principles on Security and Human Rights?
+• Are all security-related incidents documented, investigated, and disclosed?
+• Do security contracts require human rights training and VPSHR compliance?
+• Is there a dedicated complaint channel for security-related concerns?</t>
+        </is>
+      </c>
+      <c r="T52" s="122" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022 | Topic 12.16 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="130" customHeight="1" s="42">
+      <c r="A53" s="133" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022</t>
+        </is>
+      </c>
+      <c r="B53" s="133" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C53" s="133" t="inlineStr">
+        <is>
+          <t>Social Topics — Child Labour</t>
+        </is>
+      </c>
+      <c r="D53" s="134" t="inlineStr">
+        <is>
+          <t>GRI 12 — Topic 12.17</t>
+        </is>
+      </c>
+      <c r="E53" s="133" t="inlineStr">
+        <is>
+          <t>Child Labour</t>
+        </is>
+      </c>
+      <c r="F53" s="133" t="inlineStr">
+        <is>
+          <t>Report on measures to eliminate child labour in coal operations and associated supply chains.</t>
+        </is>
+      </c>
+      <c r="G53" s="133" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H53" s="133" t="inlineStr">
+        <is>
+          <t>All coal sector entities and their supply chains</t>
+        </is>
+      </c>
+      <c r="I53" s="133" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 12</t>
+        </is>
+      </c>
+      <c r="J53" s="133" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K53" s="133" t="inlineStr">
+        <is>
+          <t>Report using GRI 408 (Child Labour). Sector-specific considerations include: (a) risk of child labour in artisanal and small-scale coal mining supply chains; (b) age verification at hire and contract labour compliance; (c) supply chain due diligence for child labour risk in coal transport and port operations; (d) rehabilitation programmes for child workers found in supply chains.</t>
+        </is>
+      </c>
+      <c r="L53" s="124" t="inlineStr">
+        <is>
+          <t>• Age verification procedures and records
+• Child labour risk assessment for operations and supply chain
+• Contractor management policies and child labour clauses
+• Supply chain audit results for child labour risk
+• ILO core convention compliance documentation (C138, C182)
+• Child labour remediation programme records
+• HR screening records for minimum age verification
+• Community awareness programme records for child labour
+• Supply chain mapping identifying artisanal mining exposure</t>
+        </is>
+      </c>
+      <c r="M53" s="125" t="inlineStr">
+        <is>
+          <t>• Age verification records for all direct and contract employees
+• Supply chain audit results showing child labour screening
+• ILO conventions ratification confirmation (operating countries)
+• Remediation records for any child labour incidents found
+• Contractor compliance confirmation records
+• Independent supply chain assessment reports</t>
+        </is>
+      </c>
+      <c r="N53" s="126" t="inlineStr">
+        <is>
+          <t>• Number of operations assessed for child labour risk
+• Number of child labour incidents identified (direct operations and supply chain)
+• Percentage of suppliers audited for child labour (%)
+• Number of under-age workers found and remediated
+• Percentage of contractors with child labour clauses in contracts (%)
+• Age verification rate (% of workers age-verified at hire)
+• Number of community awareness events on child labour prevention</t>
+        </is>
+      </c>
+      <c r="O53" s="127" t="inlineStr">
+        <is>
+          <t>Supplier audit coverage = Suppliers audited for child labour / Total suppliers × 100. Age verification rate = Workers with verified age documentation / Total workers hired × 100. Remediation rate = Child labour incidents remediated / Total incidents found × 100.</t>
+        </is>
+      </c>
+      <c r="P53" s="133" t="inlineStr">
+        <is>
+          <t>HR / Procurement / Supply Chain / Sustainability / Human Rights</t>
+        </is>
+      </c>
+      <c r="Q53" s="133" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R53" s="128" t="inlineStr">
+        <is>
+          <t>• Age verification documentation is a baseline requirement — assurers will check completeness
+• Artisanal and small-scale mining supply chains carry elevated child labour risk
+• ILO Conventions 138 (minimum age) and 182 (worst forms) are the reference frameworks
+• Remediation programmes, not termination, are the preferred response to discovered cases
+• Supply chain transparency (mine-of-origin traceability) is increasingly required</t>
+        </is>
+      </c>
+      <c r="S53" s="129" t="inlineStr">
+        <is>
+          <t>• Is there a documented age verification procedure for all direct and contractor workers?
+• Are supply chain suppliers assessed for child labour risk, particularly artisanal sources?
+• Is there a remediation programme in place for child labour incidents?
+• Does the organisation have supply chain visibility beyond tier-1 for child labour risk?</t>
+        </is>
+      </c>
+      <c r="T53" s="133" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022 | Topic 12.17 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="130" customHeight="1" s="42">
+      <c r="A54" s="122" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022</t>
+        </is>
+      </c>
+      <c r="B54" s="122" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C54" s="122" t="inlineStr">
+        <is>
+          <t>Social Topics — Freedom of Association</t>
+        </is>
+      </c>
+      <c r="D54" s="123" t="inlineStr">
+        <is>
+          <t>GRI 12 — Topic 12.18</t>
+        </is>
+      </c>
+      <c r="E54" s="122" t="inlineStr">
+        <is>
+          <t>Freedom of Association and Collective Bargaining</t>
+        </is>
+      </c>
+      <c r="F54" s="122" t="inlineStr">
+        <is>
+          <t>Report on the respect for workers' rights to freedom of association and collective bargaining across coal operations and supply chains.</t>
+        </is>
+      </c>
+      <c r="G54" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H54" s="122" t="inlineStr">
+        <is>
+          <t>All coal sector entities and their supply chains</t>
+        </is>
+      </c>
+      <c r="I54" s="122" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 12</t>
+        </is>
+      </c>
+      <c r="J54" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K54" s="122" t="inlineStr">
+        <is>
+          <t>Report using GRI 407 (Freedom of Association and Collective Bargaining). Sector-specific considerations include: (a) labour relations in coal mines (including underground mining); (b) operations in jurisdictions where freedom of association is legally restricted; (c) collective bargaining agreements covering underground and surface workers; (d) migrant worker rights to association and bargaining.</t>
+        </is>
+      </c>
+      <c r="L54" s="124" t="inlineStr">
+        <is>
+          <t>• Freedom of association policy
+• Collective bargaining agreement (CBA) register
+• Trade union recognition records
+• Country risk assessment for freedom of association rights
+• Operations register with freedom of association legal status by jurisdiction
+• Migrant worker rights documentation
+• Works council or worker representative meeting records
+• ILO Conventions C87 and C98 compliance assessment
+• Labour relations incident log</t>
+        </is>
+      </c>
+      <c r="M54" s="125" t="inlineStr">
+        <is>
+          <t>• CBA signed copies with union parties
+• Trade union recognition certificates
+• ILO convention compliance assessment by country
+• Labour relations incident investigation records
+• Worker representative election records
+• Government labour inspection reports</t>
+        </is>
+      </c>
+      <c r="N54" s="126" t="inlineStr">
+        <is>
+          <t>• Percentage of employees covered by collective bargaining agreements (%)
+• Number of operational sites where freedom of association is at risk (restricted jurisdiction)
+• Number of trade unions recognised at operational sites
+• Number of labour relations incidents (strikes, lockouts, disputes)
+• Percentage of workers in restricted jurisdictions with alternative representation (%)
+• Number of CBAs under negotiation or recently concluded
+• Migrant workers' access to worker representation (count, % with representation)</t>
+        </is>
+      </c>
+      <c r="O54" s="127" t="inlineStr">
+        <is>
+          <t>CBA coverage = Employees under CBA / Total employees × 100. Restricted jurisdiction rate = Operations in restricted jurisdictions / Total operations × 100. Labour dispute rate = Labour disputes / Total operations × 100.</t>
+        </is>
+      </c>
+      <c r="P54" s="122" t="inlineStr">
+        <is>
+          <t>HR / Industrial Relations / Legal / Sustainability / Human Rights</t>
+        </is>
+      </c>
+      <c r="Q54" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R54" s="128" t="inlineStr">
+        <is>
+          <t>• CBA coverage is a primary metric — percentage must be disclosed with clear scope
+• Operations in restricted jurisdictions require alternative mechanisms and explicit disclosure
+• Migrant workers have equivalent rights — assurers check that these are enforceable in practice
+• Union independence must be genuine — company-sponsored unions do not satisfy the standard
+• Labour relations incidents (strikes) must be disclosed, including duration and resolution</t>
+        </is>
+      </c>
+      <c r="S54" s="129" t="inlineStr">
+        <is>
+          <t>• What percentage of employees are covered by collective bargaining agreements?
+• Are there operations in jurisdictions where freedom of association is legally restricted?
+• Are alternative representation mechanisms in place for workers in restricted jurisdictions?
+• Are migrant workers able to exercise their rights to freedom of association in practice?</t>
+        </is>
+      </c>
+      <c r="T54" s="122" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022 | Topic 12.18 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="130" customHeight="1" s="42">
+      <c r="A55" s="133" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022</t>
+        </is>
+      </c>
+      <c r="B55" s="133" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C55" s="133" t="inlineStr">
+        <is>
+          <t>Social Topics — Forced Labour</t>
+        </is>
+      </c>
+      <c r="D55" s="134" t="inlineStr">
+        <is>
+          <t>GRI 12 — Topic 12.19</t>
+        </is>
+      </c>
+      <c r="E55" s="133" t="inlineStr">
+        <is>
+          <t>Forced Labour and Modern Slavery</t>
+        </is>
+      </c>
+      <c r="F55" s="133" t="inlineStr">
+        <is>
+          <t>Report on measures to prevent forced labour and modern slavery in coal operations and supply chains, including debt bondage and migrant worker exploitation.</t>
+        </is>
+      </c>
+      <c r="G55" s="133" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H55" s="133" t="inlineStr">
+        <is>
+          <t>All coal sector entities and their supply chains</t>
+        </is>
+      </c>
+      <c r="I55" s="133" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 12</t>
+        </is>
+      </c>
+      <c r="J55" s="133" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K55" s="133" t="inlineStr">
+        <is>
+          <t>Report using GRI 409 (Forced or Compulsory Labour). Sector-specific considerations include: (a) risk of forced labour in underground coal mining and contracted labour; (b) debt bondage risk for migrant workers in coal supply chains; (c) passport confiscation and recruitment fee abuses; (d) modern slavery risk in coal transport, logistics and port operations; (e) UK Modern Slavery Act and equivalent national statute compliance.</t>
+        </is>
+      </c>
+      <c r="L55" s="124" t="inlineStr">
+        <is>
+          <t>• Forced labour and modern slavery risk assessment
+• Modern Slavery Act statement (UK or equivalent jurisdiction)
+• Migrant worker recruitment fee policy and monitoring records
+• No-passport-confiscation policy and compliance records
+• Supply chain due diligence records (forced labour focus)
+• Labour broker management and screening records
+• Worker voice mechanisms accessible to vulnerable workers
+• Remediation programme for identified forced labour cases
+• ILO Convention C29 and C105 compliance assessment
+• Supplier contract clauses on forced labour prohibition</t>
+        </is>
+      </c>
+      <c r="M55" s="125" t="inlineStr">
+        <is>
+          <t>• Modern Slavery Act statement (published, board-approved)
+• Supply chain audit results showing forced labour screening
+• Migrant worker recruitment fee compliance records
+• Independent social audit reports for high-risk suppliers
+• Remediation records for any forced labour incidents
+• Legal compliance records for anti-forced-labour legislation
+• Worker survey results on key modern slavery indicators</t>
+        </is>
+      </c>
+      <c r="N55" s="126" t="inlineStr">
+        <is>
+          <t>• Number of operations and suppliers assessed for forced labour risk
+• Number of forced labour incidents identified and remediated
+• Percentage of suppliers with forced labour clauses in contracts (%)
+• Percentage of migrant workers who paid zero recruitment fees (%)
+• Number of workers who experienced passport confiscation (target: zero)
+• Supply chain audit coverage in high-risk geographies (%)
+• Number of workers supported through remediation programmes</t>
+        </is>
+      </c>
+      <c r="O55" s="127" t="inlineStr">
+        <is>
+          <t>Zero-recruitment-fee compliance = Migrant workers paying zero fees / Total migrant workers × 100. Forced labour audit coverage = High-risk suppliers audited / Total high-risk suppliers × 100. Incident remediation rate = Cases remediated / Cases identified × 100.</t>
+        </is>
+      </c>
+      <c r="P55" s="133" t="inlineStr">
+        <is>
+          <t>HR / Procurement / Supply Chain / Sustainability / Legal / Human Rights</t>
+        </is>
+      </c>
+      <c r="Q55" s="133" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R55" s="128" t="inlineStr">
+        <is>
+          <t>• Modern Slavery Act statement must be board-approved, published, and meet all 6 reporting areas
+• No-recruitment-fee policy must be actively enforced, not just stated
+• Migrant worker debt bondage risk requires specific monitoring beyond standard audits
+• Passport confiscation is an absolute prohibition — one confirmed case requires immediate escalation
+• Worker Voice mechanisms must be trusted by workers to detect forced labour</t>
+        </is>
+      </c>
+      <c r="S55" s="129" t="inlineStr">
+        <is>
+          <t>• Is there a board-approved Modern Slavery Act statement covering the entire value chain?
+• Is the zero-recruitment-fee policy actively monitored with evidence of compliance?
+• Are migrant worker recruitment channels screened and regularly audited?
+• Is there a remediation programme in place for any identified forced labour cases?</t>
+        </is>
+      </c>
+      <c r="T55" s="133" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022 | Topic 12.19 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="130" customHeight="1" s="42">
+      <c r="A56" s="122" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022</t>
+        </is>
+      </c>
+      <c r="B56" s="122" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C56" s="122" t="inlineStr">
+        <is>
+          <t>Social Topics — Non-discrimination</t>
+        </is>
+      </c>
+      <c r="D56" s="123" t="inlineStr">
+        <is>
+          <t>GRI 12 — Topic 12.20</t>
+        </is>
+      </c>
+      <c r="E56" s="122" t="inlineStr">
+        <is>
+          <t>Non-discrimination and Equal Opportunity</t>
+        </is>
+      </c>
+      <c r="F56" s="122" t="inlineStr">
+        <is>
+          <t>Report on measures to prevent discrimination and advance equal opportunity across coal sector workplaces.</t>
+        </is>
+      </c>
+      <c r="G56" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H56" s="122" t="inlineStr">
+        <is>
+          <t>All coal sector entities</t>
+        </is>
+      </c>
+      <c r="I56" s="122" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 12</t>
+        </is>
+      </c>
+      <c r="J56" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K56" s="122" t="inlineStr">
+        <is>
+          <t>Report using GRI 406 (Non-discrimination). Sector-specific considerations include: (a) gender representation in underground and surface coal mining roles; (b) discrimination risks for indigenous workers and workers from local communities; (c) racial, ethnic, and caste-based discrimination in coal supply chain operations; (d) equal opportunity policies and enforcement mechanisms.</t>
+        </is>
+      </c>
+      <c r="L56" s="124" t="inlineStr">
+        <is>
+          <t>• Equal opportunity and non-discrimination policy
+• Diversity and inclusion strategy document
+• Workforce diversity data (gender, ethnicity, disability, age)
+• Discrimination incident register and investigation records
+• Equal pay analysis and gender pay gap report
+• Indigenous worker employment programme records
+• Recruitment and promotion equity analysis
+• Grievance mechanism records (discrimination-specific)
+• Training records on unconscious bias and harassment prevention
+• ILO Conventions C100 and C111 compliance assessment</t>
+        </is>
+      </c>
+      <c r="M56" s="125" t="inlineStr">
+        <is>
+          <t>• Discrimination incident investigation records
+• Equal pay gap analysis signed off by HR director
+• Workforce diversity data from HRIS
+• Training completion records for equity and inclusion
+• Third-party diversity audit or certification
+• Legal compliance records for equal opportunity legislation
+• Regulatory complaints to labour authorities (count and outcomes)</t>
+        </is>
+      </c>
+      <c r="N56" s="126" t="inlineStr">
+        <is>
+          <t>• Gender breakdown of workforce (% female by grade/level)
+• Gender pay gap (%) — median and mean
+• Number of discrimination incidents reported and investigated
+• Percentage of discrimination incidents substantiated (%)
+• Number of disciplinary actions for discrimination
+• Representation of indigenous and local community workers (%)
+• Female representation in senior management (%)
+• Training completion rate for equality and inclusion (%)</t>
+        </is>
+      </c>
+      <c r="O56" s="127" t="inlineStr">
+        <is>
+          <t>Gender pay gap = (Male median pay − Female median pay) / Male median pay × 100. Female representation = Female employees / Total employees × 100. Discrimination substantiation rate = Substantiated incidents / Total complaints × 100. Promotion equity = Female promotions / Total promotions × 100 vs. female share of total workforce.</t>
+        </is>
+      </c>
+      <c r="P56" s="122" t="inlineStr">
+        <is>
+          <t>HR / Diversity &amp; Inclusion / Legal / Sustainability / Operations</t>
+        </is>
+      </c>
+      <c r="Q56" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R56" s="128" t="inlineStr">
+        <is>
+          <t>• Gender pay gap analysis is legally required in many jurisdictions and assurance-sensitive
+• Underground mining historically male-dominated — gender targets require specific programme evidence
+• Indigenous worker discrimination requires particular attention in coal sector given historical tensions
+• Zero-tolerance policy must be backed by demonstrable enforcement records
+• Assurers will scrutinise substantiation rate of complaints — too low or too high both raise questions</t>
+        </is>
+      </c>
+      <c r="S56" s="129" t="inlineStr">
+        <is>
+          <t>• Is the gender pay gap calculated, disclosed, and explained?
+• Are there measurable targets for increasing diversity in mining roles?
+• Are discrimination complaints consistently investigated with documented outcomes?
+• Are indigenous workers and local community members represented at all levels of the workforce?</t>
+        </is>
+      </c>
+      <c r="T56" s="122" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022 | Topic 12.20 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="130" customHeight="1" s="42">
+      <c r="A57" s="133" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022</t>
+        </is>
+      </c>
+      <c r="B57" s="133" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C57" s="133" t="inlineStr">
+        <is>
+          <t>Social Topics — Employment Practices</t>
+        </is>
+      </c>
+      <c r="D57" s="134" t="inlineStr">
+        <is>
+          <t>GRI 12 — Topic 12.21</t>
+        </is>
+      </c>
+      <c r="E57" s="133" t="inlineStr">
+        <is>
+          <t>Employment Practices</t>
+        </is>
+      </c>
+      <c r="F57" s="133" t="inlineStr">
+        <is>
+          <t>Report on employment practices in coal operations including hiring, contracts, remuneration, benefits, and workforce planning in the context of energy transition.</t>
+        </is>
+      </c>
+      <c r="G57" s="133" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H57" s="133" t="inlineStr">
+        <is>
+          <t>All coal sector entities</t>
+        </is>
+      </c>
+      <c r="I57" s="133" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 12</t>
+        </is>
+      </c>
+      <c r="J57" s="133" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K57" s="133" t="inlineStr">
+        <is>
+          <t>Report using GRI 401 (Employment). Sector-specific considerations include: (a) workforce composition in coal operations (permanent, contract, agency); (b) impact of energy transition on employment and just transition planning; (c) employee benefits for underground and hazardous work; (d) redundancy and severance policies for transition-affected workers; (e) retraining and reskilling programmes for displaced coal workers.</t>
+        </is>
+      </c>
+      <c r="L57" s="124" t="inlineStr">
+        <is>
+          <t>• Employment policy and contracts register
+• Workforce composition data (permanent, fixed-term, contract, agency)
+• Compensation and benefits structure documentation
+• Just transition plan with workforce impact assessment
+• Retraining and reskilling programme records
+• Redundancy and severance policy document
+• Parental leave policy and take-up data
+• Employee benefits register by grade/band
+• Collective bargaining records relating to employment terms
+• HRIS reports on turnover, hiring, and separations</t>
+        </is>
+      </c>
+      <c r="M57" s="125" t="inlineStr">
+        <is>
+          <t>• HRIS workforce composition reports
+• Benefit plan documents and enrolment records
+• Redundancy payment records (if applicable)
+• Retraining completion records and qualification outcomes
+• Collective bargaining agreement terms on employment conditions
+• Regulatory compliance records for labour law requirements
+• Board or management approval of just transition workforce plan</t>
+        </is>
+      </c>
+      <c r="N57" s="126" t="inlineStr">
+        <is>
+          <t>• Total workforce by employment type (permanent, fixed-term, contract)
+• Turnover rate (%) by region and gender
+• New hires as % of total workforce
+• Parental leave take-up rate (%)
+• Average benefits value per employee ($)
+• Number of workers affected by transition or restructuring
+• Number of workers enrolled in retraining programmes
+• Retraining completion rate and re-employment rate (%)</t>
+        </is>
+      </c>
+      <c r="O57" s="127" t="inlineStr">
+        <is>
+          <t>Turnover rate = Employees who left / Average headcount × 100. Parental leave return rate = Employees returning after parental leave / Employees taking leave × 100. Retraining completion = Workers completing retraining / Workers enrolled × 100. Transition support rate = Workers receiving support / Workers affected by transition × 100.</t>
+        </is>
+      </c>
+      <c r="P57" s="133" t="inlineStr">
+        <is>
+          <t>HR / Operations / Sustainability / Finance / Just Transition Planning</t>
+        </is>
+      </c>
+      <c r="Q57" s="133" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R57" s="128" t="inlineStr">
+        <is>
+          <t>• Just transition workforce planning is a sector-critical disclosure for coal — assurers will probe depth
+• Benefits disclosure must cover all significant benefit types (pension, health, disability)
+• Contract worker benefits vs. permanent worker benefits disparity must be acknowledged
+• Retraining outcomes (did workers find new employment?) are more meaningful than enrolment numbers
+• Turnover rates in coal mining are an indicator of workplace conditions</t>
+        </is>
+      </c>
+      <c r="S57" s="129" t="inlineStr">
+        <is>
+          <t>• Does the just transition plan quantify workforce impact and set specific retraining commitments?
+• Are contract and agency workers provided with comparable benefits to permanent employees?
+• Is the retraining programme independently evaluated for effectiveness (employment outcomes)?
+• Are turnover rates analysed by demographic and location to identify workforce retention issues?</t>
+        </is>
+      </c>
+      <c r="T57" s="133" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022 | Topic 12.21 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="130" customHeight="1" s="42">
+      <c r="A58" s="122" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022</t>
+        </is>
+      </c>
+      <c r="B58" s="122" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C58" s="122" t="inlineStr">
+        <is>
+          <t>Environmental Topics — Tailings Management</t>
+        </is>
+      </c>
+      <c r="D58" s="123" t="inlineStr">
+        <is>
+          <t>GRI 12 — Topic 12.22</t>
+        </is>
+      </c>
+      <c r="E58" s="122" t="inlineStr">
+        <is>
+          <t>Tailings Management</t>
+        </is>
+      </c>
+      <c r="F58" s="122" t="inlineStr">
+        <is>
+          <t>Report on the management of coal tailings and mine waste, including tailings storage facility (TSF) safety, closure planning, and environmental impacts.</t>
+        </is>
+      </c>
+      <c r="G58" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H58" s="122" t="inlineStr">
+        <is>
+          <t>All coal mining entities with tailings storage facilities</t>
+        </is>
+      </c>
+      <c r="I58" s="122" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 12</t>
+        </is>
+      </c>
+      <c r="J58" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K58" s="122" t="inlineStr">
+        <is>
+          <t>Sector-specific disclosure for coal tailings. Report: (a) number, size, and classification of tailings storage facilities (TSFs); (b) Global Industry Standard on Tailings Management (GISTM) implementation status; (c) TSF stability, safety, and inspection records; (d) environmental impacts of tailings (acid mine drainage, heavy metals, dust); (e) tailings facility closure and rehabilitation plans; (f) community risk from tailings facilities.</t>
+        </is>
+      </c>
+      <c r="L58" s="124" t="inlineStr">
+        <is>
+          <t>• Tailings storage facility register with location, size, and classification
+• GISTM implementation plan and progress reports
+• TSF stability assessment and independent review reports
+• Environmental monitoring data for tailings facilities (water quality, dust, seepage)
+• Emergency response plan for each TSF
+• TSF closure and rehabilitation plan
+• Acid mine drainage (AMD) management records
+• Community risk assessment for downstream TSF populations
+• Annual TSF inspection records and certification
+• Insurance and liability documentation for TSFs</t>
+        </is>
+      </c>
+      <c r="M58" s="125" t="inlineStr">
+        <is>
+          <t>• Independent geotechnical review reports for each TSF
+• Environmental monitoring data confirming compliance with limits
+• GISTM self-assessment and third-party verification reports
+• Emergency response plan exercise records
+• Regulatory inspection reports and compliance certificates
+• Closure bond/fund documentation
+• Community risk communication records</t>
+        </is>
+      </c>
+      <c r="N58" s="126" t="inlineStr">
+        <is>
+          <t>• Number of tailings storage facilities (active, inactive, closed)
+• Total volume of tailings stored (tonnes or m³)
+• GISTM conformance status (% of facilities conforming)
+• Number of TSF safety inspections conducted
+• Number of TSF incidents, failures, or seepage events
+• AMD monitoring exceedances (count)
+• Closure and rehabilitation fund balance ($)
+• Area rehabilitated (ha) and area remaining to rehabilitate (ha)
+• Community risk assessments completed (count)</t>
+        </is>
+      </c>
+      <c r="O58" s="127" t="inlineStr">
+        <is>
+          <t>GISTM conformance rate = Facilities with GISTM conformance / Total active TSFs × 100. AMD compliance rate = Monitoring periods within licence limits / Total monitoring periods × 100. Closure progress = Area rehabilitated / Total mine footprint area × 100. Incident rate = TSF incidents / Total TSFs × 100.</t>
+        </is>
+      </c>
+      <c r="P58" s="122" t="inlineStr">
+        <is>
+          <t>Mining Operations / Environment / Safety / Risk Management / Sustainability</t>
+        </is>
+      </c>
+      <c r="Q58" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R58" s="128" t="inlineStr">
+        <is>
+          <t>• GISTM (2020) requires CEO-level accountable executive for each TSF — this must be named
+• GISTM conformance requires annual independent review and senior management sign-off
+• TSF failure risk is a catastrophic risk — assurers will require detailed evidence
+• Acid mine drainage is a long-tail liability — monitoring data must span decades
+• Closure fund adequacy is a financial materiality issue — actuarial review should be documented</t>
+        </is>
+      </c>
+      <c r="S58" s="129" t="inlineStr">
+        <is>
+          <t>• Has the organisation implemented GISTM for all active tailings storage facilities?
+• Are independent geotechnical reviews conducted annually and findings disclosed?
+• Is the tailings closure fund adequately funded for all closure liabilities?
+• Are communities at risk from TSF failure informed and engaged in emergency planning?</t>
+        </is>
+      </c>
+      <c r="T58" s="122" t="inlineStr">
+        <is>
+          <t>GRI 12: Coal Sector 2022 | Topic 12.22 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1" s="42">
+      <c r="A59" s="132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 — Additional Topics (13.1–13.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="130" customHeight="1" s="42">
+      <c r="A60" s="122" t="inlineStr">
+        <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
         </is>
       </c>
-      <c r="B50" s="122" t="inlineStr">
+      <c r="B60" s="122" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C50" s="122" t="inlineStr">
+      <c r="C60" s="122" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Environmental</t>
         </is>
       </c>
-      <c r="D50" s="123" t="inlineStr">
+      <c r="D60" s="123" t="inlineStr">
         <is>
           <t>GRI 13 — Topic 13.2</t>
         </is>
       </c>
-      <c r="E50" s="122" t="inlineStr">
+      <c r="E60" s="122" t="inlineStr">
         <is>
           <t>Land and Soil (Agriculture)</t>
         </is>
       </c>
-      <c r="F50" s="122" t="inlineStr">
+      <c r="F60" s="122" t="inlineStr">
         <is>
           <t>Land use, soil health, and prevention of land degradation are a likely material topic for agriculture.</t>
         </is>
       </c>
-      <c r="G50" s="122" t="inlineStr">
+      <c r="G60" s="122" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H50" s="122" t="inlineStr">
+      <c r="H60" s="122" t="inlineStr">
         <is>
           <t>All agricultural sector organizations</t>
         </is>
       </c>
-      <c r="I50" s="122" t="inlineStr">
+      <c r="I60" s="122" t="inlineStr">
         <is>
           <t>Likely material per GRI 13</t>
         </is>
       </c>
-      <c r="J50" s="122" t="inlineStr">
+      <c r="J60" s="122" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K50" s="122" t="inlineStr">
+      <c r="K60" s="122" t="inlineStr">
         <is>
           <t>Report: total land under management; land use types; soil health management; sustainable agriculture certifications; prevention of land degradation; soil carbon.</t>
         </is>
       </c>
-      <c r="L50" s="124" t="inlineStr">
+      <c r="L60" s="124" t="inlineStr">
         <is>
           <t>• Land use register
 • Soil health assessment records
@@ -23858,7 +25036,7 @@
 • Cover crop programme records</t>
         </is>
       </c>
-      <c r="M50" s="125" t="inlineStr">
+      <c r="M60" s="125" t="inlineStr">
         <is>
           <t>• Land registry records
 • Soil survey reports
@@ -23867,7 +25045,7 @@
 • Soil carbon measurement reports</t>
         </is>
       </c>
-      <c r="N50" s="126" t="inlineStr">
+      <c r="N60" s="126" t="inlineStr">
         <is>
           <t>• Total land managed (ha)
 • Land use by type (crops, pasture, forest, other)
@@ -23878,22 +25056,22 @@
 • Remediation area</t>
         </is>
       </c>
-      <c r="O50" s="127" t="inlineStr">
+      <c r="O60" s="127" t="inlineStr">
         <is>
           <t>Soil organic carbon (SOC) = measured by laboratory analysis. Erosion rate: RUSLE = R × K × LS × C × P. Certified % = Certified area / Total managed area × 100.</t>
         </is>
       </c>
-      <c r="P50" s="122" t="inlineStr">
+      <c r="P60" s="122" t="inlineStr">
         <is>
           <t>Agronomy / Operations / Environmental Manager / Sustainability</t>
         </is>
       </c>
-      <c r="Q50" s="122" t="inlineStr">
+      <c r="Q60" s="122" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R50" s="128" t="inlineStr">
+      <c r="R60" s="128" t="inlineStr">
         <is>
           <t>• TNFD framework addresses land and soil as nature-related financial issues
 • Science-based targets for land (SBTs for Nature) are emerging
@@ -23901,7 +25079,7 @@
 • Soil carbon sequestration can contribute to emissions offsets</t>
         </is>
       </c>
-      <c r="S50" s="129" t="inlineStr">
+      <c r="S60" s="129" t="inlineStr">
         <is>
           <t>• Is land use mapped and reported by category?
 • Is soil health formally assessed and monitored?
@@ -23909,69 +25087,69 @@
 • Is soil carbon measured and reported as a climate asset?</t>
         </is>
       </c>
-      <c r="T50" s="122" t="inlineStr">
+      <c r="T60" s="122" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.2 | V1.1 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="130" customHeight="1" s="42">
-      <c r="A51" s="133" t="inlineStr">
+    <row r="61" ht="130" customHeight="1" s="42">
+      <c r="A61" s="133" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
         </is>
       </c>
-      <c r="B51" s="133" t="inlineStr">
+      <c r="B61" s="133" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C51" s="133" t="inlineStr">
+      <c r="C61" s="133" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Environmental</t>
         </is>
       </c>
-      <c r="D51" s="134" t="inlineStr">
+      <c r="D61" s="134" t="inlineStr">
         <is>
           <t>GRI 13 — Topic 13.3</t>
         </is>
       </c>
-      <c r="E51" s="133" t="inlineStr">
+      <c r="E61" s="133" t="inlineStr">
         <is>
           <t>Water (Agriculture)</t>
         </is>
       </c>
-      <c r="F51" s="133" t="inlineStr">
+      <c r="F61" s="133" t="inlineStr">
         <is>
           <t>Water use, irrigation efficiency, and water quality impacts are a likely material topic for agriculture.</t>
         </is>
       </c>
-      <c r="G51" s="133" t="inlineStr">
+      <c r="G61" s="133" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H51" s="133" t="inlineStr">
+      <c r="H61" s="133" t="inlineStr">
         <is>
           <t>All agricultural sector organizations</t>
         </is>
       </c>
-      <c r="I51" s="133" t="inlineStr">
+      <c r="I61" s="133" t="inlineStr">
         <is>
           <t>Likely material per GRI 13</t>
         </is>
       </c>
-      <c r="J51" s="133" t="inlineStr">
+      <c r="J61" s="133" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K51" s="133" t="inlineStr">
+      <c r="K61" s="133" t="inlineStr">
         <is>
           <t>Report: total water withdrawal by source; water use efficiency; irrigation efficiency; water quality; water stress exposure; water management approach.</t>
         </is>
       </c>
-      <c r="L51" s="124" t="inlineStr">
+      <c r="L61" s="124" t="inlineStr">
         <is>
           <t>• Water withdrawal records by source
 • Irrigation water use records
@@ -23982,7 +25160,7 @@
 • Aquifer level monitoring data</t>
         </is>
       </c>
-      <c r="M51" s="125" t="inlineStr">
+      <c r="M61" s="125" t="inlineStr">
         <is>
           <t>• Water meter records
 • Irrigation system records
@@ -23991,7 +25169,7 @@
 • Regulatory water permit compliance records</t>
         </is>
       </c>
-      <c r="N51" s="126" t="inlineStr">
+      <c r="N61" s="126" t="inlineStr">
         <is>
           <t>• Total water withdrawal (ML)
 • By source (surface, groundwater, rainwater, recycled)
@@ -24001,22 +25179,22 @@
 • % operations in high water stress areas</t>
         </is>
       </c>
-      <c r="O51" s="127" t="inlineStr">
+      <c r="O61" s="127" t="inlineStr">
         <is>
           <t>Irrigation efficiency = Crop water use / Total irrigation water applied × 100. Water intensity = Total withdrawal / Production volume. Water consumption = Withdrawal − Return flows.</t>
         </is>
       </c>
-      <c r="P51" s="133" t="inlineStr">
+      <c r="P61" s="133" t="inlineStr">
         <is>
           <t>Agronomy / Operations / Environmental Manager</t>
         </is>
       </c>
-      <c r="Q51" s="133" t="inlineStr">
+      <c r="Q61" s="133" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R51" s="128" t="inlineStr">
+      <c r="R61" s="128" t="inlineStr">
         <is>
           <t>• Agriculture accounts for ~70% of global freshwater withdrawal — material globally
 • Groundwater depletion is critical risk in many agricultural regions
@@ -24024,7 +25202,7 @@
 • Water use efficiency targets link to precision agriculture technology adoption</t>
         </is>
       </c>
-      <c r="S51" s="129" t="inlineStr">
+      <c r="S61" s="129" t="inlineStr">
         <is>
           <t>• Is water use intensity per product unit tracked?
 • Are operations in water-stressed areas identified and managed?
@@ -24032,69 +25210,69 @@
 • Is discharge quality meeting environmental standards?</t>
         </is>
       </c>
-      <c r="T51" s="133" t="inlineStr">
+      <c r="T61" s="133" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.3 | V1.1 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="130" customHeight="1" s="42">
-      <c r="A52" s="122" t="inlineStr">
+    <row r="62" ht="130" customHeight="1" s="42">
+      <c r="A62" s="122" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
         </is>
       </c>
-      <c r="B52" s="122" t="inlineStr">
+      <c r="B62" s="122" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C52" s="122" t="inlineStr">
+      <c r="C62" s="122" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Social</t>
         </is>
       </c>
-      <c r="D52" s="123" t="inlineStr">
+      <c r="D62" s="123" t="inlineStr">
         <is>
           <t>GRI 13 — Topic 13.5</t>
         </is>
       </c>
-      <c r="E52" s="122" t="inlineStr">
+      <c r="E62" s="122" t="inlineStr">
         <is>
           <t>Animal Welfare (Agriculture)</t>
         </is>
       </c>
-      <c r="F52" s="122" t="inlineStr">
+      <c r="F62" s="122" t="inlineStr">
         <is>
           <t>Animal welfare standards in agricultural production are a likely material topic for agriculture and aquaculture.</t>
         </is>
       </c>
-      <c r="G52" s="122" t="inlineStr">
+      <c r="G62" s="122" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H52" s="122" t="inlineStr">
+      <c r="H62" s="122" t="inlineStr">
         <is>
           <t>Agricultural organizations with animal production</t>
         </is>
       </c>
-      <c r="I52" s="122" t="inlineStr">
+      <c r="I62" s="122" t="inlineStr">
         <is>
           <t>Likely material per GRI 13 where livestock/poultry/aquaculture involved</t>
         </is>
       </c>
-      <c r="J52" s="122" t="inlineStr">
+      <c r="J62" s="122" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K52" s="122" t="inlineStr">
+      <c r="K62" s="122" t="inlineStr">
         <is>
           <t>Report: animal welfare policies; management systems; compliance with welfare standards; certification status; species covered; welfare performance metrics.</t>
         </is>
       </c>
-      <c r="L52" s="124" t="inlineStr">
+      <c r="L62" s="124" t="inlineStr">
         <is>
           <t>• Animal welfare policy
 • Animal welfare management system documentation
@@ -24106,7 +25284,7 @@
 • Five Freedoms compliance documentation</t>
         </is>
       </c>
-      <c r="M52" s="125" t="inlineStr">
+      <c r="M62" s="125" t="inlineStr">
         <is>
           <t>• Welfare audit/certification records
 • Veterinary records
@@ -24115,7 +25293,7 @@
 • Third-party welfare certification</t>
         </is>
       </c>
-      <c r="N52" s="126" t="inlineStr">
+      <c r="N62" s="126" t="inlineStr">
         <is>
           <t>• Animal welfare standard adopted
 • % animals covered by welfare certification
@@ -24126,22 +25304,22 @@
 • Species and production systems covered</t>
         </is>
       </c>
-      <c r="O52" s="127" t="inlineStr">
+      <c r="O62" s="127" t="inlineStr">
         <is>
           <t>Mortality rate = Deaths / Average stock × 100. Antibiotic use = Total mg active ingredient used / PCU (population correction unit). Welfare score from certified on-farm assessment.</t>
         </is>
       </c>
-      <c r="P52" s="122" t="inlineStr">
+      <c r="P62" s="122" t="inlineStr">
         <is>
           <t>Animal Production / Veterinary / Quality / Sustainability</t>
         </is>
       </c>
-      <c r="Q52" s="122" t="inlineStr">
+      <c r="Q62" s="122" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R52" s="128" t="inlineStr">
+      <c r="R62" s="128" t="inlineStr">
         <is>
           <t>• Five Freedoms / Five Domains are the international welfare assessment framework
 • EU Farming Welfare Regulations are being revised under Farm to Fork
@@ -24149,7 +25327,7 @@
 • Welfare certification schemes (RSPCA Assured, GlobalG.A.P.) provide assurance-ready data</t>
         </is>
       </c>
-      <c r="S52" s="129" t="inlineStr">
+      <c r="S62" s="129" t="inlineStr">
         <is>
           <t>• Is a formal animal welfare management system documented?
 • Is welfare certification applied across all production systems?
@@ -24157,69 +25335,69 @@
 • Are welfare audits conducted by independent parties?</t>
         </is>
       </c>
-      <c r="T52" s="122" t="inlineStr">
+      <c r="T62" s="122" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.5 | V1.1 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="130" customHeight="1" s="42">
-      <c r="A53" s="133" t="inlineStr">
+    <row r="63" ht="130" customHeight="1" s="42">
+      <c r="A63" s="133" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
         </is>
       </c>
-      <c r="B53" s="133" t="inlineStr">
+      <c r="B63" s="133" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C53" s="133" t="inlineStr">
+      <c r="C63" s="133" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Social</t>
         </is>
       </c>
-      <c r="D53" s="134" t="inlineStr">
+      <c r="D63" s="134" t="inlineStr">
         <is>
           <t>GRI 13 — Topic 13.6</t>
         </is>
       </c>
-      <c r="E53" s="133" t="inlineStr">
+      <c r="E63" s="133" t="inlineStr">
         <is>
           <t>Food Safety (Agriculture)</t>
         </is>
       </c>
-      <c r="F53" s="133" t="inlineStr">
+      <c r="F63" s="133" t="inlineStr">
         <is>
           <t>Food safety and quality management are a likely material topic for food and agriculture organizations.</t>
         </is>
       </c>
-      <c r="G53" s="133" t="inlineStr">
+      <c r="G63" s="133" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H53" s="133" t="inlineStr">
+      <c r="H63" s="133" t="inlineStr">
         <is>
           <t>Agricultural organizations producing food and feed</t>
         </is>
       </c>
-      <c r="I53" s="133" t="inlineStr">
+      <c r="I63" s="133" t="inlineStr">
         <is>
           <t>Likely material per GRI 13</t>
         </is>
       </c>
-      <c r="J53" s="133" t="inlineStr">
+      <c r="J63" s="133" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K53" s="133" t="inlineStr">
+      <c r="K63" s="133" t="inlineStr">
         <is>
           <t>Report: food safety management systems; certifications (HACCP, GFSI); incidents; recalls; pesticide residue testing; contaminant monitoring.</t>
         </is>
       </c>
-      <c r="L53" s="124" t="inlineStr">
+      <c r="L63" s="124" t="inlineStr">
         <is>
           <t>• HACCP plan documentation
 • GFSI certification records (BRCGS, SQF, FSSC 22000)
@@ -24231,7 +25409,7 @@
 • Regulatory compliance records</t>
         </is>
       </c>
-      <c r="M53" s="125" t="inlineStr">
+      <c r="M63" s="125" t="inlineStr">
         <is>
           <t>• GFSI certification certificates
 • Food safety audit reports
@@ -24240,7 +25418,7 @@
 • Regulatory inspection records</t>
         </is>
       </c>
-      <c r="N53" s="126" t="inlineStr">
+      <c r="N63" s="126" t="inlineStr">
         <is>
           <t>• HACCP/GFSI certification status
 • Number of food safety incidents
@@ -24251,22 +25429,22 @@
 • Traceability system coverage</t>
         </is>
       </c>
-      <c r="O53" s="127" t="inlineStr">
+      <c r="O63" s="127" t="inlineStr">
         <is>
           <t>Recall rate = Recalls / Total products / 1000. MRL compliance = Samples within limits / Total samples × 100. Audit non-conformance rate = NCRs / Total audit findings × 100.</t>
         </is>
       </c>
-      <c r="P53" s="133" t="inlineStr">
+      <c r="P63" s="133" t="inlineStr">
         <is>
           <t>Quality / Operations / Food Safety / Legal / Procurement</t>
         </is>
       </c>
-      <c r="Q53" s="133" t="inlineStr">
+      <c r="Q63" s="133" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R53" s="128" t="inlineStr">
+      <c r="R63" s="128" t="inlineStr">
         <is>
           <t>• GFSI (Global Food Safety Initiative) benchmarks: BRCGS, SQF, FSSC 22000, IFS
 • EU General Food Law (Regulation 178/2002) mandates traceability
@@ -24274,7 +25452,7 @@
 • Assurers need certification evidence, not self-declaration</t>
         </is>
       </c>
-      <c r="S53" s="129" t="inlineStr">
+      <c r="S63" s="129" t="inlineStr">
         <is>
           <t>• Is GFSI certification maintained across all production sites?
 • Are food safety incidents and recalls tracked in a formal register?
@@ -24282,69 +25460,69 @@
 • Is product traceability implemented end-to-end?</t>
         </is>
       </c>
-      <c r="T53" s="133" t="inlineStr">
+      <c r="T63" s="133" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.6 | V1.1 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="130" customHeight="1" s="42">
-      <c r="A54" s="122" t="inlineStr">
+    <row r="64" ht="130" customHeight="1" s="42">
+      <c r="A64" s="122" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
         </is>
       </c>
-      <c r="B54" s="122" t="inlineStr">
+      <c r="B64" s="122" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C54" s="122" t="inlineStr">
+      <c r="C64" s="122" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Social</t>
         </is>
       </c>
-      <c r="D54" s="123" t="inlineStr">
+      <c r="D64" s="123" t="inlineStr">
         <is>
           <t>GRI 13 — Topic 13.7</t>
         </is>
       </c>
-      <c r="E54" s="122" t="inlineStr">
+      <c r="E64" s="122" t="inlineStr">
         <is>
           <t>Product Labeling and Marketing (Agriculture)</t>
         </is>
       </c>
-      <c r="F54" s="122" t="inlineStr">
+      <c r="F64" s="122" t="inlineStr">
         <is>
           <t>Product labeling, claims, and marketing practices are a likely material topic for agricultural organizations.</t>
         </is>
       </c>
-      <c r="G54" s="122" t="inlineStr">
+      <c r="G64" s="122" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H54" s="122" t="inlineStr">
+      <c r="H64" s="122" t="inlineStr">
         <is>
           <t>Agricultural organizations selling food and feed products</t>
         </is>
       </c>
-      <c r="I54" s="122" t="inlineStr">
+      <c r="I64" s="122" t="inlineStr">
         <is>
           <t>Likely material per GRI 13</t>
         </is>
       </c>
-      <c r="J54" s="122" t="inlineStr">
+      <c r="J64" s="122" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K54" s="122" t="inlineStr">
+      <c r="K64" s="122" t="inlineStr">
         <is>
           <t>Report: labeling policy; environmental and social labeling claims; certification labels used; incidents of non-compliance; greenwashing risk management.</t>
         </is>
       </c>
-      <c r="L54" s="124" t="inlineStr">
+      <c r="L64" s="124" t="inlineStr">
         <is>
           <t>• Labeling policy documentation
 • Certification label licensing records
@@ -24355,7 +25533,7 @@
 • Greenwashing risk assessment</t>
         </is>
       </c>
-      <c r="M54" s="125" t="inlineStr">
+      <c r="M64" s="125" t="inlineStr">
         <is>
           <t>• Certification label licensing records
 • Labeling audit reports
@@ -24363,7 +25541,7 @@
 • Non-compliance case records</t>
         </is>
       </c>
-      <c r="N54" s="126" t="inlineStr">
+      <c r="N64" s="126" t="inlineStr">
         <is>
           <t>• % products with certified labels
 • Types of labels used (organic, Fairtrade, Rainforest Alliance, etc.)
@@ -24372,22 +25550,22 @@
 • Jurisdictions with labeling requirements met</t>
         </is>
       </c>
-      <c r="O54" s="127" t="inlineStr">
+      <c r="O64" s="127" t="inlineStr">
         <is>
           <t>Label coverage = Products with certified label / Total products × 100. Non-compliance rate = Labeling incidents / Total products × 100.</t>
         </is>
       </c>
-      <c r="P54" s="122" t="inlineStr">
+      <c r="P64" s="122" t="inlineStr">
         <is>
           <t>Marketing / Legal / Quality / Sustainability</t>
         </is>
       </c>
-      <c r="Q54" s="122" t="inlineStr">
+      <c r="Q64" s="122" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R54" s="128" t="inlineStr">
+      <c r="R64" s="128" t="inlineStr">
         <is>
           <t>• EU Green Claims Directive will impose strict substantiation requirements for environmental marketing claims
 • Organic labeling is strictly regulated (EU Reg 2018/848)
@@ -24395,7 +25573,7 @@
 • Assurers look for certification body audit records, not just label presence</t>
         </is>
       </c>
-      <c r="S54" s="129" t="inlineStr">
+      <c r="S64" s="129" t="inlineStr">
         <is>
           <t>• Are all environmental and social claims on labels substantiated by certification?
 • Are labeling non-compliances tracked and corrected?
@@ -24403,69 +25581,69 @@
 • Are certification audits maintained for all label types used?</t>
         </is>
       </c>
-      <c r="T54" s="122" t="inlineStr">
+      <c r="T64" s="122" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.7 | V1.1 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="130" customHeight="1" s="42">
-      <c r="A55" s="133" t="inlineStr">
+    <row r="65" ht="130" customHeight="1" s="42">
+      <c r="A65" s="133" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
         </is>
       </c>
-      <c r="B55" s="133" t="inlineStr">
+      <c r="B65" s="133" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C55" s="133" t="inlineStr">
+      <c r="C65" s="133" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Social</t>
         </is>
       </c>
-      <c r="D55" s="134" t="inlineStr">
+      <c r="D65" s="134" t="inlineStr">
         <is>
           <t>GRI 13 — Topic 13.9</t>
         </is>
       </c>
-      <c r="E55" s="133" t="inlineStr">
+      <c r="E65" s="133" t="inlineStr">
         <is>
           <t>Local Communities (Agriculture)</t>
         </is>
       </c>
-      <c r="F55" s="133" t="inlineStr">
+      <c r="F65" s="133" t="inlineStr">
         <is>
           <t>Impacts on local and rural communities from agricultural operations are a likely material topic.</t>
         </is>
       </c>
-      <c r="G55" s="133" t="inlineStr">
+      <c r="G65" s="133" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H55" s="133" t="inlineStr">
+      <c r="H65" s="133" t="inlineStr">
         <is>
           <t>Agricultural organizations with community-dependent operations</t>
         </is>
       </c>
-      <c r="I55" s="133" t="inlineStr">
+      <c r="I65" s="133" t="inlineStr">
         <is>
           <t>Likely material per GRI 13</t>
         </is>
       </c>
-      <c r="J55" s="133" t="inlineStr">
+      <c r="J65" s="133" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K55" s="133" t="inlineStr">
+      <c r="K65" s="133" t="inlineStr">
         <is>
           <t>Report: community engagement; grievance mechanisms; community benefit sharing; rural development investment; smallholder farmer support.</t>
         </is>
       </c>
-      <c r="L55" s="124" t="inlineStr">
+      <c r="L65" s="124" t="inlineStr">
         <is>
           <t>• Community engagement records
 • Grievance register and resolution data
@@ -24475,7 +25653,7 @@
 • Social impact assessments</t>
         </is>
       </c>
-      <c r="M55" s="125" t="inlineStr">
+      <c r="M65" s="125" t="inlineStr">
         <is>
           <t>• Community engagement records
 • Grievance records
@@ -24483,7 +25661,7 @@
 • Community investment data</t>
         </is>
       </c>
-      <c r="N55" s="126" t="inlineStr">
+      <c r="N65" s="126" t="inlineStr">
         <is>
           <t>• Community grievances (count and resolution rate)
 • Community investment ($)
@@ -24492,22 +25670,22 @@
 • Community benefit agreements</t>
         </is>
       </c>
-      <c r="O55" s="127" t="inlineStr">
+      <c r="O65" s="127" t="inlineStr">
         <is>
           <t>Grievance resolution = Resolved / Total × 100. Smallholder support investment = $ invested / Farmer supported.</t>
         </is>
       </c>
-      <c r="P55" s="133" t="inlineStr">
+      <c r="P65" s="133" t="inlineStr">
         <is>
           <t>Community Affairs / Sustainability / Operations</t>
         </is>
       </c>
-      <c r="Q55" s="133" t="inlineStr">
+      <c r="Q65" s="133" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R55" s="128" t="inlineStr">
+      <c r="R65" s="128" t="inlineStr">
         <is>
           <t>• Smallholder farmers are central to agricultural supply chains — fair price is key
 • ILO Living Wage for agricultural workers is a growing expectation
@@ -24515,7 +25693,7 @@
 • Community land rights are at risk from large-scale land acquisition</t>
         </is>
       </c>
-      <c r="S55" s="129" t="inlineStr">
+      <c r="S65" s="129" t="inlineStr">
         <is>
           <t>• Are smallholder farmer livelihoods formally assessed?
 • Is a community grievance mechanism accessible in local languages?
@@ -24523,69 +25701,69 @@
 • Are FPIC processes conducted for land acquisitions?</t>
         </is>
       </c>
-      <c r="T55" s="133" t="inlineStr">
+      <c r="T65" s="133" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.9 | V1.1 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="130" customHeight="1" s="42">
-      <c r="A56" s="122" t="inlineStr">
+    <row r="66" ht="130" customHeight="1" s="42">
+      <c r="A66" s="122" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
         </is>
       </c>
-      <c r="B56" s="122" t="inlineStr">
+      <c r="B66" s="122" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C56" s="122" t="inlineStr">
+      <c r="C66" s="122" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Social</t>
         </is>
       </c>
-      <c r="D56" s="123" t="inlineStr">
+      <c r="D66" s="123" t="inlineStr">
         <is>
           <t>GRI 13 — Topic 13.10</t>
         </is>
       </c>
-      <c r="E56" s="122" t="inlineStr">
+      <c r="E66" s="122" t="inlineStr">
         <is>
           <t>Land Rights (Agriculture)</t>
         </is>
       </c>
-      <c r="F56" s="122" t="inlineStr">
+      <c r="F66" s="122" t="inlineStr">
         <is>
           <t>Land rights, land tenure security, and prevention of land grabbing are a likely material topic for agriculture.</t>
         </is>
       </c>
-      <c r="G56" s="122" t="inlineStr">
+      <c r="G66" s="122" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H56" s="122" t="inlineStr">
+      <c r="H66" s="122" t="inlineStr">
         <is>
           <t>Agricultural organizations with significant land holdings or acquisitions</t>
         </is>
       </c>
-      <c r="I56" s="122" t="inlineStr">
+      <c r="I66" s="122" t="inlineStr">
         <is>
           <t>Likely material per GRI 13</t>
         </is>
       </c>
-      <c r="J56" s="122" t="inlineStr">
+      <c r="J66" s="122" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K56" s="122" t="inlineStr">
+      <c r="K66" s="122" t="inlineStr">
         <is>
           <t>Report: land tenure documentation; land acquisition due diligence; land rights disputes; FPIC; community land rights protection.</t>
         </is>
       </c>
-      <c r="L56" s="124" t="inlineStr">
+      <c r="L66" s="124" t="inlineStr">
         <is>
           <t>• Land title and ownership records
 • Land due diligence assessment reports
@@ -24596,7 +25774,7 @@
 • Voluntary Guidelines on RTTG compliance documents</t>
         </is>
       </c>
-      <c r="M56" s="125" t="inlineStr">
+      <c r="M66" s="125" t="inlineStr">
         <is>
           <t>• Land title records
 • Land due diligence reports
@@ -24605,7 +25783,7 @@
 • Regulatory land rights compliance</t>
         </is>
       </c>
-      <c r="N56" s="126" t="inlineStr">
+      <c r="N66" s="126" t="inlineStr">
         <is>
           <t>• Total land held by type (owned, leased, licensed)
 • Land acquisitions in period (ha)
@@ -24615,22 +25793,22 @@
 • Disputed area resolved</t>
         </is>
       </c>
-      <c r="O56" s="127" t="inlineStr">
+      <c r="O66" s="127" t="inlineStr">
         <is>
           <t>Land acquisition due diligence rate = Acquisitions with full due diligence / Total acquisitions × 100.</t>
         </is>
       </c>
-      <c r="P56" s="122" t="inlineStr">
+      <c r="P66" s="122" t="inlineStr">
         <is>
           <t>Legal / Land Management / Sustainability / Community Affairs</t>
         </is>
       </c>
-      <c r="Q56" s="122" t="inlineStr">
+      <c r="Q66" s="122" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R56" s="128" t="inlineStr">
+      <c r="R66" s="128" t="inlineStr">
         <is>
           <t>• UN Voluntary Guidelines on Responsible Governance of Tenure (VGGT) are the global standard
 • EU Deforestation Regulation requires land ownership due diligence for key commodities
@@ -24638,7 +25816,7 @@
 • IFC PS5 governs physical and economic displacement</t>
         </is>
       </c>
-      <c r="S56" s="129" t="inlineStr">
+      <c r="S66" s="129" t="inlineStr">
         <is>
           <t>• Is land title due diligence conducted for all significant land acquisitions?
 • Are FPIC processes documented for acquisitions affecting communities?
@@ -24646,69 +25824,69 @@
 • Are land rights disputes tracked and resolved?</t>
         </is>
       </c>
-      <c r="T56" s="122" t="inlineStr">
+      <c r="T66" s="122" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.10 | V1.1 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="130" customHeight="1" s="42">
-      <c r="A57" s="133" t="inlineStr">
+    <row r="67" ht="130" customHeight="1" s="42">
+      <c r="A67" s="133" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
         </is>
       </c>
-      <c r="B57" s="133" t="inlineStr">
+      <c r="B67" s="133" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C57" s="133" t="inlineStr">
+      <c r="C67" s="133" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Social</t>
         </is>
       </c>
-      <c r="D57" s="134" t="inlineStr">
+      <c r="D67" s="134" t="inlineStr">
         <is>
           <t>GRI 13 — Topic 13.11</t>
         </is>
       </c>
-      <c r="E57" s="133" t="inlineStr">
+      <c r="E67" s="133" t="inlineStr">
         <is>
           <t>Rights of Indigenous Peoples (Agriculture)</t>
         </is>
       </c>
-      <c r="F57" s="133" t="inlineStr">
+      <c r="F67" s="133" t="inlineStr">
         <is>
           <t>Respect for rights of indigenous peoples is a likely material topic for agriculture on or near indigenous territories.</t>
         </is>
       </c>
-      <c r="G57" s="133" t="inlineStr">
+      <c r="G67" s="133" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H57" s="133" t="inlineStr">
+      <c r="H67" s="133" t="inlineStr">
         <is>
           <t>Agricultural organizations operating near indigenous territories</t>
         </is>
       </c>
-      <c r="I57" s="133" t="inlineStr">
+      <c r="I67" s="133" t="inlineStr">
         <is>
           <t>Likely material per GRI 13</t>
         </is>
       </c>
-      <c r="J57" s="133" t="inlineStr">
+      <c r="J67" s="133" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K57" s="133" t="inlineStr">
+      <c r="K67" s="133" t="inlineStr">
         <is>
           <t>Report: FPIC processes; indigenous land rights; cultural heritage protection; violations; UNDRIP alignment.</t>
         </is>
       </c>
-      <c r="L57" s="124" t="inlineStr">
+      <c r="L67" s="124" t="inlineStr">
         <is>
           <t>• FPIC documentation
 • Indigenous community engagement records
@@ -24718,7 +25896,7 @@
 • Land rights records for indigenous territories</t>
         </is>
       </c>
-      <c r="M57" s="125" t="inlineStr">
+      <c r="M67" s="125" t="inlineStr">
         <is>
           <t>• FPIC process records
 • Community engagement documentation
@@ -24726,7 +25904,7 @@
 • Incident records</t>
         </is>
       </c>
-      <c r="N57" s="126" t="inlineStr">
+      <c r="N67" s="126" t="inlineStr">
         <is>
           <t>• FPIC processes (count)
 • Indigenous communities engaged
@@ -24735,98 +25913,98 @@
 • Remediation actions</t>
         </is>
       </c>
-      <c r="O57" s="127" t="inlineStr">
+      <c r="O67" s="127" t="inlineStr">
         <is>
           <t>FPIC compliance = Projects with FPIC / Projects requiring FPIC × 100.</t>
         </is>
       </c>
-      <c r="P57" s="133" t="inlineStr">
+      <c r="P67" s="133" t="inlineStr">
         <is>
           <t>Legal / Community Affairs / Sustainability</t>
         </is>
       </c>
-      <c r="Q57" s="133" t="inlineStr">
+      <c r="Q67" s="133" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R57" s="128" t="inlineStr">
+      <c r="R67" s="128" t="inlineStr">
         <is>
           <t>• Agricultural expansion into indigenous territories is a high litigation risk
 • ILO 169 and UNDRIP are foundational instruments
 • EU Deforestation Regulation requires no deforestation on indigenous lands</t>
         </is>
       </c>
-      <c r="S57" s="129" t="inlineStr">
+      <c r="S67" s="129" t="inlineStr">
         <is>
           <t>• Are FPIC processes documented for all activities on indigenous lands?
 • Is cultural heritage assessment conducted?
 • Is UNDRIP compliance formally assessed?</t>
         </is>
       </c>
-      <c r="T57" s="133" t="inlineStr">
+      <c r="T67" s="133" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.11 | V1.1 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="130" customHeight="1" s="42">
-      <c r="A58" s="122" t="inlineStr">
+    <row r="68" ht="130" customHeight="1" s="42">
+      <c r="A68" s="122" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
         </is>
       </c>
-      <c r="B58" s="122" t="inlineStr">
+      <c r="B68" s="122" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C58" s="122" t="inlineStr">
+      <c r="C68" s="122" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Labor</t>
         </is>
       </c>
-      <c r="D58" s="123" t="inlineStr">
+      <c r="D68" s="123" t="inlineStr">
         <is>
           <t>GRI 13 — Topic 13.12</t>
         </is>
       </c>
-      <c r="E58" s="122" t="inlineStr">
+      <c r="E68" s="122" t="inlineStr">
         <is>
           <t>Employment Practices (Agriculture)</t>
         </is>
       </c>
-      <c r="F58" s="122" t="inlineStr">
+      <c r="F68" s="122" t="inlineStr">
         <is>
           <t>Employment conditions, wages, and worker rights are a likely material topic in agriculture.</t>
         </is>
       </c>
-      <c r="G58" s="122" t="inlineStr">
+      <c r="G68" s="122" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H58" s="122" t="inlineStr">
+      <c r="H68" s="122" t="inlineStr">
         <is>
           <t>All agricultural sector organizations</t>
         </is>
       </c>
-      <c r="I58" s="122" t="inlineStr">
+      <c r="I68" s="122" t="inlineStr">
         <is>
           <t>Likely material per GRI 13</t>
         </is>
       </c>
-      <c r="J58" s="122" t="inlineStr">
+      <c r="J68" s="122" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K58" s="122" t="inlineStr">
+      <c r="K68" s="122" t="inlineStr">
         <is>
           <t>Report: workforce composition; seasonal worker management; wages vs. living wage; CBA coverage; migrant worker protections; benefits.</t>
         </is>
       </c>
-      <c r="L58" s="124" t="inlineStr">
+      <c r="L68" s="124" t="inlineStr">
         <is>
           <t>• Workforce census (permanent, seasonal, migrant)
 • Payroll records
@@ -24837,7 +26015,7 @@
 • Benefits by worker category</t>
         </is>
       </c>
-      <c r="M58" s="125" t="inlineStr">
+      <c r="M68" s="125" t="inlineStr">
         <is>
           <t>• HR census data
 • Payroll records
@@ -24846,7 +26024,7 @@
 • Worker survey data</t>
         </is>
       </c>
-      <c r="N58" s="126" t="inlineStr">
+      <c r="N68" s="126" t="inlineStr">
         <is>
           <t>• Total workers by category
 • Living wage benchmark vs. actual wages
@@ -24856,22 +26034,22 @@
 • Gender pay gap</t>
         </is>
       </c>
-      <c r="O58" s="127" t="inlineStr">
+      <c r="O68" s="127" t="inlineStr">
         <is>
           <t>Living wage gap = (Living wage benchmark − Actual wage) / Living wage benchmark × 100. CBA coverage = CBA workers / Total × 100.</t>
         </is>
       </c>
-      <c r="P58" s="122" t="inlineStr">
+      <c r="P68" s="122" t="inlineStr">
         <is>
           <t>HR / Operations / Labor Relations</t>
         </is>
       </c>
-      <c r="Q58" s="122" t="inlineStr">
+      <c r="Q68" s="122" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R58" s="128" t="inlineStr">
+      <c r="R68" s="128" t="inlineStr">
         <is>
           <t>• Agriculture is the sector with highest risk of wage below living wage — Anker methodology
 • Seasonal workers often have weakest employment protections
@@ -24879,76 +26057,76 @@
 • Living wage disclosure expected by major food companies via supply chain requirements</t>
         </is>
       </c>
-      <c r="S58" s="129" t="inlineStr">
+      <c r="S68" s="129" t="inlineStr">
         <is>
           <t>• Is a living wage assessment conducted against Anker benchmark?
 • Are seasonal workers' rights protected equivalently to permanent workers?
 • Is a zero-fee recruitment policy applied for migrant workers?</t>
         </is>
       </c>
-      <c r="T58" s="122" t="inlineStr">
+      <c r="T68" s="122" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.12 | V1.1 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="130" customHeight="1" s="42">
-      <c r="A59" s="133" t="inlineStr">
+    <row r="69" ht="130" customHeight="1" s="42">
+      <c r="A69" s="133" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
         </is>
       </c>
-      <c r="B59" s="133" t="inlineStr">
+      <c r="B69" s="133" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C59" s="133" t="inlineStr">
+      <c r="C69" s="133" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Governance</t>
         </is>
       </c>
-      <c r="D59" s="134" t="inlineStr">
+      <c r="D69" s="134" t="inlineStr">
         <is>
           <t>GRI 13 — Topic 13.13</t>
         </is>
       </c>
-      <c r="E59" s="133" t="inlineStr">
+      <c r="E69" s="133" t="inlineStr">
         <is>
           <t>Anti-corruption (Agriculture)</t>
         </is>
       </c>
-      <c r="F59" s="133" t="inlineStr">
+      <c r="F69" s="133" t="inlineStr">
         <is>
           <t>Anti-corruption policies and practices are a likely material topic for agricultural organizations.</t>
         </is>
       </c>
-      <c r="G59" s="133" t="inlineStr">
+      <c r="G69" s="133" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H59" s="133" t="inlineStr">
+      <c r="H69" s="133" t="inlineStr">
         <is>
           <t>All agricultural sector organizations</t>
         </is>
       </c>
-      <c r="I59" s="133" t="inlineStr">
+      <c r="I69" s="133" t="inlineStr">
         <is>
           <t>Likely material per GRI 13</t>
         </is>
       </c>
-      <c r="J59" s="133" t="inlineStr">
+      <c r="J69" s="133" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K59" s="133" t="inlineStr">
+      <c r="K69" s="133" t="inlineStr">
         <is>
           <t>Report: anti-corruption policy; training; confirmed incidents; payments; due diligence for high-risk markets.</t>
         </is>
       </c>
-      <c r="L59" s="124" t="inlineStr">
+      <c r="L69" s="124" t="inlineStr">
         <is>
           <t>• Anti-corruption policy
 • Training records
@@ -24957,14 +26135,14 @@
 • Third-party due diligence records</t>
         </is>
       </c>
-      <c r="M59" s="125" t="inlineStr">
+      <c r="M69" s="125" t="inlineStr">
         <is>
           <t>• Policy documentation
 • Training completion records
 • Incident and resolution records</t>
         </is>
       </c>
-      <c r="N59" s="126" t="inlineStr">
+      <c r="N69" s="126" t="inlineStr">
         <is>
           <t>• Policy in place (yes/no)
 • Training coverage (%)
@@ -24973,105 +26151,2072 @@
 • Remediation actions</t>
         </is>
       </c>
-      <c r="O59" s="127" t="inlineStr">
+      <c r="O69" s="127" t="inlineStr">
         <is>
           <t>Training coverage = Employees trained / Total employees × 100.</t>
         </is>
       </c>
-      <c r="P59" s="133" t="inlineStr">
+      <c r="P69" s="133" t="inlineStr">
         <is>
           <t>Legal / Compliance / Finance</t>
         </is>
       </c>
-      <c r="Q59" s="133" t="inlineStr">
+      <c r="Q69" s="133" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R59" s="128" t="inlineStr">
+      <c r="R69" s="128" t="inlineStr">
         <is>
           <t>• Agricultural markets in developing countries have high corruption risk
 • FCPA and UK Bribery Act extraterritorial jurisdiction
 • Customs and border controls are common corruption touchpoints in agricultural trade</t>
         </is>
       </c>
-      <c r="S59" s="129" t="inlineStr">
+      <c r="S69" s="129" t="inlineStr">
         <is>
           <t>• Is anti-corruption training mandatory for staff in high-risk markets?
 • Are agents and intermediaries subject to due diligence?
 • Are all confirmed incidents investigated?</t>
         </is>
       </c>
-      <c r="T59" s="133" t="inlineStr">
+      <c r="T69" s="133" t="inlineStr">
         <is>
           <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.13 | V1.1 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="22" customHeight="1" s="42">
-      <c r="A60" s="132" t="inlineStr">
+    <row r="70" ht="22" customHeight="1" s="42">
+      <c r="A70" s="132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 — Additional Topics (13.14–13.28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="130" customHeight="1" s="42">
+      <c r="A71" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B71" s="122" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C71" s="122" t="inlineStr">
+        <is>
+          <t>Social Topics — Forced Labour</t>
+        </is>
+      </c>
+      <c r="D71" s="123" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.14</t>
+        </is>
+      </c>
+      <c r="E71" s="122" t="inlineStr">
+        <is>
+          <t>Forced Labour and Modern Slavery</t>
+        </is>
+      </c>
+      <c r="F71" s="122" t="inlineStr">
+        <is>
+          <t>Agriculture sector entities must report on the risk of forced labour and modern slavery in farming, processing, and fishing supply chains.</t>
+        </is>
+      </c>
+      <c r="G71" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H71" s="122" t="inlineStr">
+        <is>
+          <t>All agricultural, aquaculture, and fishing entities</t>
+        </is>
+      </c>
+      <c r="I71" s="122" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J71" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K71" s="122" t="inlineStr">
+        <is>
+          <t>Report using GRI 409 (Forced or Compulsory Labour). Sector-specific considerations include: (a) debt bondage and recruitment fee exploitation of seasonal and migrant agricultural workers; (b) forced labour risk in fishing vessels and aquaculture operations; (c) passport confiscation in agricultural worker housing; (d) supply chain traceability and due diligence for forced labour in commodity supply chains (cocoa, palm oil, shrimp, coffee, rubber); (e) UK Modern Slavery Act and equivalent statute compliance.</t>
+        </is>
+      </c>
+      <c r="L71" s="124" t="inlineStr">
+        <is>
+          <t>• Modern Slavery Act statement (board-approved, published)
+• Forced labour risk assessment for operations and supply chain
+• Migrant and seasonal worker recruitment policy and records
+• No-recruitment-fee policy and monitoring records
+• Labour broker screening and management records
+• Supply chain audit programme results (forced labour focus)
+• Worker voice mechanisms accessible to migrant workers
+• Remediation programme documentation for identified cases
+• ILO Convention C29 and C105 compliance records
+• Agricultural commodity traceability records</t>
+        </is>
+      </c>
+      <c r="M71" s="125" t="inlineStr">
+        <is>
+          <t>• Modern Slavery Act statement (signed, published)
+• Supply chain social audit results for forced labour
+• Recruitment fee compliance monitoring records
+• Remediation case records
+• Independent worker survey results on debt bondage indicators
+• Third-party certification (Fairtrade, Rainforest Alliance, MSC) records
+• Government compliance records for labour law in operations countries</t>
+        </is>
+      </c>
+      <c r="N71" s="126" t="inlineStr">
+        <is>
+          <t>• Number of workers assessed for forced labour risk
+• Number of forced labour incidents identified and remediated
+• Percentage of migrant workers with zero recruitment fees (%)
+• Supply chain audit coverage in high-risk geographies (%)
+• Number of workers in remediation programmes
+• Commodity traceability coverage (% of supply by commodity)
+• Number of farms or fishing vessels with forced labour audits
+• Labour broker audit coverage (%)</t>
+        </is>
+      </c>
+      <c r="O71" s="127" t="inlineStr">
+        <is>
+          <t>Zero-fee compliance = Workers paying zero fees / Total migrant workers × 100. Forced labour audit coverage = High-risk suppliers audited / Total high-risk suppliers × 100. Remediation rate = Cases remediated / Cases identified × 100. Commodity traceability = Volume traceable to farm/vessel / Total volume sourced × 100.</t>
+        </is>
+      </c>
+      <c r="P71" s="122" t="inlineStr">
+        <is>
+          <t>Supply Chain / Human Rights / Procurement / Sustainability / Legal</t>
+        </is>
+      </c>
+      <c r="Q71" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R71" s="128" t="inlineStr">
+        <is>
+          <t>• Agricultural and fishing sectors are among the highest-risk sectors for forced labour globally
+• Seasonal and migrant workers are most vulnerable — specific monitoring is required
+• Passport confiscation is an absolute red line — one confirmed case requires escalation
+• Fishing vessels at sea present unique monitoring challenges requiring specialist audit methodologies
+• Commodity traceability (farm-level) is increasingly expected by investors and regulators</t>
+        </is>
+      </c>
+      <c r="S71" s="129" t="inlineStr">
+        <is>
+          <t>• Is there a board-approved Modern Slavery Act statement with specific agricultural sector risk analysis?
+• Are seasonal and migrant worker recruitment channels monitored for debt bondage risk?
+• Does the organisation have supply chain visibility to farm and vessel level for forced labour risk?
+• Is there a credible remediation programme for identified forced labour cases?</t>
+        </is>
+      </c>
+      <c r="T71" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.14 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="130" customHeight="1" s="42">
+      <c r="A72" s="133" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B72" s="133" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C72" s="133" t="inlineStr">
+        <is>
+          <t>Social Topics — Child Labour</t>
+        </is>
+      </c>
+      <c r="D72" s="134" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.15</t>
+        </is>
+      </c>
+      <c r="E72" s="133" t="inlineStr">
+        <is>
+          <t>Child Labour</t>
+        </is>
+      </c>
+      <c r="F72" s="133" t="inlineStr">
+        <is>
+          <t>Report on measures to prevent child labour in agricultural, aquaculture, and fishing operations and supply chains.</t>
+        </is>
+      </c>
+      <c r="G72" s="133" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H72" s="133" t="inlineStr">
+        <is>
+          <t>All agricultural, aquaculture, and fishing entities</t>
+        </is>
+      </c>
+      <c r="I72" s="133" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J72" s="133" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K72" s="133" t="inlineStr">
+        <is>
+          <t>Report using GRI 408 (Child Labour). Sector-specific considerations include: (a) child labour risk in smallholder farming supply chains (cocoa, coffee, tobacco, cotton); (b) hazardous child labour in agriculture (pesticide exposure, heavy machinery); (c) child labour on fishing vessels; (d) community-based child labour monitoring systems (CLMS); (e) school enrolment programmes in sourcing communities.</t>
+        </is>
+      </c>
+      <c r="L72" s="124" t="inlineStr">
+        <is>
+          <t>• Child labour risk assessment for operations and supply chain
+• Age verification procedures and records for all workers
+• Community-based child labour monitoring system (CLMS) documentation
+• School enrolment and retention programme records
+• Supplier and farm audit results for child labour
+• Remediation programme documentation
+• ILO Conventions C138 and C182 compliance records
+• Commodity-specific child labour action plan records
+• Hazardous work exclusion documentation
+• Agricultural extension programme records</t>
+        </is>
+      </c>
+      <c r="M72" s="125" t="inlineStr">
+        <is>
+          <t>• Age verification records for direct and contract workers
+• Child labour audit results by farm/supplier
+• CLMS monitoring reports
+• School enrolment data from sourcing communities
+• Remediation records for identified cases
+• ILO convention compliance confirmation
+• Third-party certification records (Fairtrade, UTZ) for child labour criteria</t>
+        </is>
+      </c>
+      <c r="N72" s="126" t="inlineStr">
+        <is>
+          <t>• Number of farms/vessels audited for child labour
+• Number of child labour incidents identified
+• Percentage of suppliers audited for child labour (%)
+• Number of children enrolled in CLMS-linked programmes
+• School enrolment rate in sourcing communities (%)
+• Number of remediation cases and outcomes
+• Hazardous work assessment coverage (%)
+• Age verification rate for direct and contracted workers (%)</t>
+        </is>
+      </c>
+      <c r="O72" s="127" t="inlineStr">
+        <is>
+          <t>Supplier audit coverage = Suppliers audited / Total suppliers × 100. Age verification rate = Workers age-verified / Total workers hired × 100. CLMS coverage = Communities with CLMS / Total sourcing communities × 100. Remediation rate = Children remediated / Children identified in child labour × 100.</t>
+        </is>
+      </c>
+      <c r="P72" s="133" t="inlineStr">
+        <is>
+          <t>Supply Chain / HR / Sustainability / Community Affairs / Human Rights</t>
+        </is>
+      </c>
+      <c r="Q72" s="133" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R72" s="128" t="inlineStr">
+        <is>
+          <t>• Child labour in cocoa and coffee supply chains is a global audit focus — expect intense scrutiny
+• CLMS is the gold-standard approach for community-level monitoring in agricultural supply chains
+• ILO C182 hazardous work list for agriculture is specific — must be applied at farm level
+• Remediation must include family support and school enrolment, not just removal from work
+• Third-party certification (Fairtrade, Rainforest Alliance) provides some but not all required coverage</t>
+        </is>
+      </c>
+      <c r="S72" s="129" t="inlineStr">
+        <is>
+          <t>• Does the child labour risk assessment extend to smallholder supplier farms and fishing vessels?
+• Is there a community-based child labour monitoring system in place in high-risk sourcing areas?
+• Does the remediation approach include school enrolment support for identified children?
+• Are hazardous work assessments conducted at farm level to identify age-restricted tasks?</t>
+        </is>
+      </c>
+      <c r="T72" s="133" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.15 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="130" customHeight="1" s="42">
+      <c r="A73" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B73" s="122" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C73" s="122" t="inlineStr">
+        <is>
+          <t>Social Topics — Freedom of Association</t>
+        </is>
+      </c>
+      <c r="D73" s="123" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.16</t>
+        </is>
+      </c>
+      <c r="E73" s="122" t="inlineStr">
+        <is>
+          <t>Freedom of Association and Collective Bargaining</t>
+        </is>
+      </c>
+      <c r="F73" s="122" t="inlineStr">
+        <is>
+          <t>Report on respect for workers' rights to freedom of association and collective bargaining in agricultural operations and supply chains.</t>
+        </is>
+      </c>
+      <c r="G73" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H73" s="122" t="inlineStr">
+        <is>
+          <t>All agricultural, aquaculture, and fishing entities</t>
+        </is>
+      </c>
+      <c r="I73" s="122" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J73" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K73" s="122" t="inlineStr">
+        <is>
+          <t>Report using GRI 407 (Freedom of Association and Collective Bargaining). Sector-specific considerations include: (a) labour relations in seasonal and migrant-dominated agricultural workforces; (b) operations in jurisdictions restricting trade union rights; (c) smallholder worker representation challenges; (d) collective bargaining coverage for fisheries workers; (e) enabling environment for worker voice on farms.</t>
+        </is>
+      </c>
+      <c r="L73" s="124" t="inlineStr">
+        <is>
+          <t>• Freedom of association policy
+• Collective bargaining agreement register
+• Trade union recognition records
+• Country risk assessment for freedom of association by operating jurisdiction
+• Migrant and seasonal worker representation documentation
+• Smallholder organisation engagement records
+• ILO Conventions C87 and C98 compliance assessment
+• Labour relations incident log
+• Alternative representation mechanism records (restricted jurisdictions)</t>
+        </is>
+      </c>
+      <c r="M73" s="125" t="inlineStr">
+        <is>
+          <t>• CBA documents signed by recognised unions
+• Trade union recognition certificates
+• Country risk assessment outputs by jurisdiction
+• Labour relations incident investigation reports
+• Worker representation election records
+• Government labour inspection reports
+• Smallholder cooperative engagement records</t>
+        </is>
+      </c>
+      <c r="N73" s="126" t="inlineStr">
+        <is>
+          <t>• Percentage of workers under collective bargaining agreements (%)
+• Number of trade unions recognised across operations
+• Number of operations in jurisdictions restricting freedom of association
+• Percentage of operations with alternative worker representation mechanisms (%)
+• Number of labour disputes (strikes, go-slows, sit-ins)
+• Number of smallholder farmers with cooperative or collective representation
+• Labour dispute resolution rate and average resolution time</t>
+        </is>
+      </c>
+      <c r="O73" s="127" t="inlineStr">
+        <is>
+          <t>CBA coverage = Workers under CBA / Total workers × 100. Restricted jurisdiction rate = Operations in restricted countries / Total operations × 100. Alternative representation coverage = Workers with alternative voice mechanism in restricted jurisdictions / Total workers in restricted jurisdictions × 100.</t>
+        </is>
+      </c>
+      <c r="P73" s="122" t="inlineStr">
+        <is>
+          <t>HR / Industrial Relations / Supply Chain / Legal / Sustainability</t>
+        </is>
+      </c>
+      <c r="Q73" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R73" s="128" t="inlineStr">
+        <is>
+          <t>• Seasonal workers often lack union access — specific mechanisms needed
+• Migrant workers face barriers to association — these must be addressed explicitly
+• Smallholder farmer organisations (cooperatives) are a proxy for collective voice
+• Operations in restricted jurisdictions require documented alternative mechanisms
+• Assurers will probe whether CBAs are genuine collective agreements or management-imposed</t>
+        </is>
+      </c>
+      <c r="S73" s="129" t="inlineStr">
+        <is>
+          <t>• What percentage of agricultural workers are covered by collective bargaining agreements?
+• Are seasonal and migrant workers able to exercise their right to association in practice?
+• Are there operations in jurisdictions where trade union rights are legally restricted?
+• What alternative representation mechanisms are in place in restricted jurisdictions?</t>
+        </is>
+      </c>
+      <c r="T73" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.16 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="130" customHeight="1" s="42">
+      <c r="A74" s="133" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B74" s="133" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C74" s="133" t="inlineStr">
+        <is>
+          <t>Social Topics — Non-discrimination</t>
+        </is>
+      </c>
+      <c r="D74" s="134" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.17</t>
+        </is>
+      </c>
+      <c r="E74" s="133" t="inlineStr">
+        <is>
+          <t>Non-discrimination and Equal Opportunity</t>
+        </is>
+      </c>
+      <c r="F74" s="133" t="inlineStr">
+        <is>
+          <t>Report on non-discrimination policies and equal opportunity practices in agricultural, aquaculture, and fishing operations.</t>
+        </is>
+      </c>
+      <c r="G74" s="133" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H74" s="133" t="inlineStr">
+        <is>
+          <t>All agricultural, aquaculture, and fishing entities</t>
+        </is>
+      </c>
+      <c r="I74" s="133" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J74" s="133" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K74" s="133" t="inlineStr">
+        <is>
+          <t>Report using GRI 406 (Non-discrimination). Sector-specific considerations include: (a) gender-based discrimination in agricultural labour markets; (b) discrimination against migrant workers and workers from ethnic minorities; (c) caste-based discrimination in South Asian agricultural supply chains; (d) gender representation in farm management and cooperatives; (e) equal pay and access to benefits for seasonal vs. permanent workers.</t>
+        </is>
+      </c>
+      <c r="L74" s="124" t="inlineStr">
+        <is>
+          <t>• Equal opportunity and non-discrimination policy
+• Diversity and inclusion strategy
+• Workforce diversity data disaggregated by gender, ethnicity, migrant status
+• Discrimination incident register and investigation records
+• Equal pay analysis (permanent vs. seasonal, gender)
+• Training records on discrimination prevention
+• Recruitment equity analysis
+• Grievance records specifically for discrimination cases
+• ILO Conventions C100 and C111 compliance assessment
+• Caste/ethnicity risk assessment for supply chain (where applicable)</t>
+        </is>
+      </c>
+      <c r="M74" s="125" t="inlineStr">
+        <is>
+          <t>• HRIS workforce data reports
+• Equal pay gap analysis
+• Discrimination complaint and investigation records
+• Training completion records
+• Regulatory compliance records for equal opportunity laws
+• Third-party social audit findings on discrimination</t>
+        </is>
+      </c>
+      <c r="N74" s="126" t="inlineStr">
+        <is>
+          <t>• Gender breakdown of workforce (%)
+• Percentage of female farm/vessel workers and managers (%)
+• Gender pay gap (%) for agricultural workers
+• Number of discrimination complaints by type (gender, ethnicity, nationality)
+• Substantiation rate for discrimination complaints (%)
+• Disciplinary actions for discrimination (count)
+• Seasonal worker pay gap vs. permanent equivalents (%)
+• Female representation on farmer cooperative boards (%)</t>
+        </is>
+      </c>
+      <c r="O74" s="127" t="inlineStr">
+        <is>
+          <t>Gender pay gap = (Male median pay − Female median pay) / Male median pay × 100. Female management representation = Female managers / Total managers × 100. Complaint substantiation rate = Substantiated complaints / Total complaints × 100. Seasonal pay parity = Seasonal worker equivalent hourly rate / Permanent worker rate × 100.</t>
+        </is>
+      </c>
+      <c r="P74" s="133" t="inlineStr">
+        <is>
+          <t>HR / Supply Chain / Sustainability / Human Rights / Legal</t>
+        </is>
+      </c>
+      <c r="Q74" s="133" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R74" s="128" t="inlineStr">
+        <is>
+          <t>• Gender discrimination in agriculture requires specific evidence beyond general diversity metrics
+• Caste-based discrimination is a material risk in South Asian supply chains — must be addressed explicitly
+• Seasonal worker pay parity is often overlooked — assurers now specifically request this
+• Female farmer cooperative representation is an increasingly tracked indicator
+• Discrimination complaint substantiation rates that are very low may indicate underreporting</t>
+        </is>
+      </c>
+      <c r="S74" s="129" t="inlineStr">
+        <is>
+          <t>• Are gender pay gaps calculated and disclosed for both direct and supply chain agricultural workers?
+• Are caste and ethnicity-based discrimination risks assessed in supply chains operating in South Asia?
+• Do seasonal workers have access to the same non-discrimination protections as permanent employees?
+• Is female representation tracked and targeted at farm management and cooperative leadership levels?</t>
+        </is>
+      </c>
+      <c r="T74" s="133" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.17 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="130" customHeight="1" s="42">
+      <c r="A75" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B75" s="122" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C75" s="122" t="inlineStr">
+        <is>
+          <t>Social Topics — Living Wage</t>
+        </is>
+      </c>
+      <c r="D75" s="123" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.18</t>
+        </is>
+      </c>
+      <c r="E75" s="122" t="inlineStr">
+        <is>
+          <t>Living Wage</t>
+        </is>
+      </c>
+      <c r="F75" s="122" t="inlineStr">
+        <is>
+          <t>Report on the organisation's approach to ensuring workers in agricultural operations and supply chains receive a living wage.</t>
+        </is>
+      </c>
+      <c r="G75" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H75" s="122" t="inlineStr">
+        <is>
+          <t>All agricultural, aquaculture, and fishing entities</t>
+        </is>
+      </c>
+      <c r="I75" s="122" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J75" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K75" s="122" t="inlineStr">
+        <is>
+          <t>Disclose: (a) whether the organisation has committed to paying a living wage; (b) the living wage benchmark used (Anker, WageIndicator, or local equivalent); (c) the percentage of direct and supply chain workers receiving a living wage; (d) the gap between current wages and the living wage benchmark; (e) actions taken or planned to close the living wage gap.</t>
+        </is>
+      </c>
+      <c r="L75" s="124" t="inlineStr">
+        <is>
+          <t>• Living wage policy or commitment document
+• Living wage benchmark data (Anker Research Institute or equivalent)
+• Wage data by location disaggregated by worker type and gender
+• Living wage gap analysis records
+• Supply chain wage survey data
+• Collective bargaining agreements with wage provisions
+• Wage improvement programme records
+• Smallholder income assessment data
+• Living income benchmark data for smallholder farmers
+• Year-on-year wage progression data by worker category</t>
+        </is>
+      </c>
+      <c r="M75" s="125" t="inlineStr">
+        <is>
+          <t>• Wage data verified by payroll system or third-party payroll audit
+• Benchmark living wage data from recognised institution
+• Living wage gap calculation methodology
+• Supply chain wage audit data
+• Third-party verification of living wage claims
+• Collective bargaining records confirming wage rates</t>
+        </is>
+      </c>
+      <c r="N75" s="126" t="inlineStr">
+        <is>
+          <t>• Percentage of direct workers earning living wage or above (%)
+• Percentage of supply chain workers (tier-1 farms/vessels) earning living wage (%)
+• Living wage gap (average actual wage / living wage benchmark × 100)
+• Smallholder farmer income vs. living income benchmark (%)
+• Year-on-year wage improvement rate (%)
+• Number of workers receiving below living wage
+• Investment in wage improvements ($)
+• Benchmark used and source organisation</t>
+        </is>
+      </c>
+      <c r="O75" s="127" t="inlineStr">
+        <is>
+          <t>Living wage attainment = Workers earning ≥ living wage / Total workers × 100. Living wage gap % = (Living wage − Actual wage) / Living wage × 100. Wage progression = (Current year median wage − Prior year) / Prior year × 100. Smallholder income gap = (Living income benchmark − Actual median household income) / Living income benchmark × 100.</t>
+        </is>
+      </c>
+      <c r="P75" s="122" t="inlineStr">
+        <is>
+          <t>HR / Supply Chain / Sustainability / Procurement / Finance</t>
+        </is>
+      </c>
+      <c r="Q75" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R75" s="128" t="inlineStr">
+        <is>
+          <t>• Living wage is distinct from minimum wage — must use recognised external benchmark
+• Anker Research Institute is the most widely accepted benchmark — state if different one used
+• Supply chain living wage is emerging as a priority — scope must be clearly defined
+• Smallholder living income is distinct from worker living wage — both required for agricultural reporters
+• Assurers will check whether living wage includes all employment-related costs (housing, transport)</t>
+        </is>
+      </c>
+      <c r="S75" s="129" t="inlineStr">
+        <is>
+          <t>• Which living wage benchmark is used, and is it independently calculated and verifiable?
+• What percentage of direct employees earn at or above the living wage benchmark?
+• Is there a target and timeline for achieving 100% living wage coverage in direct operations?
+• Does living wage assessment extend into the smallholder and contracted labour supply chain?</t>
+        </is>
+      </c>
+      <c r="T75" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.18 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="130" customHeight="1" s="42">
+      <c r="A76" s="133" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B76" s="133" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C76" s="133" t="inlineStr">
+        <is>
+          <t>Social Topics — OHS</t>
+        </is>
+      </c>
+      <c r="D76" s="134" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.19</t>
+        </is>
+      </c>
+      <c r="E76" s="133" t="inlineStr">
+        <is>
+          <t>Occupational Health and Safety</t>
+        </is>
+      </c>
+      <c r="F76" s="133" t="inlineStr">
+        <is>
+          <t>Report on occupational health and safety management and performance in agricultural, aquaculture, and fishing operations.</t>
+        </is>
+      </c>
+      <c r="G76" s="133" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H76" s="133" t="inlineStr">
+        <is>
+          <t>All agricultural, aquaculture, and fishing entities</t>
+        </is>
+      </c>
+      <c r="I76" s="133" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J76" s="133" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K76" s="133" t="inlineStr">
+        <is>
+          <t>Report using GRI 403 (Occupational Health and Safety). Sector-specific considerations include: (a) pesticide and agrochemical exposure risk; (b) heat stress in field operations; (c) fishing vessel safety at sea; (d) machinery and equipment hazards (harvesters, chainsaws, nets); (e) zoonotic disease risk in livestock operations; (f) musculoskeletal disorders from harvesting work.</t>
+        </is>
+      </c>
+      <c r="L76" s="124" t="inlineStr">
+        <is>
+          <t>• OHS management system documentation (ISO 45001 or equivalent)
+• Hazard identification and risk assessment records
+• Pesticide and agrochemical exposure monitoring records
+• Heat stress management plan and monitoring data
+• Fishing vessel safety inspection records and certificates
+• Personal protective equipment (PPE) provision records
+• OHS training records by job type and hazard
+• Incident register (injuries, near misses, fatalities)
+• Emergency response plan for vessel and field emergencies
+• Annual OHS performance review and management sign-off</t>
+        </is>
+      </c>
+      <c r="M76" s="125" t="inlineStr">
+        <is>
+          <t>• OHS incident investigation reports
+• TRIR and LTIFR calculation records with raw data
+• Pesticide exposure monitoring laboratory results
+• Fishing vessel safety certificate records
+• Regulatory inspection reports and compliance records
+• Third-party OHS audit reports
+• Workers' compensation records</t>
+        </is>
+      </c>
+      <c r="N76" s="126" t="inlineStr">
+        <is>
+          <t>• Total recordable incident rate (TRIR)
+• Lost-time injury frequency rate (LTIFR)
+• Number of work-related fatalities
+• Number of pesticide exposure incidents
+• Heat stress illness incidents (count)
+• Fishing vessel accident rate (incidents per vessel per year)
+• OHS training completion rate (%)
+• Number of workers with job-related musculoskeletal conditions
+• Near-miss reporting rate (leading indicator)</t>
+        </is>
+      </c>
+      <c r="O76" s="127" t="inlineStr">
+        <is>
+          <t>TRIR = Recordable incidents × 200,000 / Hours worked. LTIFR = Lost-time injuries × 1,000,000 / Hours worked. Fatality rate = Fatalities / Average employees × 100,000. Pesticide incident rate = Pesticide incidents / Total workers × 1,000. Near-miss rate = Near misses / Hours worked × 1,000,000.</t>
+        </is>
+      </c>
+      <c r="P76" s="133" t="inlineStr">
+        <is>
+          <t>HSE / Operations / HR / Sustainability / Agricultural Management</t>
+        </is>
+      </c>
+      <c r="Q76" s="133" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R76" s="128" t="inlineStr">
+        <is>
+          <t>• Pesticide exposure is a sector-critical OHS hazard — biological monitoring required for applicators
+• Fishing vessels require vessel-specific OHS management including SOLAS compliance
+• Heat stress is an emerging material risk — wet bulb globe temperature monitoring is best practice
+• Zoonotic disease risk (avian flu, brucellosis) requires specific protocols for livestock workers
+• OHS data must cover contract and seasonal workers, not just permanent employees</t>
+        </is>
+      </c>
+      <c r="S76" s="129" t="inlineStr">
+        <is>
+          <t>• Are sector-specific OHS hazards (pesticides, heat, vessels) addressed with dedicated controls?
+• Does OHS data cover seasonal and contract workers who make up a high proportion of the workforce?
+• Is pesticide exposure monitored biologically (blood tests for cholinesterase inhibition) for applicators?
+• Are fishing vessel OHS incidents reported separately from land-based operations?</t>
+        </is>
+      </c>
+      <c r="T76" s="133" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.19 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="130" customHeight="1" s="42">
+      <c r="A77" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B77" s="122" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C77" s="122" t="inlineStr">
+        <is>
+          <t>Governance Topics — Anti-corruption</t>
+        </is>
+      </c>
+      <c r="D77" s="123" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.20</t>
+        </is>
+      </c>
+      <c r="E77" s="122" t="inlineStr">
+        <is>
+          <t>Anti-corruption</t>
+        </is>
+      </c>
+      <c r="F77" s="122" t="inlineStr">
+        <is>
+          <t>Report on anti-corruption policies, risk assessments, training, and incidents in agricultural and food sector operations.</t>
+        </is>
+      </c>
+      <c r="G77" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H77" s="122" t="inlineStr">
+        <is>
+          <t>All agricultural, aquaculture, and fishing entities</t>
+        </is>
+      </c>
+      <c r="I77" s="122" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J77" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K77" s="122" t="inlineStr">
+        <is>
+          <t>Report using GRI 205 (Anti-corruption). Sector-specific considerations include: (a) corruption risk in government permitting, export licences, and customs processes for agricultural commodities; (b) land acquisition corruption risk; (c) bribery in commodity inspection and certification processes; (d) anti-corruption in smallholder supply chain procurement.</t>
+        </is>
+      </c>
+      <c r="L77" s="124" t="inlineStr">
+        <is>
+          <t>• Anti-corruption policy and code of conduct
+• Corruption risk assessment register
+• Anti-corruption training records by role and location
+• Whistleblower hotline and case management records
+• Gift and hospitality register
+• Government interaction log
+• Third-party due diligence records (agents, brokers, inspectors)
+• Anti-corruption clauses in supplier contracts
+• Investigation records for corruption incidents
+• Regulatory compliance records (FCPA, UK Bribery Act, equivalent)</t>
+        </is>
+      </c>
+      <c r="M77" s="125" t="inlineStr">
+        <is>
+          <t>• Anti-corruption risk assessment (signed off by Legal/Compliance)
+• Training completion records by employee category
+• Whistleblower case records and outcomes
+• Investigation records for confirmed incidents
+• Third-party due diligence reports
+• Regulatory correspondence relating to corruption investigations
+• External audit of anti-corruption controls</t>
+        </is>
+      </c>
+      <c r="N77" s="126" t="inlineStr">
+        <is>
+          <t>• Number of operations assessed for corruption risk
+• Percentage of employees trained on anti-corruption (%)
+• Number of corruption incidents confirmed
+• Number of government officials interactions logged
+• Contracts with anti-corruption clauses (% of total)
+• Number of whistleblower reports relating to corruption
+• Financial losses or fines from corruption incidents ($)
+• Number of third parties (agents) with due diligence completed</t>
+        </is>
+      </c>
+      <c r="O77" s="127" t="inlineStr">
+        <is>
+          <t>Training coverage = Employees trained on anti-corruption / Total employees × 100. Incident rate = Confirmed corruption incidents / Total employees × 1,000. Third-party due diligence coverage = Agents/brokers with completed due diligence / Total third parties × 100. Sanctions screening coverage = Counterparties screened / Total new counterparties × 100.</t>
+        </is>
+      </c>
+      <c r="P77" s="122" t="inlineStr">
+        <is>
+          <t>Legal / Compliance / Sustainability / Finance / Procurement</t>
+        </is>
+      </c>
+      <c r="Q77" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R77" s="128" t="inlineStr">
+        <is>
+          <t>• Land acquisition corruption is a priority risk for agricultural operators in emerging markets
+• Commodity inspection and certification bribery is a sector-specific risk to disclose
+• Government interaction logs are a best practice for high-risk jurisdictions
+• Smallholder procurement intermediaries require specific due diligence
+• Assurers will cross-check training completion against actual role-based risk profiles</t>
+        </is>
+      </c>
+      <c r="S77" s="129" t="inlineStr">
+        <is>
+          <t>• Are government interactions logged in high-risk jurisdictions for agricultural permits and licences?
+• Are land acquisition processes subject to enhanced anti-corruption due diligence?
+• Do commodity inspection and certification agents receive anti-corruption due diligence?
+• Is anti-corruption training risk-stratified by role and geography?</t>
+        </is>
+      </c>
+      <c r="T77" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.20 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="130" customHeight="1" s="42">
+      <c r="A78" s="133" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B78" s="133" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C78" s="133" t="inlineStr">
+        <is>
+          <t>Governance Topics — Payments to Governments</t>
+        </is>
+      </c>
+      <c r="D78" s="134" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.21</t>
+        </is>
+      </c>
+      <c r="E78" s="133" t="inlineStr">
+        <is>
+          <t>Payments to Governments</t>
+        </is>
+      </c>
+      <c r="F78" s="133" t="inlineStr">
+        <is>
+          <t>Report on taxes, royalties, licence fees, and other payments made to governments in jurisdictions where the organisation operates.</t>
+        </is>
+      </c>
+      <c r="G78" s="133" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H78" s="133" t="inlineStr">
+        <is>
+          <t>Agricultural, aquaculture, and fishing entities with significant government payments</t>
+        </is>
+      </c>
+      <c r="I78" s="133" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J78" s="133" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K78" s="133" t="inlineStr">
+        <is>
+          <t>Report using GRI 207 (Tax) and GRI 201 (Economic Performance) as applicable. Sector-specific considerations include: (a) fishing licence fees and quota payments; (b) land lease payments to governments; (c) agricultural export levies and duties; (d) water use fees and irrigation charges; (e) royalties on aquaculture and fishing rights.</t>
+        </is>
+      </c>
+      <c r="L78" s="124" t="inlineStr">
+        <is>
+          <t>• Tax compliance records and returns by jurisdiction
+• Fishing licence and quota payment records
+• Land lease and concession payment records
+• Agricultural export duty and levy payment records
+• Water use and irrigation fee records
+• Royalty payment documentation
+• Country-by-country reporting (CbCR) where applicable
+• Transfer pricing documentation
+• Tax risk register and governance framework</t>
+        </is>
+      </c>
+      <c r="M78" s="125" t="inlineStr">
+        <is>
+          <t>• Audited financial statements (tax lines)
+• Tax authority correspondence and assessment records
+• Fishing licence certificates and payment receipts
+• Land lease agreements and payment records
+• Country-by-country report (if applicable)
+• External tax advisor sign-off on reporting
+• Government payment reconciliation records</t>
+        </is>
+      </c>
+      <c r="N78" s="126" t="inlineStr">
+        <is>
+          <t>• Total taxes paid by jurisdiction ($)
+• Total fishing licence and quota fees paid ($)
+• Land lease payments to governments ($)
+• Export duties and agricultural levies paid ($)
+• Water use fees paid ($)
+• Total government payments by country (country-by-country)
+• Effective tax rate (%) vs. statutory rate
+• Number of jurisdictions with government payments</t>
+        </is>
+      </c>
+      <c r="O78" s="127" t="inlineStr">
+        <is>
+          <t>Effective tax rate = Tax paid / Pre-tax profit × 100. Government payments total = Sum of all taxes, fees, royalties, levies, and licence payments by jurisdiction. Tax gap = Statutory rate − Effective tax rate. Report each payment category separately by country.</t>
+        </is>
+      </c>
+      <c r="P78" s="133" t="inlineStr">
+        <is>
+          <t>Finance / Tax / Legal / Operations / Sustainability</t>
+        </is>
+      </c>
+      <c r="Q78" s="133" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R78" s="128" t="inlineStr">
+        <is>
+          <t>• Fishing licence and quota payments are sector-specific and must be separately disclosed
+• Land concession payments in developing countries are a social and governance materiality issue
+• CbCR is increasingly mandatory — sector entities must assess whether threshold is met
+• Transfer pricing in agricultural commodity trading is an active regulatory scrutiny area
+• Government payments transparency is important for social licence in developing country operations</t>
+        </is>
+      </c>
+      <c r="S78" s="129" t="inlineStr">
+        <is>
+          <t>• Are fishing licence and quota payments disclosed at country level?
+• Is country-by-country reporting applicable and is the organisation prepared to comply?
+• Are land lease payments to governments disclosed separately from commercial leases?
+• Is the effective tax rate consistent with the statutory rate, and if not, is the difference explained?</t>
+        </is>
+      </c>
+      <c r="T78" s="133" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.21 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="130" customHeight="1" s="42">
+      <c r="A79" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B79" s="122" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C79" s="122" t="inlineStr">
+        <is>
+          <t>Economic Topics — Economic Impacts</t>
+        </is>
+      </c>
+      <c r="D79" s="123" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.22</t>
+        </is>
+      </c>
+      <c r="E79" s="122" t="inlineStr">
+        <is>
+          <t>Economic Impacts</t>
+        </is>
+      </c>
+      <c r="F79" s="122" t="inlineStr">
+        <is>
+          <t>Report on the organisation's direct and indirect economic contributions to rural communities, smallholder farmers, and food system value chains.</t>
+        </is>
+      </c>
+      <c r="G79" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H79" s="122" t="inlineStr">
+        <is>
+          <t>All agricultural, aquaculture, and fishing entities with significant local economic footprint</t>
+        </is>
+      </c>
+      <c r="I79" s="122" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J79" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K79" s="122" t="inlineStr">
+        <is>
+          <t>Report using GRI 203 (Indirect Economic Impacts) and GRI 201 (Economic Performance). Sector-specific considerations include: (a) economic contribution to smallholder farmer incomes and rural livelihoods; (b) local procurement from small and medium enterprises; (c) multiplier effects of agricultural operations on rural economies; (d) economic impacts of transition (mechanisation, supply chain consolidation) on rural employment.</t>
+        </is>
+      </c>
+      <c r="L79" s="124" t="inlineStr">
+        <is>
+          <t>• Economic impact assessment or study documentation
+• Smallholder farmer income data
+• Local procurement records and analysis
+• Rural employment data by community
+• Value chain economic mapping
+• Community development investment records
+• Wages and benefits data (total compensation paid)
+• Taxes, fees, and other fiscal contributions by jurisdiction
+• Agricultural extension and technical support programme records
+• Market access programme documentation for smallholder farmers</t>
+        </is>
+      </c>
+      <c r="M79" s="125" t="inlineStr">
+        <is>
+          <t>• Economic impact study (independent or internally validated)
+• Local procurement data from finance system
+• Smallholder price data and income calculations
+• Government economic contribution data (employment, tax)
+• Community development programme evaluation reports
+• Agricultural extension programme outcome data</t>
+        </is>
+      </c>
+      <c r="N79" s="126" t="inlineStr">
+        <is>
+          <t>• Total direct economic value generated ($)
+• Total economic value distributed (wages, taxes, dividends, reinvestment)
+• Local procurement spend ($ and % of total)
+• Number of smallholder farmers in supply chain
+• Average smallholder farmer income supported by relationship ($)
+• Rural employment created (direct and indirect)
+• Economic multiplier effect estimate (if assessed)
+• Community development investment ($)</t>
+        </is>
+      </c>
+      <c r="O79" s="127" t="inlineStr">
+        <is>
+          <t>Economic value retained = Revenue − All economic distributions. Local procurement % = Local supplier spend / Total procurement × 100. Smallholder income contribution = Average price paid to farmers × volume / Number of farmer households. Multiplier effect is assessed using input-output modelling or sector-specific multiplier data.</t>
+        </is>
+      </c>
+      <c r="P79" s="122" t="inlineStr">
+        <is>
+          <t>Finance / Sustainability / Procurement / Community Affairs / Agricultural Operations</t>
+        </is>
+      </c>
+      <c r="Q79" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R79" s="128" t="inlineStr">
+        <is>
+          <t>• Smallholder farmer income impact is the most sector-specific and auditor-scrutinised metric
+• Local procurement must define 'local' consistently and verify with sourcing data
+• Economic multiplier estimates must state methodology and assumptions clearly
+• Agricultural mechanisation impact on local employment must be disclosed proactively
+• Just transition economic planning should be linked to this disclosure</t>
+        </is>
+      </c>
+      <c r="S79" s="129" t="inlineStr">
+        <is>
+          <t>• Is smallholder farmer income tracked and disclosed as a measure of economic impact?
+• Does the local procurement definition include clear geographic scope and methodology?
+• Are economic multiplier estimates supported by recognised economic modelling?
+• Is the impact of mechanisation on rural employment assessed and disclosed?</t>
+        </is>
+      </c>
+      <c r="T79" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.22 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="130" customHeight="1" s="42">
+      <c r="A80" s="133" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B80" s="133" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C80" s="133" t="inlineStr">
+        <is>
+          <t>Governance Topics — Tax</t>
+        </is>
+      </c>
+      <c r="D80" s="134" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.23</t>
+        </is>
+      </c>
+      <c r="E80" s="133" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="F80" s="133" t="inlineStr">
+        <is>
+          <t>Report on the organisation's approach to tax governance, country-by-country tax contributions, and responsible tax practices in agricultural and food sector operations.</t>
+        </is>
+      </c>
+      <c r="G80" s="133" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H80" s="133" t="inlineStr">
+        <is>
+          <t>All agricultural, aquaculture, and fishing entities with complex tax structures</t>
+        </is>
+      </c>
+      <c r="I80" s="133" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J80" s="133" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K80" s="133" t="inlineStr">
+        <is>
+          <t>Report using GRI 207 (Tax). Sector-specific considerations include: (a) transfer pricing in agricultural commodity trading entities; (b) tax structures in developing country operations; (c) commodity trader presence in low-tax jurisdictions; (d) agricultural subsidies and tax credits; (e) CbCR requirements for agricultural multinationals.</t>
+        </is>
+      </c>
+      <c r="L80" s="124" t="inlineStr">
+        <is>
+          <t>• Tax governance framework and policy
+• Country-by-country report (CbCR) or summary
+• Transfer pricing documentation and policy
+• Tax risk register
+• Subsidy and agricultural tax credit records
+• Tax authority relationship management records
+• Board or audit committee oversight of tax records
+• Total taxes paid by jurisdiction
+• Uncertain tax position register
+• External tax advisor relationship records</t>
+        </is>
+      </c>
+      <c r="M80" s="125" t="inlineStr">
+        <is>
+          <t>• CbCR (published or regulator-submitted copy)
+• Tax return summaries by jurisdiction
+• Transfer pricing documentation
+• Audit committee sign-off on tax disclosures
+• External tax advisor confirmation of tax compliance
+• Uncertain tax position assessment
+• Tax reconciliation (statutory vs. effective rate)</t>
+        </is>
+      </c>
+      <c r="N80" s="126" t="inlineStr">
+        <is>
+          <t>• Total taxes paid by jurisdiction ($)
+• Effective tax rate (%) by jurisdiction
+• Number of jurisdictions with low or zero tax rate presence
+• Agricultural subsidies and tax credits received ($)
+• Uncertain tax positions value ($)
+• Transfer pricing adjustments made ($)
+• Tax disputes with authorities (count and value)
+• CbCR publication status (yes/no, scope)</t>
+        </is>
+      </c>
+      <c r="O80" s="127" t="inlineStr">
+        <is>
+          <t>Effective tax rate = Total income tax paid / Pre-tax profit × 100. Tax gap = (Statutory rate − Effective rate) × Pre-tax profit. Subsidy intensity = Subsidies received / Revenue × 100. CbCR disclosure should break out profit, tax, employees, and turnover by jurisdiction.</t>
+        </is>
+      </c>
+      <c r="P80" s="133" t="inlineStr">
+        <is>
+          <t>Finance / Tax / Legal / Sustainability / Group Finance</t>
+        </is>
+      </c>
+      <c r="Q80" s="133" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R80" s="128" t="inlineStr">
+        <is>
+          <t>• Agricultural commodity traders are scrutinised for use of low-tax trading hubs
+• Developing country tax contributions are a significant social impact metric
+• Agricultural subsidies received from governments must be disclosed as economic contributions
+• Uncertain tax positions require quantification and disclosure of contingent liability
+• Assurers will cross-reference effective tax rate against peer benchmarks</t>
+        </is>
+      </c>
+      <c r="S80" s="129" t="inlineStr">
+        <is>
+          <t>• Does the organisation publish or prepare a country-by-country tax report?
+• Is there a documented tax governance framework approved by the board?
+• Are agricultural subsidies and tax credits received disclosed by jurisdiction?
+• Is the effective tax rate significantly below the statutory rate, and if so, is the difference explained?</t>
+        </is>
+      </c>
+      <c r="T80" s="133" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.23 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="130" customHeight="1" s="42">
+      <c r="A81" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B81" s="122" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C81" s="122" t="inlineStr">
+        <is>
+          <t>Social Topics — Conflict and Security</t>
+        </is>
+      </c>
+      <c r="D81" s="123" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.24</t>
+        </is>
+      </c>
+      <c r="E81" s="122" t="inlineStr">
+        <is>
+          <t>Conflict and Security</t>
+        </is>
+      </c>
+      <c r="F81" s="122" t="inlineStr">
+        <is>
+          <t>Report on security practices and human rights in agricultural operations in conflict-affected or high-risk areas.</t>
+        </is>
+      </c>
+      <c r="G81" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H81" s="122" t="inlineStr">
+        <is>
+          <t>Agricultural entities operating in conflict-affected or high-risk areas</t>
+        </is>
+      </c>
+      <c r="I81" s="122" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J81" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K81" s="122" t="inlineStr">
+        <is>
+          <t>Report using GRI 410 (Security Practices). Sector-specific considerations include: (a) land-related conflict and use of security forces in land acquisition; (b) conflict over water and natural resource access; (c) violence against environmental and land rights defenders in agricultural supply chains; (d) Voluntary Principles on Security and Human Rights (VPSHR) in CAHRA operations.</t>
+        </is>
+      </c>
+      <c r="L81" s="124" t="inlineStr">
+        <is>
+          <t>• Security risk assessment and management plan
+• Security provider contracts and VPSHR compliance terms
+• Security incident register
+• Human rights training records for security personnel
+• Land dispute register and resolution records
+• Violence against land defenders case log
+• Country risk assessments for CAHRA agricultural operations
+• OECD due diligence records
+• Community grievance records related to land and security
+• Freedom from Violence policy documentation</t>
+        </is>
+      </c>
+      <c r="M81" s="125" t="inlineStr">
+        <is>
+          <t>• Security incident investigation records
+• VPSHR implementation assessment
+• Human rights training completion records for security
+• Land dispute resolution records
+• Government security force memoranda of understanding
+• Legal records for security-related human rights cases
+• Independent security risk assessment reports</t>
+        </is>
+      </c>
+      <c r="N81" s="126" t="inlineStr">
+        <is>
+          <t>• Number of security incidents involving injury or use of force
+• Security personnel human rights training rate (%)
+• Number of active land disputes related to security
+• Number of complaints regarding security conduct
+• Operations in conflict-affected or high-risk areas (count)
+• VPSHR adherence status and implementation stage
+• Violence against land defenders incidents (count) — documented and assessed</t>
+        </is>
+      </c>
+      <c r="O81" s="127" t="inlineStr">
+        <is>
+          <t>Incident rate = Security incidents / Total security personnel × 100. Training coverage = Security personnel trained / Total security personnel × 100. Land dispute resolution rate = Disputes resolved / Total land disputes × 100.</t>
+        </is>
+      </c>
+      <c r="P81" s="122" t="inlineStr">
+        <is>
+          <t>Security / Legal / Human Rights / Operations / Sustainability</t>
+        </is>
+      </c>
+      <c r="Q81" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R81" s="128" t="inlineStr">
+        <is>
+          <t>• Violence against land defenders is a priority disclosure for agricultural operators in high-risk regions
+• VPSHR commitment must be formal and implementation must be evidenced
+• Land acquisition disputes require dedicated monitoring and resolution procedures
+• Use of public security forces requires the same human rights standards as private forces
+• Assurers will cross-reference with civil society and NGO reports on the ground</t>
+        </is>
+      </c>
+      <c r="S81" s="129" t="inlineStr">
+        <is>
+          <t>• Are there documented cases of violence against land rights defenders linked to operations?
+• Has the organisation formally committed to the Voluntary Principles on Security and Human Rights?
+• Are land acquisition and land rights disputes systematically tracked and resolved?
+• Do contracts with private security providers include VPSHR compliance requirements?</t>
+        </is>
+      </c>
+      <c r="T81" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.24 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="130" customHeight="1" s="42">
+      <c r="A82" s="133" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B82" s="133" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C82" s="133" t="inlineStr">
+        <is>
+          <t>Social Topics — Indigenous Peoples</t>
+        </is>
+      </c>
+      <c r="D82" s="134" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.25</t>
+        </is>
+      </c>
+      <c r="E82" s="133" t="inlineStr">
+        <is>
+          <t>Rights of Indigenous Peoples</t>
+        </is>
+      </c>
+      <c r="F82" s="133" t="inlineStr">
+        <is>
+          <t>Report on respect for indigenous peoples' rights in relation to agricultural land use, fishing rights, and traditional resource access.</t>
+        </is>
+      </c>
+      <c r="G82" s="133" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H82" s="133" t="inlineStr">
+        <is>
+          <t>Agricultural, aquaculture, and fishing entities operating in or near indigenous territories</t>
+        </is>
+      </c>
+      <c r="I82" s="133" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J82" s="133" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K82" s="133" t="inlineStr">
+        <is>
+          <t>Report using GRI 411 (Rights of Indigenous Peoples). Sector-specific considerations include: (a) FPIC processes for agricultural land use affecting indigenous territories; (b) traditional fishing rights and customary resource access; (c) cultural heritage and sacred site protection in farming operations; (d) indigenous farmers and fisherfolk in supply chains; (e) benefit-sharing and equitable access for indigenous communities.</t>
+        </is>
+      </c>
+      <c r="L82" s="124" t="inlineStr">
+        <is>
+          <t>• Indigenous peoples identification and territory mapping
+• FPIC process documentation and consent records
+• Traditional fishing rights assessment records
+• Cultural heritage and sacred site register
+• Benefit-sharing agreement documentation
+• Indigenous community engagement programme records
+• ILO Convention 169 compliance assessment
+• UN Declaration on the Rights of Indigenous Peoples (UNDRIP) alignment assessment
+• Legal records for land and resource rights
+• Indigenous supplier and farmer inclusion programme</t>
+        </is>
+      </c>
+      <c r="M82" s="125" t="inlineStr">
+        <is>
+          <t>• FPIC consent records for affected territories
+• Cultural heritage survey reports
+• Benefit-sharing agreement copies
+• ILO 169 compliance records by country
+• Legal correspondence on land and fishing rights
+• Independent FPIC compliance assessment reports
+• Indigenous community satisfaction records</t>
+        </is>
+      </c>
+      <c r="N82" s="126" t="inlineStr">
+        <is>
+          <t>• Number of indigenous communities identified in areas of operation
+• FPIC processes completed (count and outcomes)
+• Cultural heritage and sacred sites identified and protected
+• Value of benefit-sharing agreements ($)
+• Indigenous farmers/fisherfolk in supply chain (count)
+• Legal actions regarding indigenous rights (count and outcomes)
+• Traditional fishing rights impacts assessed and managed (count)</t>
+        </is>
+      </c>
+      <c r="O82" s="127" t="inlineStr">
+        <is>
+          <t>FPIC compliance rate = Projects with FPIC / Total projects affecting indigenous territories × 100. Indigenous supplier inclusion = Indigenous farmers in supply chain / Total farmers × 100. Cultural heritage protection = Sites with protection protocols / Total identified sites × 100.</t>
+        </is>
+      </c>
+      <c r="P82" s="133" t="inlineStr">
+        <is>
+          <t>Community Affairs / Legal / Human Rights / Supply Chain / Sustainability</t>
+        </is>
+      </c>
+      <c r="Q82" s="133" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R82" s="128" t="inlineStr">
+        <is>
+          <t>• FPIC is mandatory under ILO 169 in signatory countries and emerging best practice globally
+• Traditional fishing rights are increasingly legally protected — engagement required pre-development
+• Benefit-sharing agreements must be legally binding and monitored for compliance
+• UNDRIP alignment is increasingly expected by investors and institutional buyers
+• Cultural heritage destruction is an irreversible impact — assurers treat this as a red line</t>
+        </is>
+      </c>
+      <c r="S82" s="129" t="inlineStr">
+        <is>
+          <t>• Are FPIC processes in place for all activities affecting indigenous territories?
+• Are traditional fishing and resource rights assessed before new aquaculture or agricultural developments?
+• Are benefit-sharing arrangements in place and independently monitored?
+• Is the organisation actively including indigenous farmers and fisherfolk in supply chains?</t>
+        </is>
+      </c>
+      <c r="T82" s="133" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.25 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="130" customHeight="1" s="42">
+      <c r="A83" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B83" s="122" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C83" s="122" t="inlineStr">
+        <is>
+          <t>Social Topics — Smallholder Welfare</t>
+        </is>
+      </c>
+      <c r="D83" s="123" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.26</t>
+        </is>
+      </c>
+      <c r="E83" s="122" t="inlineStr">
+        <is>
+          <t>Smallholder and Farmer Welfare — Living Income</t>
+        </is>
+      </c>
+      <c r="F83" s="122" t="inlineStr">
+        <is>
+          <t>Report on the organisation's approach to supporting smallholder farmers and fishing communities to achieve a living income.</t>
+        </is>
+      </c>
+      <c r="G83" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H83" s="122" t="inlineStr">
+        <is>
+          <t>All agricultural and fishing entities sourcing from smallholder farmers or small-scale fishers</t>
+        </is>
+      </c>
+      <c r="I83" s="122" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J83" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K83" s="122" t="inlineStr">
+        <is>
+          <t>Report: (a) the organisation's approach to smallholder farmer welfare and living income; (b) the benchmark used for living income assessment; (c) the gap between actual farmer income and the living income benchmark; (d) actions taken to close the living income gap (price premiums, productivity support, direct payments); (e) number of farmers supported and outcomes achieved.</t>
+        </is>
+      </c>
+      <c r="L83" s="124" t="inlineStr">
+        <is>
+          <t>• Smallholder farmer income assessment methodology and data
+• Living income benchmark documentation (IDH, Fairtrade, sector-specific)
+• Smallholder price premium records
+• Agricultural extension and technical support programme records
+• Farmer training and productivity improvement records
+• Long-term supply agreement documentation
+• Farmer income monitoring data year-on-year
+• Fairtrade, Rainforest Alliance, or UTZ income premium records
+• Living income roadmap or strategy document
+• Farmer segmentation and vulnerability data</t>
+        </is>
+      </c>
+      <c r="M83" s="125" t="inlineStr">
+        <is>
+          <t>• Farmer income survey results with methodology
+• Living income benchmark comparison calculations
+• Price premium payment records
+• Agricultural extension programme evaluation reports
+• Long-term supply agreement signed copies
+• Third-party verification of living income progress claims
+• Certification body reports on income outcomes</t>
+        </is>
+      </c>
+      <c r="N83" s="126" t="inlineStr">
+        <is>
+          <t>• Number of smallholder farmers in supply chain
+• Percentage of farmers assessed for living income (%)
+• Average farmer household income ($)
+• Living income benchmark for key sourcing regions ($)
+• Living income gap (% of benchmark achieved)
+• Price premium paid above market price ($ per unit)
+• Number of farmers receiving technical or productivity support
+• Year-on-year change in average farmer income (%)</t>
+        </is>
+      </c>
+      <c r="O83" s="127" t="inlineStr">
+        <is>
+          <t>Living income attainment = Households at or above benchmark / Total households assessed × 100. Income gap = (Living income benchmark − Actual income) / Living income benchmark × 100. Premium effectiveness = Price premium per unit × Volume × Number of farmers. Income trend = (Current year income − Prior year income) / Prior year income × 100.</t>
+        </is>
+      </c>
+      <c r="P83" s="122" t="inlineStr">
+        <is>
+          <t>Supply Chain / Agricultural Operations / Sustainability / Procurement / Finance</t>
+        </is>
+      </c>
+      <c r="Q83" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R83" s="128" t="inlineStr">
+        <is>
+          <t>• Living income for smallholders is distinct from living wage for workers — both may be needed
+• IDH Sustainable Trade Initiative benchmark and Fairtrade Living Income data are reference sources
+• Income gap disclosure requires a named, credible benchmark to be meaningful
+• Price premiums alone are insufficient — productivity and yield improvements are also needed
+• Assurers will scrutinise the robustness of farmer income survey methodology</t>
+        </is>
+      </c>
+      <c r="S83" s="129" t="inlineStr">
+        <is>
+          <t>• Is a recognised external benchmark used for living income assessment (IDH, Fairtrade, sector body)?
+• What is the current living income gap, and is there a time-bound plan to close it?
+• Does the approach address structural factors (yield, market access, productivity) not just price premiums?
+• Is farmer income data collected through independent surveys or directly from farmers?</t>
+        </is>
+      </c>
+      <c r="T83" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.26 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="130" customHeight="1" s="42">
+      <c r="A84" s="133" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B84" s="133" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C84" s="133" t="inlineStr">
+        <is>
+          <t>Environmental Topics — Pesticides</t>
+        </is>
+      </c>
+      <c r="D84" s="134" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.27</t>
+        </is>
+      </c>
+      <c r="E84" s="133" t="inlineStr">
+        <is>
+          <t>Pesticides</t>
+        </is>
+      </c>
+      <c r="F84" s="133" t="inlineStr">
+        <is>
+          <t>Report on the organisation's use, management, and reduction of pesticides, including hazardous chemical management in agricultural operations.</t>
+        </is>
+      </c>
+      <c r="G84" s="133" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H84" s="133" t="inlineStr">
+        <is>
+          <t>All agricultural entities using pesticides in operations or supply chains</t>
+        </is>
+      </c>
+      <c r="I84" s="133" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J84" s="133" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K84" s="133" t="inlineStr">
+        <is>
+          <t>Disclose: (a) total volume of pesticides used by hazard classification; (b) approach to integrated pest management (IPM) and pesticide reduction; (c) use of WHO Class I (highly hazardous) pesticides and phase-out plans; (d) pesticide drift and water contamination management; (e) farmer training on safe pesticide handling; (f) Fairtrade, SAS, and industry banned substance lists.</t>
+        </is>
+      </c>
+      <c r="L84" s="124" t="inlineStr">
+        <is>
+          <t>• Pesticide use register by type, volume, and active ingredient
+• WHO and FAO hazard classification records per pesticide
+• Integrated Pest Management (IPM) programme documentation
+• Highly hazardous pesticide (HHP) phase-out plan
+• Pesticide application training records by job role
+• PPE provision and inspection records for pesticide applicators
+• Water quality monitoring records near agricultural operations
+• Pesticide residue testing records (product and environmental)
+• Banned substance list compliance records (SAS, Fairtrade, buyer codes)
+• Biological monitoring records for pesticide applicators</t>
+        </is>
+      </c>
+      <c r="M84" s="125" t="inlineStr">
+        <is>
+          <t>• Pesticide use data from procurement or application records
+• IPM audit reports showing pest management approach
+• Biological monitoring results for applicators (cholinesterase tests)
+• Water quality monitoring data for pesticide residues
+• Banned substance compliance audit records
+• Certification body reports (Rainforest Alliance, LEAF) on pesticide standards
+• Supplier pesticide compliance audit results</t>
+        </is>
+      </c>
+      <c r="N84" s="126" t="inlineStr">
+        <is>
+          <t>• Total pesticide volume used (kg active ingredient)
+• Pesticides by WHO hazard class (% volume in Class I, II, III, U)
+• Number of highly hazardous pesticides used — and phased out vs. plan
+• Pesticide use intensity (kg active ingredient / ha)
+• IPM adoption rate (% of operations/farms using IPM)
+• Biological monitoring coverage for pesticide applicators (%)
+• Water quality exceedances related to pesticides (count)
+• Year-on-year pesticide use reduction (%)</t>
+        </is>
+      </c>
+      <c r="O84" s="127" t="inlineStr">
+        <is>
+          <t>Pesticide intensity = Total active ingredient kg / Total cultivated area ha. HHP phase-out rate = HHPs phased out / Total HHPs identified × 100. IPM adoption = Farms using IPM / Total farms × 100. Pesticide reduction = (Prior year volume − Current year volume) / Prior year volume × 100. Water exceedance rate = Exceedances / Total monitoring events × 100.</t>
+        </is>
+      </c>
+      <c r="P84" s="133" t="inlineStr">
+        <is>
+          <t>Agricultural Operations / HSE / Sustainability / Supply Chain / ESG</t>
+        </is>
+      </c>
+      <c r="Q84" s="133" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R84" s="128" t="inlineStr">
+        <is>
+          <t>• WHO Class I (Ia and Ib) pesticide use is an absolute red line for many buyers and certifiers
+• HHP phase-out must have a named timeline and active substitution programme
+• Biological monitoring of applicators is a legal requirement in many jurisdictions — verify scope
+• Pesticide drift to water bodies is a regulatory compliance risk — water monitoring data required
+• IPM is the global best practice standard — adoption rate is a leading indicator of performance</t>
+        </is>
+      </c>
+      <c r="S84" s="129" t="inlineStr">
+        <is>
+          <t>• Is the use of highly hazardous pesticides (WHO Class I) reported with a phase-out timeline?
+• Are pesticide applicators subject to biological monitoring for exposure?
+• Is integrated pest management adopted and tracked across all farming operations and supplier farms?
+• Are water quality exceedances related to pesticide use monitored and disclosed?</t>
+        </is>
+      </c>
+      <c r="T84" s="133" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.27 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="130" customHeight="1" s="42">
+      <c r="A85" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022</t>
+        </is>
+      </c>
+      <c r="B85" s="122" t="inlineStr">
+        <is>
+          <t>Sector Standard</t>
+        </is>
+      </c>
+      <c r="C85" s="122" t="inlineStr">
+        <is>
+          <t>Environmental Topics — Responsible Aquaculture/Fishing</t>
+        </is>
+      </c>
+      <c r="D85" s="123" t="inlineStr">
+        <is>
+          <t>GRI 13 — Topic 13.28</t>
+        </is>
+      </c>
+      <c r="E85" s="122" t="inlineStr">
+        <is>
+          <t>Responsible Aquaculture and Fishing Practices</t>
+        </is>
+      </c>
+      <c r="F85" s="122" t="inlineStr">
+        <is>
+          <t>Report on sustainable and responsible practices in aquaculture and wild-catch fishing operations to prevent overfishing, habitat damage, and ecosystem impacts.</t>
+        </is>
+      </c>
+      <c r="G85" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (sector likely material)</t>
+        </is>
+      </c>
+      <c r="H85" s="122" t="inlineStr">
+        <is>
+          <t>Aquaculture and fishing entities</t>
+        </is>
+      </c>
+      <c r="I85" s="122" t="inlineStr">
+        <is>
+          <t>Likely material per GRI 13</t>
+        </is>
+      </c>
+      <c r="J85" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K85" s="122" t="inlineStr">
+        <is>
+          <t>Disclose: (a) fishing methods and certification status (MSC, ASC, or equivalent); (b) stock status for key target species relative to Maximum Sustainable Yield (MSY); (c) bycatch reduction measures and discard rates; (d) aquaculture feed source sustainability (fishmeal, fish oil, soy); (e) antimicrobial use in aquaculture; (f) disease management and sea lice control; (g) escapes of farmed fish into the wild.</t>
+        </is>
+      </c>
+      <c r="L85" s="124" t="inlineStr">
+        <is>
+          <t>• Fishing method and gear type register
+• MSC or ASC certification documents
+• Stock assessment reports for key target species
+• Bycatch monitoring and discard records
+• Aquaculture feed ingredient sourcing records (fishmeal, fish oil traceability)
+• Antimicrobial use register with veterinary prescriptions
+• Sea lice treatment records and lice level monitoring data
+• Escape incident records
+• Aquaculture site environmental impact assessments
+• Observer programme records (on-vessel catch monitoring)</t>
+        </is>
+      </c>
+      <c r="M85" s="125" t="inlineStr">
+        <is>
+          <t>• MSC/ASC certification audit reports
+• Stock status data from fisheries management authority
+• Bycatch and discard monitoring reports
+• Feed ingredient traceability records (IFFO RS, ProTerra)
+• Antimicrobial use veterinary records
+• Escape incident reports and regulatory notifications
+• Environmental monitoring data for aquaculture sites
+• Independent observer catch certification records</t>
+        </is>
+      </c>
+      <c r="N85" s="126" t="inlineStr">
+        <is>
+          <t>• Volume of wild-catch by species and stock status (MSY reference point)
+• Percentage of wild-catch from MSC-certified fisheries (%)
+• Bycatch rate (% of total catch)
+• Discard rate (% of total catch)
+• Feed conversion ratio (FCR) for aquaculture
+• Fishmeal and fish oil sourcing from certified/responsible sources (%)
+• Antimicrobial use per tonne of production (mg/kg)
+• Sea lice levels (count per fish) vs. regulatory threshold
+• Number of escape incidents and estimated individuals escaped</t>
+        </is>
+      </c>
+      <c r="O85" s="127" t="inlineStr">
+        <is>
+          <t>Bycatch rate = Bycatch volume / Total catch × 100. Discard rate = Discards / Total catch × 100. Feed conversion ratio = Feed input / Biomass gain. AMU intensity = Total antimicrobials used (mg) / Total production (kg). Sea lice intensity = Average lice per fish across all sites. Escape rate = Escaped individuals / Total stocked individuals × 100.</t>
+        </is>
+      </c>
+      <c r="P85" s="122" t="inlineStr">
+        <is>
+          <t>Aquaculture/Fisheries Operations / Sustainability / ESG / Supply Chain / Regulatory Affairs</t>
+        </is>
+      </c>
+      <c r="Q85" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R85" s="128" t="inlineStr">
+        <is>
+          <t>• Stock status relative to MSY is the foundational disclosure for wild-catch fisheries
+• MSC certification does not substitute for disclosure — both are required
+• Antimicrobial use in aquaculture is a key public health metric — trends must be disclosed
+• Sea lice levels are a regulatory compliance and ecological impact metric — disclose against licence thresholds
+• Escape incidents must be reported to regulators and disclosed even if zero — absence of incidents should be confirmed</t>
+        </is>
+      </c>
+      <c r="S85" s="129" t="inlineStr">
+        <is>
+          <t>• Is the stock status of all commercially significant target species reported relative to MSY?
+• What percentage of wild-catch volume is certified to the Marine Stewardship Council standard?
+• Is antimicrobial use reported per tonne of production with a year-on-year trend?
+• Are all fish escape incidents reported to regulators and disclosed in the sustainability report?</t>
+        </is>
+      </c>
+      <c r="T85" s="122" t="inlineStr">
+        <is>
+          <t>GRI 13: Agriculture, Aquaculture and Fishing Sectors 2022 | Topic 13.28 | V1.1 | globalreporting.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1" s="42">
+      <c r="A86" s="132" t="inlineStr">
         <is>
           <t xml:space="preserve">   GRI 14: Mining Sector 2024</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="130" customHeight="1" s="42">
-      <c r="A61" s="122" t="inlineStr">
+    <row r="87" ht="130" customHeight="1" s="42">
+      <c r="A87" s="122" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024</t>
         </is>
       </c>
-      <c r="B61" s="122" t="inlineStr">
+      <c r="B87" s="122" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C61" s="122" t="inlineStr">
+      <c r="C87" s="122" t="inlineStr">
         <is>
           <t>Sector Context &amp; Applicability</t>
         </is>
       </c>
-      <c r="D61" s="123" t="inlineStr">
+      <c r="D87" s="123" t="inlineStr">
         <is>
           <t>GRI 14</t>
         </is>
       </c>
-      <c r="E61" s="122" t="inlineStr">
+      <c r="E87" s="122" t="inlineStr">
         <is>
           <t>Mining Sector — Overview</t>
         </is>
       </c>
-      <c r="F61" s="122" t="inlineStr">
+      <c r="F87" s="122" t="inlineStr">
         <is>
           <t>GRI 14 applies to all organizations whose primary activities include mining of metals, non-metallic minerals, and associated processing.</t>
         </is>
       </c>
-      <c r="G61" s="122" t="inlineStr">
+      <c r="G87" s="122" t="inlineStr">
         <is>
           <t>Mandatory (if sector applies)</t>
         </is>
       </c>
-      <c r="H61" s="122" t="inlineStr">
+      <c r="H87" s="122" t="inlineStr">
         <is>
           <t>Organizations with primary mining activities (metals, non-metals, aggregates)</t>
         </is>
       </c>
-      <c r="I61" s="122" t="inlineStr">
+      <c r="I87" s="122" t="inlineStr">
         <is>
           <t>Primary or significant mining activities (NACE B05, B07, B08)</t>
         </is>
       </c>
-      <c r="J61" s="122" t="inlineStr">
+      <c r="J87" s="122" t="inlineStr">
         <is>
           <t>Qualitative</t>
         </is>
       </c>
-      <c r="K61" s="122" t="inlineStr">
+      <c r="K87" s="122" t="inlineStr">
         <is>
           <t>GRI 14 identifies 23 likely material topics for the mining sector. All mining organizations should apply relevant GRI topic standards to these likely material topics. Organizations must explain omissions if a likely material topic is excluded.</t>
         </is>
       </c>
-      <c r="L61" s="124" t="inlineStr">
+      <c r="L87" s="124" t="inlineStr">
         <is>
           <t>• Mining licenses and permits
 • NACE/SIC code classification evidence
@@ -25082,7 +28227,7 @@
 • ICMM membership commitments (if applicable)</t>
         </is>
       </c>
-      <c r="M61" s="125" t="inlineStr">
+      <c r="M87" s="125" t="inlineStr">
         <is>
           <t>• Corporate registration records
 • Mining licenses
@@ -25090,7 +28235,7 @@
 • Sector association memberships</t>
         </is>
       </c>
-      <c r="N61" s="126" t="inlineStr">
+      <c r="N87" s="126" t="inlineStr">
         <is>
           <t>• Sector classification (NACE code)
 • Types of mining activities
@@ -25100,22 +28245,22 @@
 • ICMM membership status</t>
         </is>
       </c>
-      <c r="O61" s="127" t="inlineStr">
+      <c r="O87" s="127" t="inlineStr">
         <is>
           <t>No specific formula for overview. Disclosure is qualitative — organizational profile and sector classification.</t>
         </is>
       </c>
-      <c r="P61" s="122" t="inlineStr">
+      <c r="P87" s="122" t="inlineStr">
         <is>
           <t>Sustainability / Legal / Operations</t>
         </is>
       </c>
-      <c r="Q61" s="122" t="inlineStr">
+      <c r="Q87" s="122" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R61" s="128" t="inlineStr">
+      <c r="R87" s="128" t="inlineStr">
         <is>
           <t>• GRI 14 was published in 2024 — most recent sector standard
 • ICMM (International Council on Mining and Metals) membership requires GRI 14 alignment
@@ -25123,7 +28268,7 @@
 • 23 likely material topics identified — all should be assessed for materiality</t>
         </is>
       </c>
-      <c r="S61" s="129" t="inlineStr">
+      <c r="S87" s="129" t="inlineStr">
         <is>
           <t>• Is the organization classified correctly under mining NACE codes?
 • Are all mine sites included in the sustainability reporting boundary?
@@ -25131,69 +28276,69 @@
 • Are all 23 GRI 14 likely material topics assessed for materiality?</t>
         </is>
       </c>
-      <c r="T61" s="122" t="inlineStr">
+      <c r="T87" s="122" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024 | V1.1 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="130" customHeight="1" s="42">
-      <c r="A62" s="133" t="inlineStr">
+    <row r="88" ht="130" customHeight="1" s="42">
+      <c r="A88" s="133" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024</t>
         </is>
       </c>
-      <c r="B62" s="133" t="inlineStr">
+      <c r="B88" s="133" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C62" s="133" t="inlineStr">
+      <c r="C88" s="133" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Environmental</t>
         </is>
       </c>
-      <c r="D62" s="134" t="inlineStr">
+      <c r="D88" s="134" t="inlineStr">
         <is>
           <t>GRI 14 — Topic 14.1</t>
         </is>
       </c>
-      <c r="E62" s="133" t="inlineStr">
+      <c r="E88" s="133" t="inlineStr">
         <is>
           <t>GHG Emissions (Mining)</t>
         </is>
       </c>
-      <c r="F62" s="133" t="inlineStr">
+      <c r="F88" s="133" t="inlineStr">
         <is>
           <t>GHG emissions are a likely material topic for all mining organizations.</t>
         </is>
       </c>
-      <c r="G62" s="133" t="inlineStr">
+      <c r="G88" s="133" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H62" s="133" t="inlineStr">
+      <c r="H88" s="133" t="inlineStr">
         <is>
           <t>All mining sector organizations</t>
         </is>
       </c>
-      <c r="I62" s="133" t="inlineStr">
+      <c r="I88" s="133" t="inlineStr">
         <is>
           <t>Likely material per GRI 14</t>
         </is>
       </c>
-      <c r="J62" s="133" t="inlineStr">
+      <c r="J88" s="133" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K62" s="133" t="inlineStr">
+      <c r="K88" s="133" t="inlineStr">
         <is>
           <t>Report: gross Scope 1, 2 and 3 GHG emissions; GHG intensity; climate targets; fugitive methane (coal mines); diesel consumption; process emissions.</t>
         </is>
       </c>
-      <c r="L62" s="124" t="inlineStr">
+      <c r="L88" s="124" t="inlineStr">
         <is>
           <t>• GHG inventory workbooks
 • Fuel consumption records
@@ -25205,7 +28350,7 @@
 • Scope 3 calculation worksheets</t>
         </is>
       </c>
-      <c r="M62" s="125" t="inlineStr">
+      <c r="M88" s="125" t="inlineStr">
         <is>
           <t>• GHG inventory calculation records
 • Fuel purchase records
@@ -25213,7 +28358,7 @@
 • Third-party GHG verification statement</t>
         </is>
       </c>
-      <c r="N62" s="126" t="inlineStr">
+      <c r="N88" s="126" t="inlineStr">
         <is>
           <t>• Scope 1 GHG (tCO₂e)
 • Scope 2 GHG (tCO₂e) — location and market-based
@@ -25223,22 +28368,22 @@
 • GHG reduction targets and progress</t>
         </is>
       </c>
-      <c r="O62" s="127" t="inlineStr">
+      <c r="O88" s="127" t="inlineStr">
         <is>
           <t>Scope 1 = Σ(Activity × EF × GWP). Diesel: litres × 0.00268 tCO₂e/litre. GHG intensity = Total GHG / Ore processed. GWP from IPCC AR6.</t>
         </is>
       </c>
-      <c r="P62" s="133" t="inlineStr">
+      <c r="P88" s="133" t="inlineStr">
         <is>
           <t>Environmental Manager / Operations / Energy Manager</t>
         </is>
       </c>
-      <c r="Q62" s="133" t="inlineStr">
+      <c r="Q88" s="133" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R62" s="128" t="inlineStr">
+      <c r="R88" s="128" t="inlineStr">
         <is>
           <t>• Mining typically has high Scope 1 due to diesel use in haul trucks and process equipment
 • Electrification of mining equipment is a key decarbonization pathway
@@ -25246,7 +28391,7 @@
 • Science-based targets aligned with 1.5°C are expected by institutional investors</t>
         </is>
       </c>
-      <c r="S62" s="129" t="inlineStr">
+      <c r="S88" s="129" t="inlineStr">
         <is>
           <t>• Are all GHG sources identified including diesel, blasting, and process emissions?
 • Is a Scope 3 emissions assessment conducted for value chain categories?
@@ -25254,69 +28399,69 @@
 • Are science-based GHG reduction targets set?</t>
         </is>
       </c>
-      <c r="T62" s="133" t="inlineStr">
+      <c r="T88" s="133" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024 | Topic 14.1 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="130" customHeight="1" s="42">
-      <c r="A63" s="122" t="inlineStr">
+    <row r="89" ht="130" customHeight="1" s="42">
+      <c r="A89" s="122" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024</t>
         </is>
       </c>
-      <c r="B63" s="122" t="inlineStr">
+      <c r="B89" s="122" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C63" s="122" t="inlineStr">
+      <c r="C89" s="122" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Environmental</t>
         </is>
       </c>
-      <c r="D63" s="123" t="inlineStr">
+      <c r="D89" s="123" t="inlineStr">
         <is>
           <t>GRI 14 — Topic 14.2</t>
         </is>
       </c>
-      <c r="E63" s="122" t="inlineStr">
+      <c r="E89" s="122" t="inlineStr">
         <is>
           <t>Air Emissions (Mining)</t>
         </is>
       </c>
-      <c r="F63" s="122" t="inlineStr">
+      <c r="F89" s="122" t="inlineStr">
         <is>
           <t>Non-GHG air emissions including dust, NOx, SOx, mercury, and lead are a likely material topic for mining.</t>
         </is>
       </c>
-      <c r="G63" s="122" t="inlineStr">
+      <c r="G89" s="122" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H63" s="122" t="inlineStr">
+      <c r="H89" s="122" t="inlineStr">
         <is>
           <t>All mining sector organizations</t>
         </is>
       </c>
-      <c r="I63" s="122" t="inlineStr">
+      <c r="I89" s="122" t="inlineStr">
         <is>
           <t>Likely material per GRI 14</t>
         </is>
       </c>
-      <c r="J63" s="122" t="inlineStr">
+      <c r="J89" s="122" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K63" s="122" t="inlineStr">
+      <c r="K89" s="122" t="inlineStr">
         <is>
           <t>Report: total air emissions by pollutant type; dust management; stack monitoring; permit compliance; community health impacts from air quality.</t>
         </is>
       </c>
-      <c r="L63" s="124" t="inlineStr">
+      <c r="L89" s="124" t="inlineStr">
         <is>
           <t>• CEMS data records
 • Fugitive dust monitoring records
@@ -25327,7 +28472,7 @@
 • LDAR programme records</t>
         </is>
       </c>
-      <c r="M63" s="125" t="inlineStr">
+      <c r="M89" s="125" t="inlineStr">
         <is>
           <t>• Stack monitoring records
 • Permit compliance records
@@ -25335,7 +28480,7 @@
 • Third-party air quality audits</t>
         </is>
       </c>
-      <c r="N63" s="126" t="inlineStr">
+      <c r="N89" s="126" t="inlineStr">
         <is>
           <t>• Total NOx (tonnes)
 • Total SOx (tonnes)
@@ -25345,22 +28490,22 @@
 • Community health incidents related to air quality</t>
         </is>
       </c>
-      <c r="O63" s="127" t="inlineStr">
+      <c r="O89" s="127" t="inlineStr">
         <is>
           <t>Dust emission = area × wind erosion factor × control factor. Stack emissions: CEMS data or stack test. Heavy metals per speciated stack test results.</t>
         </is>
       </c>
-      <c r="P63" s="122" t="inlineStr">
+      <c r="P89" s="122" t="inlineStr">
         <is>
           <t>Environmental Manager / EHS / Operations</t>
         </is>
       </c>
-      <c r="Q63" s="122" t="inlineStr">
+      <c r="Q89" s="122" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R63" s="128" t="inlineStr">
+      <c r="R89" s="128" t="inlineStr">
         <is>
           <t>• Smelting and processing create significant SOx and heavy metal emissions
 • Dust from open-cut mines and haul roads is a major community concern
@@ -25368,7 +28513,7 @@
 • EU Industrial Emissions Directive applies to mining processing facilities</t>
         </is>
       </c>
-      <c r="S63" s="129" t="inlineStr">
+      <c r="S89" s="129" t="inlineStr">
         <is>
           <t>• Are dust monitoring programmes in place near communities?
 • Are stack emissions monitored continuously on significant sources?
@@ -25376,69 +28521,69 @@
 • Are all permit exceedances reported to regulators?</t>
         </is>
       </c>
-      <c r="T63" s="122" t="inlineStr">
+      <c r="T89" s="122" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024 | Topic 14.2 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="130" customHeight="1" s="42">
-      <c r="A64" s="133" t="inlineStr">
+    <row r="90" ht="130" customHeight="1" s="42">
+      <c r="A90" s="133" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024</t>
         </is>
       </c>
-      <c r="B64" s="133" t="inlineStr">
+      <c r="B90" s="133" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C64" s="133" t="inlineStr">
+      <c r="C90" s="133" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Environmental</t>
         </is>
       </c>
-      <c r="D64" s="134" t="inlineStr">
+      <c r="D90" s="134" t="inlineStr">
         <is>
           <t>GRI 14 — Topic 14.3</t>
         </is>
       </c>
-      <c r="E64" s="133" t="inlineStr">
+      <c r="E90" s="133" t="inlineStr">
         <is>
           <t>Water and Effluents (Mining)</t>
         </is>
       </c>
-      <c r="F64" s="133" t="inlineStr">
+      <c r="F90" s="133" t="inlineStr">
         <is>
           <t>Water withdrawal, consumption, acid mine drainage, and effluent quality are a likely material topic for mining.</t>
         </is>
       </c>
-      <c r="G64" s="133" t="inlineStr">
+      <c r="G90" s="133" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H64" s="133" t="inlineStr">
+      <c r="H90" s="133" t="inlineStr">
         <is>
           <t>All mining sector organizations</t>
         </is>
       </c>
-      <c r="I64" s="133" t="inlineStr">
+      <c r="I90" s="133" t="inlineStr">
         <is>
           <t>Likely material per GRI 14</t>
         </is>
       </c>
-      <c r="J64" s="133" t="inlineStr">
+      <c r="J90" s="133" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K64" s="133" t="inlineStr">
+      <c r="K90" s="133" t="inlineStr">
         <is>
           <t>Report: water withdrawal by source; water consumption; acid mine drainage management; tailings dam water; effluent quality; water stress.</t>
         </is>
       </c>
-      <c r="L64" s="124" t="inlineStr">
+      <c r="L90" s="124" t="inlineStr">
         <is>
           <t>• Water withdrawal records
 • Acid mine drainage records
@@ -25449,7 +28594,7 @@
 • Dewatering records</t>
         </is>
       </c>
-      <c r="M64" s="125" t="inlineStr">
+      <c r="M90" s="125" t="inlineStr">
         <is>
           <t>• Water meter data
 • AMD monitoring reports
@@ -25458,7 +28603,7 @@
 • Third-party water quality audits</t>
         </is>
       </c>
-      <c r="N64" s="126" t="inlineStr">
+      <c r="N90" s="126" t="inlineStr">
         <is>
           <t>• Water withdrawal by source (ML)
 • Water consumption (ML)
@@ -25468,22 +28613,22 @@
 • Tailings dam leakage monitoring</t>
         </is>
       </c>
-      <c r="O64" s="127" t="inlineStr">
+      <c r="O90" s="127" t="inlineStr">
         <is>
           <t>Water consumption = Withdrawal − Return flows. AMD treatment efficiency = AMD treated / Generated × 100.</t>
         </is>
       </c>
-      <c r="P64" s="133" t="inlineStr">
+      <c r="P90" s="133" t="inlineStr">
         <is>
           <t>Environmental Manager / Operations / EHS</t>
         </is>
       </c>
-      <c r="Q64" s="133" t="inlineStr">
+      <c r="Q90" s="133" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R64" s="128" t="inlineStr">
+      <c r="R90" s="128" t="inlineStr">
         <is>
           <t>• AMD is one of the most significant long-term environmental risks from mining
 • Water balance accounting should cover all inputs and outputs at site level
@@ -25491,7 +28636,7 @@
 • ICMM Water Stewardship Framework provides sector-specific guidance</t>
         </is>
       </c>
-      <c r="S64" s="129" t="inlineStr">
+      <c r="S90" s="129" t="inlineStr">
         <is>
           <t>• Is AMD prevention and treatment the primary water management priority?
 • Is a site-level water balance conducted?
@@ -25499,69 +28644,69 @@
 • Are operations in water-stressed areas managed under a water stewardship framework?</t>
         </is>
       </c>
-      <c r="T64" s="133" t="inlineStr">
+      <c r="T90" s="133" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024 | Topic 14.3 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="130" customHeight="1" s="42">
-      <c r="A65" s="122" t="inlineStr">
+    <row r="91" ht="130" customHeight="1" s="42">
+      <c r="A91" s="122" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024</t>
         </is>
       </c>
-      <c r="B65" s="122" t="inlineStr">
+      <c r="B91" s="122" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C65" s="122" t="inlineStr">
+      <c r="C91" s="122" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Environmental</t>
         </is>
       </c>
-      <c r="D65" s="123" t="inlineStr">
+      <c r="D91" s="123" t="inlineStr">
         <is>
           <t>GRI 14 — Topic 14.4</t>
         </is>
       </c>
-      <c r="E65" s="122" t="inlineStr">
+      <c r="E91" s="122" t="inlineStr">
         <is>
           <t>Biodiversity (Mining)</t>
         </is>
       </c>
-      <c r="F65" s="122" t="inlineStr">
+      <c r="F91" s="122" t="inlineStr">
         <is>
           <t>Biodiversity impacts from land disturbance, habitatss cleared, and mine rehabilitation are a likely material topic.</t>
         </is>
       </c>
-      <c r="G65" s="122" t="inlineStr">
+      <c r="G91" s="122" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H65" s="122" t="inlineStr">
+      <c r="H91" s="122" t="inlineStr">
         <is>
           <t>All mining sector organizations</t>
         </is>
       </c>
-      <c r="I65" s="122" t="inlineStr">
+      <c r="I91" s="122" t="inlineStr">
         <is>
           <t>Likely material per GRI 14</t>
         </is>
       </c>
-      <c r="J65" s="122" t="inlineStr">
+      <c r="J91" s="122" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K65" s="122" t="inlineStr">
+      <c r="K91" s="122" t="inlineStr">
         <is>
           <t>Report: land disturbed; habitats cleared; biodiversity management plans; rehabilitation area; offsets; protected areas impacted; species affected.</t>
         </is>
       </c>
-      <c r="L65" s="124" t="inlineStr">
+      <c r="L91" s="124" t="inlineStr">
         <is>
           <t>• Land disturbance records
 • ESIA biodiversity chapters
@@ -25573,7 +28718,7 @@
 • Mine closure biodiversity plan</t>
         </is>
       </c>
-      <c r="M65" s="125" t="inlineStr">
+      <c r="M91" s="125" t="inlineStr">
         <is>
           <t>• Third-party ecological surveys
 • ESIA reports
@@ -25581,7 +28726,7 @@
 • Offset verification documentation</t>
         </is>
       </c>
-      <c r="N65" s="126" t="inlineStr">
+      <c r="N91" s="126" t="inlineStr">
         <is>
           <t>• Land disturbed (ha)
 • Land rehabilitated (ha)
@@ -25591,22 +28736,22 @@
 • Biodiversity offsets committed and delivered</t>
         </is>
       </c>
-      <c r="O65" s="127" t="inlineStr">
+      <c r="O91" s="127" t="inlineStr">
         <is>
           <t>Rehabilitation rate = Area rehabilitated / Total disturbed × 100. Net biodiversity outcome = Biodiversity units created − Units lost.</t>
         </is>
       </c>
-      <c r="P65" s="122" t="inlineStr">
+      <c r="P91" s="122" t="inlineStr">
         <is>
           <t>Environmental Manager / Land Management / Operations</t>
         </is>
       </c>
-      <c r="Q65" s="122" t="inlineStr">
+      <c r="Q91" s="122" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R65" s="128" t="inlineStr">
+      <c r="R91" s="128" t="inlineStr">
         <is>
           <t>• TNFD (Taskforce on Nature-related Financial Disclosures) framework is emerging reference
 • ICMM Biodiversity Framework provides sector-specific guidance
@@ -25614,7 +28759,7 @@
 • No net loss is the sector target — net positive increasingly expected</t>
         </is>
       </c>
-      <c r="S65" s="129" t="inlineStr">
+      <c r="S91" s="129" t="inlineStr">
         <is>
           <t>• Is a biodiversity action plan in place for each mine?
 • Is rehabilitation rate tracked against targets and legally required conditions?
@@ -25622,69 +28767,69 @@
 • Is critical habitat assessment conducted per IFC PS6?</t>
         </is>
       </c>
-      <c r="T65" s="122" t="inlineStr">
+      <c r="T91" s="122" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024 | Topic 14.4 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="130" customHeight="1" s="42">
-      <c r="A66" s="133" t="inlineStr">
+    <row r="92" ht="130" customHeight="1" s="42">
+      <c r="A92" s="133" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024</t>
         </is>
       </c>
-      <c r="B66" s="133" t="inlineStr">
+      <c r="B92" s="133" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C66" s="133" t="inlineStr">
+      <c r="C92" s="133" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Environmental</t>
         </is>
       </c>
-      <c r="D66" s="134" t="inlineStr">
+      <c r="D92" s="134" t="inlineStr">
         <is>
           <t>GRI 14 — Topic 14.5</t>
         </is>
       </c>
-      <c r="E66" s="133" t="inlineStr">
+      <c r="E92" s="133" t="inlineStr">
         <is>
           <t>Waste and Tailings (Mining)</t>
         </is>
       </c>
-      <c r="F66" s="133" t="inlineStr">
+      <c r="F92" s="133" t="inlineStr">
         <is>
           <t>Waste generation including tailings management are a likely material topic for mining organizations.</t>
         </is>
       </c>
-      <c r="G66" s="133" t="inlineStr">
+      <c r="G92" s="133" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H66" s="133" t="inlineStr">
+      <c r="H92" s="133" t="inlineStr">
         <is>
           <t>All mining sector organizations</t>
         </is>
       </c>
-      <c r="I66" s="133" t="inlineStr">
+      <c r="I92" s="133" t="inlineStr">
         <is>
           <t>Likely material per GRI 14</t>
         </is>
       </c>
-      <c r="J66" s="133" t="inlineStr">
+      <c r="J92" s="133" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K66" s="133" t="inlineStr">
+      <c r="K92" s="133" t="inlineStr">
         <is>
           <t>Report: total waste by type; tailings volume; tailings dam status; waste rock management; hazardous waste; waste reduction initiatives; tailings dam safety.</t>
         </is>
       </c>
-      <c r="L66" s="124" t="inlineStr">
+      <c r="L92" s="124" t="inlineStr">
         <is>
           <t>• Waste inventory by type
 • Tailings volume records
@@ -25696,7 +28841,7 @@
 • Dam safety review reports</t>
         </is>
       </c>
-      <c r="M66" s="125" t="inlineStr">
+      <c r="M92" s="125" t="inlineStr">
         <is>
           <t>• Tailings storage facility inspection records
 • GISTM compliance assessment
@@ -25705,7 +28850,7 @@
 • Waste inventory records</t>
         </is>
       </c>
-      <c r="N66" s="126" t="inlineStr">
+      <c r="N92" s="126" t="inlineStr">
         <is>
           <t>• Total tailings generated (tonnes)
 • Tailings stored (volume/mass)
@@ -25717,22 +28862,22 @@
 • GISTM compliance status</t>
         </is>
       </c>
-      <c r="O66" s="127" t="inlineStr">
+      <c r="O92" s="127" t="inlineStr">
         <is>
           <t>Tailings volume = Mining rate × strip ratio × density. ARD potential: net acid generation (NAG) test results. Waste sent to reprocessing = Tonnes recovered / Total waste × 100.</t>
         </is>
       </c>
-      <c r="P66" s="133" t="inlineStr">
+      <c r="P92" s="133" t="inlineStr">
         <is>
           <t>Operations / Environmental Manager / Tailings Management / EHS</t>
         </is>
       </c>
-      <c r="Q66" s="133" t="inlineStr">
+      <c r="Q92" s="133" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R66" s="128" t="inlineStr">
+      <c r="R92" s="128" t="inlineStr">
         <is>
           <t>• GISTM (Global Industry Standard on Tailings Management) — ICMM/UNEP/PRI 2020 is mandatory for ICMM members
 • Tailings dam failures cause catastrophic harm — independent engineer review minimum annual
@@ -25740,7 +28885,7 @@
 • TSF classification and Emergency Action Plans are minimum disclosure requirements</t>
         </is>
       </c>
-      <c r="S66" s="129" t="inlineStr">
+      <c r="S92" s="129" t="inlineStr">
         <is>
           <t>• Is the organization GISTM-compliant?
 • Is independent engineer review of TSF conducted annually?
@@ -25748,69 +28893,69 @@
 • Is ARD potential assessed and managed for waste rock?</t>
         </is>
       </c>
-      <c r="T66" s="133" t="inlineStr">
+      <c r="T92" s="133" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024 | Topic 14.5 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="130" customHeight="1" s="42">
-      <c r="A67" s="122" t="inlineStr">
+    <row r="93" ht="130" customHeight="1" s="42">
+      <c r="A93" s="122" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024</t>
         </is>
       </c>
-      <c r="B67" s="122" t="inlineStr">
+      <c r="B93" s="122" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C67" s="122" t="inlineStr">
+      <c r="C93" s="122" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Labor</t>
         </is>
       </c>
-      <c r="D67" s="123" t="inlineStr">
+      <c r="D93" s="123" t="inlineStr">
         <is>
           <t>GRI 14 — Topic 14.6</t>
         </is>
       </c>
-      <c r="E67" s="122" t="inlineStr">
+      <c r="E93" s="122" t="inlineStr">
         <is>
           <t>Occupational Health and Safety (Mining)</t>
         </is>
       </c>
-      <c r="F67" s="122" t="inlineStr">
+      <c r="F93" s="122" t="inlineStr">
         <is>
           <t>OHS including fatalities, injuries, and disease is a likely material topic for all mining organizations.</t>
         </is>
       </c>
-      <c r="G67" s="122" t="inlineStr">
+      <c r="G93" s="122" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H67" s="122" t="inlineStr">
+      <c r="H93" s="122" t="inlineStr">
         <is>
           <t>All mining sector organizations</t>
         </is>
       </c>
-      <c r="I67" s="122" t="inlineStr">
+      <c r="I93" s="122" t="inlineStr">
         <is>
           <t>Likely material per GRI 14</t>
         </is>
       </c>
-      <c r="J67" s="122" t="inlineStr">
+      <c r="J93" s="122" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K67" s="122" t="inlineStr">
+      <c r="K93" s="122" t="inlineStr">
         <is>
           <t>Report: TRIFR; LTIFR; fatalities; occupational diseases; OHS management system; high potential incident management; contractor safety.</t>
         </is>
       </c>
-      <c r="L67" s="124" t="inlineStr">
+      <c r="L93" s="124" t="inlineStr">
         <is>
           <t>• Incident records
 • OHS management system documentation
@@ -25821,7 +28966,7 @@
 • OHSAS/ISO 45001 certification</t>
         </is>
       </c>
-      <c r="M67" s="125" t="inlineStr">
+      <c r="M93" s="125" t="inlineStr">
         <is>
           <t>• Incident records verified by safety team
 • ISO 45001 certificate
@@ -25829,7 +28974,7 @@
 • Independent safety audit reports</t>
         </is>
       </c>
-      <c r="N67" s="126" t="inlineStr">
+      <c r="N93" s="126" t="inlineStr">
         <is>
           <t>• Fatalities (employees and contractors)
 • TRIFR (per million hours)
@@ -25840,22 +28985,22 @@
 • Contractor vs. employee split</t>
         </is>
       </c>
-      <c r="O67" s="127" t="inlineStr">
+      <c r="O93" s="127" t="inlineStr">
         <is>
           <t>TRIFR = (Fatal + LTI + RWI + MTI) × 1,000,000 / Hours worked. LTIFR = LTIs × 1,000,000 / Hours worked. Use ICMM Safety Data Exchange (SDE) definitions.</t>
         </is>
       </c>
-      <c r="P67" s="122" t="inlineStr">
+      <c r="P93" s="122" t="inlineStr">
         <is>
           <t>EHS / Operations / HR</t>
         </is>
       </c>
-      <c r="Q67" s="122" t="inlineStr">
+      <c r="Q93" s="122" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R67" s="128" t="inlineStr">
+      <c r="R93" s="128" t="inlineStr">
         <is>
           <t>• ICMM Safety Data Exchange (SDE) provides standardized definitions for mining safety metrics
 • Use 1,000,000 hours worked as the base rate (not 200,000) — per ICMM/ESRS standard
@@ -25863,7 +29008,7 @@
 • High Potential Incidents (HPIs) are leading indicators — should exceed lagging indicator counts</t>
         </is>
       </c>
-      <c r="S67" s="129" t="inlineStr">
+      <c r="S93" s="129" t="inlineStr">
         <is>
           <t>• Are contractor fatalities and injuries included in safety statistics?
 • Is TRIFR calculated per ICMM SDE definitions?
@@ -25871,69 +29016,69 @@
 • Is an ISO 45001 or equivalent OHS management system independently audited?</t>
         </is>
       </c>
-      <c r="T67" s="122" t="inlineStr">
+      <c r="T93" s="122" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024 | Topic 14.6 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="130" customHeight="1" s="42">
-      <c r="A68" s="133" t="inlineStr">
+    <row r="94" ht="130" customHeight="1" s="42">
+      <c r="A94" s="133" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024</t>
         </is>
       </c>
-      <c r="B68" s="133" t="inlineStr">
+      <c r="B94" s="133" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C68" s="133" t="inlineStr">
+      <c r="C94" s="133" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Social</t>
         </is>
       </c>
-      <c r="D68" s="134" t="inlineStr">
+      <c r="D94" s="134" t="inlineStr">
         <is>
           <t>GRI 14 — Topic 14.7</t>
         </is>
       </c>
-      <c r="E68" s="133" t="inlineStr">
+      <c r="E94" s="133" t="inlineStr">
         <is>
           <t>Local Communities (Mining)</t>
         </is>
       </c>
-      <c r="F68" s="133" t="inlineStr">
+      <c r="F94" s="133" t="inlineStr">
         <is>
           <t>Impacts on local communities from mining are a likely material topic.</t>
         </is>
       </c>
-      <c r="G68" s="133" t="inlineStr">
+      <c r="G94" s="133" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H68" s="133" t="inlineStr">
+      <c r="H94" s="133" t="inlineStr">
         <is>
           <t>All mining sector organizations</t>
         </is>
       </c>
-      <c r="I68" s="133" t="inlineStr">
+      <c r="I94" s="133" t="inlineStr">
         <is>
           <t>Likely material per GRI 14</t>
         </is>
       </c>
-      <c r="J68" s="133" t="inlineStr">
+      <c r="J94" s="133" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K68" s="133" t="inlineStr">
+      <c r="K94" s="133" t="inlineStr">
         <is>
           <t>Report: community engagement; grievance mechanisms; community benefit sharing; resettlement; social impact assessment; community health, safety and security.</t>
         </is>
       </c>
-      <c r="L68" s="124" t="inlineStr">
+      <c r="L94" s="124" t="inlineStr">
         <is>
           <t>• Community engagement records
 • Grievance mechanism records
@@ -25944,7 +29089,7 @@
 • Social baseline studies</t>
         </is>
       </c>
-      <c r="M68" s="125" t="inlineStr">
+      <c r="M94" s="125" t="inlineStr">
         <is>
           <t>• Community engagement records
 • Grievance register
@@ -25953,7 +29098,7 @@
 • Community investment documentation</t>
         </is>
       </c>
-      <c r="N68" s="126" t="inlineStr">
+      <c r="N94" s="126" t="inlineStr">
         <is>
           <t>• Community grievances (count, resolution rate)
 • Community investment ($)
@@ -25962,22 +29107,22 @@
 • Community benefit sharing mechanisms</t>
         </is>
       </c>
-      <c r="O68" s="127" t="inlineStr">
+      <c r="O94" s="127" t="inlineStr">
         <is>
           <t>Grievance resolution rate = Resolved / Total × 100.</t>
         </is>
       </c>
-      <c r="P68" s="133" t="inlineStr">
+      <c r="P94" s="133" t="inlineStr">
         <is>
           <t>Community Affairs / Sustainability / Legal / Operations</t>
         </is>
       </c>
-      <c r="Q68" s="133" t="inlineStr">
+      <c r="Q94" s="133" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R68" s="128" t="inlineStr">
+      <c r="R94" s="128" t="inlineStr">
         <is>
           <t>• IFC PS1 governs community engagement and ESMS for project finance
 • Resettlement requires IFC PS5 compliance
@@ -25985,7 +29130,7 @@
 • Mining community impacts are long-term — multi-generational planning required</t>
         </is>
       </c>
-      <c r="S68" s="129" t="inlineStr">
+      <c r="S94" s="129" t="inlineStr">
         <is>
           <t>• Is an ESMS in place covering community impacts?
 • Is community grievance mechanism accessible and culturally appropriate?
@@ -25993,69 +29138,69 @@
 • Is post-closure community planning addressed?</t>
         </is>
       </c>
-      <c r="T68" s="133" t="inlineStr">
+      <c r="T94" s="133" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024 | Topic 14.7 | globalreporting.org</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="130" customHeight="1" s="42">
-      <c r="A69" s="122" t="inlineStr">
+    <row r="95" ht="130" customHeight="1" s="42">
+      <c r="A95" s="122" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024</t>
         </is>
       </c>
-      <c r="B69" s="122" t="inlineStr">
+      <c r="B95" s="122" t="inlineStr">
         <is>
           <t>Sector Standard</t>
         </is>
       </c>
-      <c r="C69" s="122" t="inlineStr">
+      <c r="C95" s="122" t="inlineStr">
         <is>
           <t>Sector-Topic Mapping: Governance</t>
         </is>
       </c>
-      <c r="D69" s="123" t="inlineStr">
+      <c r="D95" s="123" t="inlineStr">
         <is>
           <t>GRI 14 — Topic 14.8</t>
         </is>
       </c>
-      <c r="E69" s="122" t="inlineStr">
+      <c r="E95" s="122" t="inlineStr">
         <is>
           <t>Payments to Governments (Mining)</t>
         </is>
       </c>
-      <c r="F69" s="122" t="inlineStr">
+      <c r="F95" s="122" t="inlineStr">
         <is>
           <t>Payments to governments including taxes, royalties and fees are a likely material topic for mining.</t>
         </is>
       </c>
-      <c r="G69" s="122" t="inlineStr">
+      <c r="G95" s="122" t="inlineStr">
         <is>
           <t>Mandatory (sector likely material)</t>
         </is>
       </c>
-      <c r="H69" s="122" t="inlineStr">
+      <c r="H95" s="122" t="inlineStr">
         <is>
           <t>All mining sector organizations</t>
         </is>
       </c>
-      <c r="I69" s="122" t="inlineStr">
+      <c r="I95" s="122" t="inlineStr">
         <is>
           <t>Likely material per GRI 14</t>
         </is>
       </c>
-      <c r="J69" s="122" t="inlineStr">
+      <c r="J95" s="122" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K69" s="122" t="inlineStr">
+      <c r="K95" s="122" t="inlineStr">
         <is>
           <t>Report: total payments to governments by type and country; royalties; income tax; EITI compliance; mineral resource royalty calculation.</t>
         </is>
       </c>
-      <c r="L69" s="124" t="inlineStr">
+      <c r="L95" s="124" t="inlineStr">
         <is>
           <t>• Government payment records by country
 • Mining royalty calculation records
@@ -26065,7 +29210,7 @@
 • Mineral right acquisition costs</t>
         </is>
       </c>
-      <c r="M69" s="125" t="inlineStr">
+      <c r="M95" s="125" t="inlineStr">
         <is>
           <t>• Tax payment receipts
 • Royalty calculation documentation
@@ -26073,7 +29218,7 @@
 • Finance sign-off on data</t>
         </is>
       </c>
-      <c r="N69" s="126" t="inlineStr">
+      <c r="N95" s="126" t="inlineStr">
         <is>
           <t>• Income tax by country
 • Royalties by country
@@ -26082,22 +29227,22 @@
 • EITI compliance status</t>
         </is>
       </c>
-      <c r="O69" s="127" t="inlineStr">
+      <c r="O95" s="127" t="inlineStr">
         <is>
           <t>Royalty = Production × Royalty rate (%) × Price. Total payments = Tax + Royalties + Fees.</t>
         </is>
       </c>
-      <c r="P69" s="122" t="inlineStr">
+      <c r="P95" s="122" t="inlineStr">
         <is>
           <t>Finance / Tax / Legal</t>
         </is>
       </c>
-      <c r="Q69" s="122" t="inlineStr">
+      <c r="Q95" s="122" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="R69" s="128" t="inlineStr">
+      <c r="R95" s="128" t="inlineStr">
         <is>
           <t>• EITI is the gold standard for extractive fiscal transparency
 • EU Accounting Directive (Chapter 10) requires payment disclosure for resource extractors
@@ -26105,7 +29250,7 @@
 • Community development levies may also be required</t>
         </is>
       </c>
-      <c r="S69" s="129" t="inlineStr">
+      <c r="S95" s="129" t="inlineStr">
         <is>
           <t>• Are payments disclosed by country and payment type?
 • Is EITI membership adopted?
@@ -26113,21 +29258,23 @@
 • Are community development levies disclosed?</t>
         </is>
       </c>
-      <c r="T69" s="122" t="inlineStr">
+      <c r="T95" s="122" t="inlineStr">
         <is>
           <t>GRI 14: Mining Sector 2024 | Topic 14.8 | globalreporting.org</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
+    <mergeCell ref="A70:T70"/>
     <mergeCell ref="A21:T21"/>
+    <mergeCell ref="A86:T86"/>
     <mergeCell ref="A15:T15"/>
+    <mergeCell ref="A59:T59"/>
     <mergeCell ref="A38:T38"/>
     <mergeCell ref="A2:T2"/>
     <mergeCell ref="A49:T49"/>
     <mergeCell ref="A10:T10"/>
-    <mergeCell ref="A60:T60"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26139,7 +29286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T79"/>
+  <dimension ref="A1:T108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="22" customWidth="1" style="42" min="1" max="1"/>
@@ -34423,17 +37570,2719 @@
         </is>
       </c>
     </row>
+    <row r="80" ht="8" customHeight="1" s="42"/>
+    <row r="81" ht="22" customHeight="1" s="42">
+      <c r="A81" s="135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ESRS 2 — Minimum Disclosure Requirements (MDR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="130" customHeight="1" s="42">
+      <c r="A82" s="122" t="inlineStr">
+        <is>
+          <t>ESRS 2: General Disclosures</t>
+        </is>
+      </c>
+      <c r="B82" s="122" t="inlineStr">
+        <is>
+          <t>ESRS Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C82" s="122" t="inlineStr">
+        <is>
+          <t>Minimum Disclosure Requirements</t>
+        </is>
+      </c>
+      <c r="D82" s="123" t="inlineStr">
+        <is>
+          <t>ESRS 2 MDR-P</t>
+        </is>
+      </c>
+      <c r="E82" s="122" t="inlineStr">
+        <is>
+          <t>Minimum Disclosure Requirements — Policies</t>
+        </is>
+      </c>
+      <c r="F82" s="122" t="inlineStr">
+        <is>
+          <t>For each material topic with policies, disclose the content, scope, and governance of those policies following the MDR-P template.</t>
+        </is>
+      </c>
+      <c r="G82" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (for each material topic with policies)</t>
+        </is>
+      </c>
+      <c r="H82" s="122" t="inlineStr">
+        <is>
+          <t>All entities in scope of CSRD with material topics requiring policy disclosure</t>
+        </is>
+      </c>
+      <c r="I82" s="122" t="inlineStr">
+        <is>
+          <t>Applicable across all material ESRS topics</t>
+        </is>
+      </c>
+      <c r="J82" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K82" s="122" t="inlineStr">
+        <is>
+          <t>For each policy related to a material sustainability matter, disclose: (a) a description of its content and key requirements; (b) the scope of the policy (entity-level, group-level, specific operations); (c) the most senior level of management or governance body accountable; (d) whether the policy is publicly available; (e) whether the policy applies to third parties (suppliers, partners); (f) the date of last review.</t>
+        </is>
+      </c>
+      <c r="L82" s="124" t="inlineStr">
+        <is>
+          <t>• Master policy register with all sustainability-related policies
+• Policy summary sheets for each material topic area
+• Governance accountability matrix (who owns each policy)
+• Policy publication records (internal intranet, public website)
+• Third-party applicability statements (supplier codes, partner requirements)
+• Policy review log with dates and version history
+• Board or management committee approval minutes for policies
+• Gap analysis against ESRS topic-specific MDR-P requirements</t>
+        </is>
+      </c>
+      <c r="M82" s="125" t="inlineStr">
+        <is>
+          <t>• Policy register signed off by Chief Sustainability Officer or equivalent
+• Published policies accessible on corporate website
+• Board/committee approval records for each policy
+• Evidence of policy communication to relevant stakeholders
+• Gap analysis against all applicable ESRS standards
+• Legal review records for regulatory compliance of policies</t>
+        </is>
+      </c>
+      <c r="N82" s="126" t="inlineStr">
+        <is>
+          <t>• Total number of sustainability-related policies in place
+• Number of material topics with formal policies
+• Percentage of material topics covered by formal policy (%)
+• Number of policies publicly available vs. internal only
+• Number of policies covering third parties (suppliers, partners)
+• Date of last review for each policy
+• Number of policies pending update or creation</t>
+        </is>
+      </c>
+      <c r="O82" s="127" t="inlineStr">
+        <is>
+          <t>Policy completeness = Topics with formal policies / Total material topics × 100. Third-party coverage = Policies extending to third parties / Total policies × 100. Timeliness = Policies reviewed within 2 years / Total policies × 100. No prescribed quantitative formula for policy content — structured narrative required.</t>
+        </is>
+      </c>
+      <c r="P82" s="122" t="inlineStr">
+        <is>
+          <t>Sustainability / ESG / Legal / Compliance / Risk Management</t>
+        </is>
+      </c>
+      <c r="Q82" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R82" s="128" t="inlineStr">
+        <is>
+          <t>• MDR-P is the baseline requirement — topic-specific standards may require additional policy content
+• 'Publicly available' requirement demands active publication, not just availability on request
+• Policies must be reviewed and current — assurers will flag out-of-date policies
+• Accountability must be explicit — named governance body, not vague 'management'
+• Third-party applicability must be enforceable through contract, not aspirational</t>
+        </is>
+      </c>
+      <c r="S82" s="129" t="inlineStr">
+        <is>
+          <t>• Does the organization have formal policies for all identified material sustainability topics?
+• Are accountability structures for each policy clearly assigned to a specific governance body?
+• Are policies publicly available, and is the MDR-P structure used consistently?
+• Is there a documented policy review process with clear frequency and sign-off requirements?</t>
+        </is>
+      </c>
+      <c r="T82" s="122" t="inlineStr">
+        <is>
+          <t>ESRS 2 | MDR-P | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="130" customHeight="1" s="42">
+      <c r="A83" s="136" t="inlineStr">
+        <is>
+          <t>ESRS 2: General Disclosures</t>
+        </is>
+      </c>
+      <c r="B83" s="136" t="inlineStr">
+        <is>
+          <t>ESRS Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C83" s="136" t="inlineStr">
+        <is>
+          <t>Minimum Disclosure Requirements</t>
+        </is>
+      </c>
+      <c r="D83" s="137" t="inlineStr">
+        <is>
+          <t>ESRS 2 MDR-A</t>
+        </is>
+      </c>
+      <c r="E83" s="136" t="inlineStr">
+        <is>
+          <t>Minimum Disclosure Requirements — Actions</t>
+        </is>
+      </c>
+      <c r="F83" s="136" t="inlineStr">
+        <is>
+          <t>For each material topic with actions, disclose the content, scope, resources, and progress of those actions following the MDR-A template.</t>
+        </is>
+      </c>
+      <c r="G83" s="136" t="inlineStr">
+        <is>
+          <t>Mandatory (for each material topic with actions)</t>
+        </is>
+      </c>
+      <c r="H83" s="136" t="inlineStr">
+        <is>
+          <t>All entities in scope of CSRD with material topics requiring action disclosure</t>
+        </is>
+      </c>
+      <c r="I83" s="136" t="inlineStr">
+        <is>
+          <t>Applicable across all material ESRS topics</t>
+        </is>
+      </c>
+      <c r="J83" s="136" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K83" s="136" t="inlineStr">
+        <is>
+          <t>For each action related to a material sustainability matter, disclose: (a) a description of the action; (b) the scope and timeline; (c) progress made in the reporting period; (d) quantitative and qualitative outcomes achieved; (e) resources allocated (financial and non-financial); (f) whether actions are preventive, mitigative or remedial; (g) how actions relate to targets.</t>
+        </is>
+      </c>
+      <c r="L83" s="124" t="inlineStr">
+        <is>
+          <t>• Action plan register for all material sustainability topics
+• Project implementation records and milestone tracking
+• Budget allocation records per action/programme
+• Progress reporting templates and completed reports
+• KPI dashboards showing action outcomes
+• Governance sign-off records for major actions
+• External programme or initiative documentation (if third-party managed)
+• Link to financial accounts for resource allocation verification</t>
+        </is>
+      </c>
+      <c r="M83" s="125" t="inlineStr">
+        <is>
+          <t>• Action implementation records with completion evidence
+• Budget expenditure vs. allocation records
+• Outcome measurement data (quantitative where possible)
+• Management sign-off on action progress reports
+• Third-party evaluation or assurance of major actions
+• Year-on-year comparison of action portfolio progress</t>
+        </is>
+      </c>
+      <c r="N83" s="126" t="inlineStr">
+        <is>
+          <t>• Total number of sustainability actions underway or completed
+• Actions classified by type (preventive / mitigative / remedial)
+• Resources allocated per action category ($)
+• Percentage of planned actions completed on schedule
+• Outcome metrics per action (quantitative where measurable)
+• Number of actions linked to formal targets
+• Actions linked to partnerships or external commitments</t>
+        </is>
+      </c>
+      <c r="O83" s="127" t="inlineStr">
+        <is>
+          <t>Action completion rate = Actions completed / Total planned actions × 100. On-time completion = Actions delivered on schedule / Total actions × 100. Budget utilisation = Actual spend / Budgeted spend × 100. Outcome metrics are action-specific — no single formula. Track each action's KPI against its baseline.</t>
+        </is>
+      </c>
+      <c r="P83" s="136" t="inlineStr">
+        <is>
+          <t>Sustainability / ESG / Operations / Finance / Project Management</t>
+        </is>
+      </c>
+      <c r="Q83" s="136" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R83" s="128" t="inlineStr">
+        <is>
+          <t>• MDR-A requires demonstration of completion, not just planning
+• Resource allocation (financial and human) must be quantifiable
+• Actions must be clearly linked to identified material impacts and targets
+• Assurers distinguish between ongoing business-as-usual activities and genuine action
+• 'Planned' actions must include a credible timeline with accountability</t>
+        </is>
+      </c>
+      <c r="S83" s="129" t="inlineStr">
+        <is>
+          <t>• Are all material sustainability actions documented with timelines and resources allocated?
+• Is there a clear distinction between business-as-usual operations and specific sustainability actions?
+• Are actions demonstrably linked to the organisation's material impacts and targets?
+• Are action outcomes measured and reported with consistent methodology?</t>
+        </is>
+      </c>
+      <c r="T83" s="136" t="inlineStr">
+        <is>
+          <t>ESRS 2 | MDR-A | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="130" customHeight="1" s="42">
+      <c r="A84" s="122" t="inlineStr">
+        <is>
+          <t>ESRS 2: General Disclosures</t>
+        </is>
+      </c>
+      <c r="B84" s="122" t="inlineStr">
+        <is>
+          <t>ESRS Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C84" s="122" t="inlineStr">
+        <is>
+          <t>Minimum Disclosure Requirements</t>
+        </is>
+      </c>
+      <c r="D84" s="123" t="inlineStr">
+        <is>
+          <t>ESRS 2 MDR-T</t>
+        </is>
+      </c>
+      <c r="E84" s="122" t="inlineStr">
+        <is>
+          <t>Minimum Disclosure Requirements — Targets</t>
+        </is>
+      </c>
+      <c r="F84" s="122" t="inlineStr">
+        <is>
+          <t>For each material topic with targets, disclose the structure, methodology, baseline, and progress following the MDR-T template.</t>
+        </is>
+      </c>
+      <c r="G84" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (for each material topic with targets)</t>
+        </is>
+      </c>
+      <c r="H84" s="122" t="inlineStr">
+        <is>
+          <t>All entities in scope of CSRD with material topics requiring targets disclosure</t>
+        </is>
+      </c>
+      <c r="I84" s="122" t="inlineStr">
+        <is>
+          <t>Applicable across all material ESRS topics</t>
+        </is>
+      </c>
+      <c r="J84" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K84" s="122" t="inlineStr">
+        <is>
+          <t>For each target related to a material sustainability matter, disclose: (a) the description of the target; (b) the relationship to applicable policies and actions; (c) the timeline with milestones; (d) the baseline value and year; (e) the target value; (f) progress made during the reporting period; (g) whether the target has been revised and why; (h) the measurement methodology.</t>
+        </is>
+      </c>
+      <c r="L84" s="124" t="inlineStr">
+        <is>
+          <t>• Target register covering all material sustainability topics
+• Baseline data records with sources for each target
+• Target governance and approval documentation
+• Milestone tracking records
+• Measurement methodology documents per target
+• Progress reporting templates and completed annual reviews
+• External commitments referenced in targets (SBTi, TCFD, SDGs)
+• Target revision log with rationale for any changes</t>
+        </is>
+      </c>
+      <c r="M84" s="125" t="inlineStr">
+        <is>
+          <t>• Baseline data verified by internal or external audit
+• Progress tracking evidence (raw data, calculations)
+• Board or management approval records for each target
+• Third-party verification reports (where applicable)
+• Explanation of any target revisions with documented rationale
+• Methodology documents for calculation of each metric</t>
+        </is>
+      </c>
+      <c r="N84" s="126" t="inlineStr">
+        <is>
+          <t>• Total number of targets set across material topics
+• Baseline year and value for each target
+• Target year and value for each target
+• Actual performance in reporting period for each target
+• Number of targets: achieved / on track / behind schedule
+• Number of targets aligned to external standards (SBTi, Paris Agreement, SDGs)
+• Number of targets revised during reporting period</t>
+        </is>
+      </c>
+      <c r="O84" s="127" t="inlineStr">
+        <is>
+          <t>Progress % = (Current − Baseline) / (Target − Baseline) × 100. Achievement rate = Targets achieved or on track / Total targets × 100. For each target, disclose the specific measurement formula used. Ensure baseline and target are expressed in the same unit and timeframe. Track lag indicators (outcomes) and lead indicators (activities) separately.</t>
+        </is>
+      </c>
+      <c r="P84" s="122" t="inlineStr">
+        <is>
+          <t>Sustainability / ESG / Strategy / Finance / Risk Management</t>
+        </is>
+      </c>
+      <c r="Q84" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R84" s="128" t="inlineStr">
+        <is>
+          <t>• MDR-T requires each target to have a documented measurement methodology
+• Baselines must be fixed — assurers will flag restated baselines without explanation
+• Targets must be distinguishable from aspirations — SMART criteria apply
+• External standard alignment (SBTi, CDP) enhances credibility
+• Revised targets require transparent rationale — downward revisions are highly scrutinised</t>
+        </is>
+      </c>
+      <c r="S84" s="129" t="inlineStr">
+        <is>
+          <t>• Does every material sustainability target have a documented baseline, methodology, and timeline?
+• Are targets across all material ESRS topics consistently structured using MDR-T?
+• Can the organisation demonstrate independence between target-setting and performance measurement?
+• Are all target revisions logged with rationale and approved by a governance body?</t>
+        </is>
+      </c>
+      <c r="T84" s="122" t="inlineStr">
+        <is>
+          <t>ESRS 2 | MDR-T | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="130" customHeight="1" s="42">
+      <c r="A85" s="136" t="inlineStr">
+        <is>
+          <t>ESRS 2: General Disclosures</t>
+        </is>
+      </c>
+      <c r="B85" s="136" t="inlineStr">
+        <is>
+          <t>ESRS Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C85" s="136" t="inlineStr">
+        <is>
+          <t>Minimum Disclosure Requirements</t>
+        </is>
+      </c>
+      <c r="D85" s="137" t="inlineStr">
+        <is>
+          <t>ESRS 2 MDR-M</t>
+        </is>
+      </c>
+      <c r="E85" s="136" t="inlineStr">
+        <is>
+          <t>Minimum Disclosure Requirements — Metrics</t>
+        </is>
+      </c>
+      <c r="F85" s="136" t="inlineStr">
+        <is>
+          <t>For each material topic with quantitative reporting requirements, disclose the metrics, methodologies, and data quality information following the MDR-M template.</t>
+        </is>
+      </c>
+      <c r="G85" s="136" t="inlineStr">
+        <is>
+          <t>Mandatory (for each material topic with quantitative disclosures)</t>
+        </is>
+      </c>
+      <c r="H85" s="136" t="inlineStr">
+        <is>
+          <t>All entities in scope of CSRD reporting quantitative sustainability data</t>
+        </is>
+      </c>
+      <c r="I85" s="136" t="inlineStr">
+        <is>
+          <t>Applicable across all material ESRS topics</t>
+        </is>
+      </c>
+      <c r="J85" s="136" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K85" s="136" t="inlineStr">
+        <is>
+          <t>For each metric related to a material sustainability matter, disclose: (a) the metric value and unit of measurement; (b) the scope of data collection; (c) the methodology used to calculate or measure; (d) any assumptions, estimation methodologies, or proxies applied; (e) changes in methodology vs. prior reporting periods and their effect.</t>
+        </is>
+      </c>
+      <c r="L85" s="124" t="inlineStr">
+        <is>
+          <t>• Metric data register covering all material topics
+• Calculation methodology documents for each quantitative metric
+• Data collection process descriptions per metric
+• Scope boundary definitions for metric calculation
+• Estimation and proxy methodology records
+• Year-on-year methodology change log
+• Data quality and completeness assessment
+• Internal data governance procedures for sustainability metrics</t>
+        </is>
+      </c>
+      <c r="M85" s="125" t="inlineStr">
+        <is>
+          <t>• Raw data records supporting each metric
+• Calculation workbooks showing methodology application
+• Internal audit or data quality review records
+• External assurance reports on metric data
+• Boundary definition sign-off records
+• Year-on-year comparability analysis</t>
+        </is>
+      </c>
+      <c r="N85" s="126" t="inlineStr">
+        <is>
+          <t>• Total number of quantitative metrics reported
+• Metrics by ESRS topic and category
+• Data coverage % (entities or operations included in scope)
+• Estimation % (proportion of data estimated vs. measured)
+• Number of methodology changes vs. prior year
+• Data quality assessment score or rating
+• External assurance coverage of metrics (%)</t>
+        </is>
+      </c>
+      <c r="O85" s="127" t="inlineStr">
+        <is>
+          <t>Data coverage % = Entities with measured data / Total in-scope entities × 100. Estimation rate = Estimated data points / Total data points × 100. Methodology change impact = (Restated current year value − Originally reported value) / Originally reported value × 100. Each metric has its own calculation formula — MDR-M requires this to be documented per metric.</t>
+        </is>
+      </c>
+      <c r="P85" s="136" t="inlineStr">
+        <is>
+          <t>Sustainability / ESG / Finance / Data Management / Internal Audit</t>
+        </is>
+      </c>
+      <c r="Q85" s="136" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R85" s="128" t="inlineStr">
+        <is>
+          <t>• MDR-M is the assurance foundation — all quantitative ESRS metrics must be anchored here
+• Estimation methodologies must be disclosed — assurers check for appropriateness
+• Methodology changes require comparative restated figures or explanation of non-restatement
+• Data coverage gaps must be disclosed with plans to close them
+• Internal controls over sustainability data quality must be documented</t>
+        </is>
+      </c>
+      <c r="S85" s="129" t="inlineStr">
+        <is>
+          <t>• Is there a documented methodology for every quantitative metric reported under ESRS?
+• Are estimation rates and methods disclosed for all material metrics?
+• Are methodology changes documented with the impact on comparability?
+• Does the organisation have adequate internal controls over sustainability data quality?</t>
+        </is>
+      </c>
+      <c r="T85" s="136" t="inlineStr">
+        <is>
+          <t>ESRS 2 | MDR-M | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="130" customHeight="1" s="42">
+      <c r="A86" s="122" t="inlineStr">
+        <is>
+          <t>ESRS 2: General Disclosures</t>
+        </is>
+      </c>
+      <c r="B86" s="122" t="inlineStr">
+        <is>
+          <t>ESRS Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C86" s="122" t="inlineStr">
+        <is>
+          <t>Minimum Disclosure Requirements</t>
+        </is>
+      </c>
+      <c r="D86" s="123" t="inlineStr">
+        <is>
+          <t>ESRS 2 MDR-E</t>
+        </is>
+      </c>
+      <c r="E86" s="122" t="inlineStr">
+        <is>
+          <t>Minimum Disclosure Requirements — Events, Conditions and Dependencies</t>
+        </is>
+      </c>
+      <c r="F86" s="122" t="inlineStr">
+        <is>
+          <t>Disclose information about significant events, conditions, and dependencies related to the sustainability matters reported, following the MDR-E template.</t>
+        </is>
+      </c>
+      <c r="G86" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (where significant events, conditions or dependencies exist for material topics)</t>
+        </is>
+      </c>
+      <c r="H86" s="122" t="inlineStr">
+        <is>
+          <t>All entities where significant events or dependencies materially affect reported sustainability information</t>
+        </is>
+      </c>
+      <c r="I86" s="122" t="inlineStr">
+        <is>
+          <t>Applicable across all material ESRS topics</t>
+        </is>
+      </c>
+      <c r="J86" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K86" s="122" t="inlineStr">
+        <is>
+          <t>For material sustainability matters affected by significant events, conditions, or dependencies, disclose: (a) descriptions of significant events or conditions arising during the reporting period that affect comparability of sustainability data; (b) material dependencies on ecosystem services, natural resources, or social conditions; (c) scenarios or assumptions underpinning forward-looking disclosures; (d) the effect of events/conditions on reported metrics.</t>
+        </is>
+      </c>
+      <c r="L86" s="124" t="inlineStr">
+        <is>
+          <t>• Event and condition log for all material sustainability topics
+• Dependency mapping records (natural capital, ecosystem services)
+• Forward-looking scenario assumptions and documentation
+• Restated data records (for events affecting prior period comparability)
+• Extraordinary event reporting records (climate events, regulatory changes)
+• Natural capital dependency assessment (TNFD/LEAP framework records)
+• Merger and acquisition impact assessment on sustainability metrics
+• Boundary change documentation</t>
+        </is>
+      </c>
+      <c r="M86" s="125" t="inlineStr">
+        <is>
+          <t>• Event log with quantified impact on sustainability metrics
+• Dependency assessment reports (ecosystem, community, regulatory)
+• Scenario modelling documentation and assumptions
+• Restated prior period data with explanation
+• Audit trail for boundary changes affecting metric comparability
+• Management sign-off on disclosure of significant events</t>
+        </is>
+      </c>
+      <c r="N86" s="126" t="inlineStr">
+        <is>
+          <t>• Number of significant events disclosed affecting sustainability metrics
+• Quantified impact of each event on reported metrics (where applicable)
+• Number of material dependencies identified (natural capital, social, regulatory)
+• Percentage of forward-looking disclosures with documented scenario assumptions
+• Number of restatements made due to boundary changes or significant events
+• Categories of events: acquisition/disposal, regulatory change, climate event, social disruption</t>
+        </is>
+      </c>
+      <c r="O86" s="127" t="inlineStr">
+        <is>
+          <t>Event impact % = Change in metric attributable to event / Total reported metric value × 100. Dependency materiality = Dependencies mapped to financial/impact materiality threshold. Restatement impact = (Restated value − Originally reported value) / Originally reported value × 100. Each event is qualitatively described and quantified where possible.</t>
+        </is>
+      </c>
+      <c r="P86" s="122" t="inlineStr">
+        <is>
+          <t>Sustainability / ESG / Finance / Risk Management / Strategy</t>
+        </is>
+      </c>
+      <c r="Q86" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R86" s="128" t="inlineStr">
+        <is>
+          <t>• MDR-E is critical for ensuring comparability of sustainability data year-on-year
+• Acquisitions and disposals are the most common events requiring disclosure
+• Natural capital dependencies are increasingly material under TNFD and biodiversity ESRS
+• Forward-looking assumptions must be disclosed for scenario-based metrics
+• Assurers will check whether significant events have been appropriately disclosed and quantified</t>
+        </is>
+      </c>
+      <c r="S86" s="129" t="inlineStr">
+        <is>
+          <t>• Are significant events that affect the comparability of sustainability metrics promptly identified and disclosed?
+• Is there a systematic process for identifying material dependencies on natural and social systems?
+• Are forward-looking disclosures supported by documented scenario assumptions?
+• Are restatements for prior period data clearly explained and quantified?</t>
+        </is>
+      </c>
+      <c r="T86" s="122" t="inlineStr">
+        <is>
+          <t>ESRS 2 | MDR-E | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="8" customHeight="1" s="42"/>
+    <row r="88" ht="22" customHeight="1" s="42">
+      <c r="A88" s="135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ESRS S2 — Workers in the Value Chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="130" customHeight="1" s="42">
+      <c r="A89" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S2: Workers in the Value Chain</t>
+        </is>
+      </c>
+      <c r="B89" s="122" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C89" s="122" t="inlineStr">
+        <is>
+          <t>Value Chain Workers</t>
+        </is>
+      </c>
+      <c r="D89" s="123" t="inlineStr">
+        <is>
+          <t>ESRS S2-1</t>
+        </is>
+      </c>
+      <c r="E89" s="122" t="inlineStr">
+        <is>
+          <t>Policies Related to Value Chain Workers</t>
+        </is>
+      </c>
+      <c r="F89" s="122" t="inlineStr">
+        <is>
+          <t>Disclose the organization's policies addressing the rights and working conditions of workers in the value chain.</t>
+        </is>
+      </c>
+      <c r="G89" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (if material)</t>
+        </is>
+      </c>
+      <c r="H89" s="122" t="inlineStr">
+        <is>
+          <t>All entities in scope of CSRD where value chain workers are material</t>
+        </is>
+      </c>
+      <c r="I89" s="122" t="inlineStr">
+        <is>
+          <t>Impact materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J89" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K89" s="122" t="inlineStr">
+        <is>
+          <t>Disclose: (a) a description of the policies adopted to manage material impacts on value chain workers; (b) how these policies apply throughout the value chain; (c) whether the organization has adopted a human rights policy that covers workers in upstream and downstream value chains; (d) reference to international standards (ILO, UNGP) underpinning the policies.</t>
+        </is>
+      </c>
+      <c r="L89" s="124" t="inlineStr">
+        <is>
+          <t>• Human rights policy covering value chain workers
+• Supplier/vendor code of conduct
+• Responsible sourcing or ethical trade policy
+• Modern slavery and forced labour policy
+• Child labour prevention policy
+• Freedom of association and collective bargaining policy
+• Policy sign-off by Board or senior management
+• Due diligence process documentation for value chain
+• Supplier onboarding and assessment procedures</t>
+        </is>
+      </c>
+      <c r="M89" s="125" t="inlineStr">
+        <is>
+          <t>• Board-approved policy documents with version control
+• Evidence of policy communication to supply chain partners
+• Supplier acknowledgement records
+• Industry certifications (SA8000, Fair Trade, RBA) if applicable
+• Human rights impact assessment reports
+• External audit reports from supply chain assessments</t>
+        </is>
+      </c>
+      <c r="N89" s="126" t="inlineStr">
+        <is>
+          <t>• Number of tier-1 suppliers covered by human rights policy
+• Percentage of procurement spend under supplier code of conduct
+• Scope of policy (categories of workers covered)
+• International standards referenced (ILO core conventions, UNGP)
+• Policy review date and approval body
+• Number of value chain worker categories identified as at-risk</t>
+        </is>
+      </c>
+      <c r="O89" s="127" t="inlineStr">
+        <is>
+          <t>Policy coverage % = Suppliers signed to CoC / Total suppliers × 100. Spend coverage % = Spend under CoC / Total procurement spend × 100. No prescribed formula for qualitative policy disclosures — narrative with quantitative coverage metrics.</t>
+        </is>
+      </c>
+      <c r="P89" s="122" t="inlineStr">
+        <is>
+          <t>Procurement / Supply Chain / Human Rights / ESG / Legal</t>
+        </is>
+      </c>
+      <c r="Q89" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R89" s="128" t="inlineStr">
+        <is>
+          <t>• Policy must explicitly name value chain workers (not just own employees)
+• Reference to ILO core conventions and UNGPs strengthens disclosure quality
+• Assurers will check policy for gaps vs. sector risks (e.g. migrant labour risk)
+• Policy must be publicly available or explain why not
+• Gap between policy intent and implementation should be acknowledged</t>
+        </is>
+      </c>
+      <c r="S89" s="129" t="inlineStr">
+        <is>
+          <t>• Does the human rights policy explicitly cover workers throughout the value chain?
+• Are there specific provisions for high-risk worker categories (migrant, seasonal, homeworkers)?
+• Is the policy communicated to and acknowledged by key suppliers?
+• Are supplier audit findings used to improve policy content?</t>
+        </is>
+      </c>
+      <c r="T89" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S2 | Disclosure S2-1 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="130" customHeight="1" s="42">
+      <c r="A90" s="136" t="inlineStr">
+        <is>
+          <t>ESRS S2: Workers in the Value Chain</t>
+        </is>
+      </c>
+      <c r="B90" s="136" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C90" s="136" t="inlineStr">
+        <is>
+          <t>Value Chain Workers</t>
+        </is>
+      </c>
+      <c r="D90" s="137" t="inlineStr">
+        <is>
+          <t>ESRS S2-2</t>
+        </is>
+      </c>
+      <c r="E90" s="136" t="inlineStr">
+        <is>
+          <t>Processes for Engaging with Value Chain Workers about Impacts</t>
+        </is>
+      </c>
+      <c r="F90" s="136" t="inlineStr">
+        <is>
+          <t>Disclose the processes through which the organization engages with value chain workers and their representatives to understand and address impacts on them.</t>
+        </is>
+      </c>
+      <c r="G90" s="136" t="inlineStr">
+        <is>
+          <t>Mandatory (if material)</t>
+        </is>
+      </c>
+      <c r="H90" s="136" t="inlineStr">
+        <is>
+          <t>All entities with material impacts on value chain workers</t>
+        </is>
+      </c>
+      <c r="I90" s="136" t="inlineStr">
+        <is>
+          <t>Impact materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J90" s="136" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K90" s="136" t="inlineStr">
+        <is>
+          <t>Disclose: (a) whether and how the organization engages with workers in the value chain (or their representatives) on impacts; (b) whether engagement is direct or through other means (worker representatives, NGOs, trade unions); (c) how feedback from value chain workers informs the organization's approach to managing impacts; (d) any barriers to effective engagement identified.</t>
+        </is>
+      </c>
+      <c r="L90" s="124" t="inlineStr">
+        <is>
+          <t>• Supplier engagement programme documentation
+• Worker voice / feedback mechanisms (hotlines, surveys, audits)
+• Grievance mechanism process description
+• Trade union or worker representative engagement records
+• Participatory assessment methodology documents
+• Stakeholder engagement logs (for value chain workers)
+• Documentation of engagement outputs and actions taken
+• Third-party social audit engagement records</t>
+        </is>
+      </c>
+      <c r="M90" s="125" t="inlineStr">
+        <is>
+          <t>• Records of grievances received and resolved from value chain workers
+• Supplier survey results and response rates
+• Worker interview records from supplier audits
+• Evidence that feedback has influenced policy or practice
+• Independent verification of engagement process
+• Trade union or NGO endorsement (where applicable)</t>
+        </is>
+      </c>
+      <c r="N90" s="126" t="inlineStr">
+        <is>
+          <t>• Number of suppliers engaged on worker impacts
+• Number of worker grievances received through value chain channels
+• Resolution rate of value chain worker grievances (%)
+• Types of engagement mechanisms (surveys, audits, hotlines, dialogue)
+• Percentage of high-risk suppliers where direct worker engagement occurred
+• Frequency of engagement activities (annual audit, quarterly survey, etc.)
+• Number of worker representatives included in engagement processes</t>
+        </is>
+      </c>
+      <c r="O90" s="127" t="inlineStr">
+        <is>
+          <t>Grievance resolution rate = Grievances resolved / Grievances received × 100. Engagement coverage = Suppliers engaged / Total suppliers × 100. Qualitative description of engagement methodology required alongside quantitative metrics.</t>
+        </is>
+      </c>
+      <c r="P90" s="136" t="inlineStr">
+        <is>
+          <t>Supply Chain / Human Rights / Sustainability / Procurement / ESG</t>
+        </is>
+      </c>
+      <c r="Q90" s="136" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R90" s="128" t="inlineStr">
+        <is>
+          <t>• Assurers look for evidence of genuine two-way engagement (not just one-way audit)
+• Distinction between audit-based information gathering vs. worker dialogue is important
+• Grievance mechanisms must be accessible, trusted, and confidential for workers
+• Response to engagement findings must be demonstrable
+• Barriers to engagement (language, geography, migrant status) should be acknowledged</t>
+        </is>
+      </c>
+      <c r="S90" s="129" t="inlineStr">
+        <is>
+          <t>• Are engagement mechanisms accessible to all categories of value chain workers?
+• Is there evidence that engagement findings have led to improvements?
+• How are workers in informal or subcontracted supply chains reached?
+• Are grievances from value chain workers tracked separately from internal grievances?</t>
+        </is>
+      </c>
+      <c r="T90" s="136" t="inlineStr">
+        <is>
+          <t>ESRS S2 | Disclosure S2-2 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="130" customHeight="1" s="42">
+      <c r="A91" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S2: Workers in the Value Chain</t>
+        </is>
+      </c>
+      <c r="B91" s="122" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C91" s="122" t="inlineStr">
+        <is>
+          <t>Value Chain Workers</t>
+        </is>
+      </c>
+      <c r="D91" s="123" t="inlineStr">
+        <is>
+          <t>ESRS S2-3</t>
+        </is>
+      </c>
+      <c r="E91" s="122" t="inlineStr">
+        <is>
+          <t>Processes to Remediate Negative Impacts and Channels for Value Chain Workers to Raise Concerns</t>
+        </is>
+      </c>
+      <c r="F91" s="122" t="inlineStr">
+        <is>
+          <t>Disclose the processes for providing remedy and the grievance channels available to value chain workers to raise workplace concerns.</t>
+        </is>
+      </c>
+      <c r="G91" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (if material)</t>
+        </is>
+      </c>
+      <c r="H91" s="122" t="inlineStr">
+        <is>
+          <t>All entities with material impacts on value chain workers</t>
+        </is>
+      </c>
+      <c r="I91" s="122" t="inlineStr">
+        <is>
+          <t>Impact materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J91" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K91" s="122" t="inlineStr">
+        <is>
+          <t>Disclose: (a) description of the processes to remedy negative impacts the organization causes or contributes to in its value chain; (b) description of channels through which value chain workers can raise concerns (grievance mechanisms, hotlines, worker helplines, ombudspersons); (c) how the effectiveness of these processes is monitored; (d) number and nature of concerns raised and resolved.</t>
+        </is>
+      </c>
+      <c r="L91" s="124" t="inlineStr">
+        <is>
+          <t>• Grievance mechanism policy and procedure document
+• Worker helpline / hotline process description
+• Supplier corrective action plan (CAP) template and records
+• Remediation fund or compensation policy
+• Third-party ombudsperson or service provider contract
+• Grievance case log (anonymised)
+• Escalation matrix and escalation records
+• Communication materials about remedy channels (translated as needed)</t>
+        </is>
+      </c>
+      <c r="M91" s="125" t="inlineStr">
+        <is>
+          <t>• Grievance case records showing receipt, processing and closure
+• Corrective action plan completion records
+• Evidence of financial remediation provided (where applicable)
+• Worker access confirmation records (channel availability)
+• Independent effectiveness assessment of grievance mechanism
+• Year-on-year trend analysis of grievances by type</t>
+        </is>
+      </c>
+      <c r="N91" s="126" t="inlineStr">
+        <is>
+          <t>• Number of grievances received (value chain workers)
+• Number of grievances resolved within reporting period
+• Average resolution time (days)
+• Types of issues raised (wages, working hours, safety, harassment)
+• Number of corrective actions issued to suppliers
+• Percentage of corrective actions completed on time
+• Number of cases escalated to senior management or external authority</t>
+        </is>
+      </c>
+      <c r="O91" s="127" t="inlineStr">
+        <is>
+          <t>Resolution rate = Cases closed / Cases received × 100. Average resolution time = Sum of resolution days / Total cases resolved. Corrective action completion rate = CAPs closed on time / Total CAPs issued × 100. Track by grievance type for trend analysis.</t>
+        </is>
+      </c>
+      <c r="P91" s="122" t="inlineStr">
+        <is>
+          <t>Supply Chain / Human Rights / Sustainability / Compliance / ESG</t>
+        </is>
+      </c>
+      <c r="Q91" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R91" s="128" t="inlineStr">
+        <is>
+          <t>• Remedy channels must be accessible in languages of value chain workers
+• Zero retaliation policy must be in place and enforceable at supplier level
+• Assurers will test channel effectiveness (awareness, accessibility, trust)
+• Remedy processes must align with UNGP Pillar 3 effectiveness criteria
+• Cases involving forced or child labour require expedited escalation</t>
+        </is>
+      </c>
+      <c r="S91" s="129" t="inlineStr">
+        <is>
+          <t>• Are grievance channels translated and accessible to all worker groups in the value chain?
+• Is there a non-retaliation policy that extends to value chain workers?
+• Can the organization demonstrate that grievance outcomes include actual remediation?
+• Are case volumes and types trended year-on-year to identify systemic issues?</t>
+        </is>
+      </c>
+      <c r="T91" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S2 | Disclosure S2-3 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="130" customHeight="1" s="42">
+      <c r="A92" s="136" t="inlineStr">
+        <is>
+          <t>ESRS S2: Workers in the Value Chain</t>
+        </is>
+      </c>
+      <c r="B92" s="136" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C92" s="136" t="inlineStr">
+        <is>
+          <t>Value Chain Workers</t>
+        </is>
+      </c>
+      <c r="D92" s="137" t="inlineStr">
+        <is>
+          <t>ESRS S2-4</t>
+        </is>
+      </c>
+      <c r="E92" s="136" t="inlineStr">
+        <is>
+          <t>Taking Action on Material Impacts on Value Chain Workers, and Approaches to Managing Material Risks and Opportunities</t>
+        </is>
+      </c>
+      <c r="F92" s="136" t="inlineStr">
+        <is>
+          <t>Disclose the actions taken or planned to address material negative impacts on value chain workers and to manage material risks and opportunities.</t>
+        </is>
+      </c>
+      <c r="G92" s="136" t="inlineStr">
+        <is>
+          <t>Mandatory (if material)</t>
+        </is>
+      </c>
+      <c r="H92" s="136" t="inlineStr">
+        <is>
+          <t>All entities with material negative impacts on value chain workers</t>
+        </is>
+      </c>
+      <c r="I92" s="136" t="inlineStr">
+        <is>
+          <t>Impact materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J92" s="136" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K92" s="136" t="inlineStr">
+        <is>
+          <t>Disclose: (a) actions taken or planned during the reporting period to address material negative impacts and prevent recurrence; (b) whether actions are corrective or preventive; (c) how the organization tracks progress and effectiveness of actions; (d) actions that address root causes of adverse impacts; (e) collaboration with industry peers, governments, or civil society where applicable.</t>
+        </is>
+      </c>
+      <c r="L92" s="124" t="inlineStr">
+        <is>
+          <t>• Supplier improvement programme documentation
+• Corrective and preventive action plans (CAPAs)
+• Root cause analysis records for significant incidents
+• Training programmes for suppliers on labour standards
+• Supplier capacity building records
+• Industry collaboration initiative documentation (e.g. Better Work, RSPO)
+• KPI tracking dashboards for supply chain labour standards
+• Third-party monitoring and verification reports</t>
+        </is>
+      </c>
+      <c r="M92" s="125" t="inlineStr">
+        <is>
+          <t>• Evidence of actions completed (vs. planned)
+• Pre/post audit scores for suppliers where actions were applied
+• Number of workers benefiting from improvement programmes
+• External verification of improvement outcomes
+• Industry body or multi-stakeholder initiative reports
+• Recurrence rate for previously remediated issues</t>
+        </is>
+      </c>
+      <c r="N92" s="126" t="inlineStr">
+        <is>
+          <t>• Number of supplier corrective actions issued
+• Number of corrective actions completed
+• Percentage improvement in supplier labour audit scores year-on-year (%)
+• Number of workers benefiting from capacity building programmes
+• Number of suppliers terminated for labour non-compliance
+• Number of root cause analyses conducted for significant incidents
+• Investment in supplier improvement programmes ($)</t>
+        </is>
+      </c>
+      <c r="O92" s="127" t="inlineStr">
+        <is>
+          <t>Corrective action completion rate = CAPAs closed / Total CAPAs issued × 100. Improvement rate = (Current audit score − Prior score) / Prior score × 100 (per supplier). Recurrence rate = Re-opened issues / Total resolved issues × 100.</t>
+        </is>
+      </c>
+      <c r="P92" s="136" t="inlineStr">
+        <is>
+          <t>Supply Chain / Procurement / Sustainability / Human Rights / ESG</t>
+        </is>
+      </c>
+      <c r="Q92" s="136" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R92" s="128" t="inlineStr">
+        <is>
+          <t>• Assurers distinguish between plans and completed actions — evidence of execution is critical
+• Actions must address root causes, not just symptoms
+• Supplier capacity building is viewed positively vs. pure enforcement
+• Industry collaboration and multi-stakeholder initiatives should be named and described
+• Effectiveness of actions requires measurable KPIs with baseline comparison</t>
+        </is>
+      </c>
+      <c r="S92" s="129" t="inlineStr">
+        <is>
+          <t>• Is there evidence that planned actions have been implemented (not just intended)?
+• Are root causes of labour impacts identified and addressed systematically?
+• Are improvement programmes tracked with measurable outcomes?
+• How does the organization handle suppliers who fail to remediate?</t>
+        </is>
+      </c>
+      <c r="T92" s="136" t="inlineStr">
+        <is>
+          <t>ESRS S2 | Disclosure S2-4 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="130" customHeight="1" s="42">
+      <c r="A93" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S2: Workers in the Value Chain</t>
+        </is>
+      </c>
+      <c r="B93" s="122" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C93" s="122" t="inlineStr">
+        <is>
+          <t>Value Chain Workers</t>
+        </is>
+      </c>
+      <c r="D93" s="123" t="inlineStr">
+        <is>
+          <t>ESRS S2-5</t>
+        </is>
+      </c>
+      <c r="E93" s="122" t="inlineStr">
+        <is>
+          <t>Targets Related to Managing Material Negative Impacts, Advancing Positive Impacts, and Managing Material Risks and Opportunities</t>
+        </is>
+      </c>
+      <c r="F93" s="122" t="inlineStr">
+        <is>
+          <t>Disclose measurable targets related to value chain worker impacts and the progress made against those targets.</t>
+        </is>
+      </c>
+      <c r="G93" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (if material, where targets set)</t>
+        </is>
+      </c>
+      <c r="H93" s="122" t="inlineStr">
+        <is>
+          <t>Entities that have set targets related to value chain workers</t>
+        </is>
+      </c>
+      <c r="I93" s="122" t="inlineStr">
+        <is>
+          <t>Impact and financial materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J93" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K93" s="122" t="inlineStr">
+        <is>
+          <t>Disclose: (a) time-bound and measurable targets related to reducing negative impacts on value chain workers or advancing positive impacts; (b) baseline value and target year; (c) progress made during the reporting period; (d) whether targets have been revised and why.</t>
+        </is>
+      </c>
+      <c r="L93" s="124" t="inlineStr">
+        <is>
+          <t>• Target-setting methodology document
+• Baseline data records for each target
+• Annual progress review reports
+• KPI tracking system outputs
+• Board or senior management approval of targets
+• External benchmark or commitment references (e.g. ILO, UN SDG targets)
+• Historical trend data supporting baseline
+• Target revision log (if applicable)</t>
+        </is>
+      </c>
+      <c r="M93" s="125" t="inlineStr">
+        <is>
+          <t>• Progress reports against each target with baseline comparisons
+• Data sources and measurement methodology per target
+• Management sign-off on progress data
+• External assurance on target metrics (if applicable)
+• Evidence of board review of target progress</t>
+        </is>
+      </c>
+      <c r="N93" s="126" t="inlineStr">
+        <is>
+          <t>• Number and description of targets set
+• Baseline year and value for each target
+• Target year for each commitment
+• Actual performance in reporting period vs. target
+• Number of targets achieved, on track, or behind schedule
+• Percentage improvement vs. baseline
+• Targets covering supplier audit scores, grievance resolution, living wage coverage</t>
+        </is>
+      </c>
+      <c r="O93" s="127" t="inlineStr">
+        <is>
+          <t>Progress % = (Current value − Baseline) / (Target − Baseline) × 100. Track each target independently with its own formula. Aggregate dashboard can show RAG (Red/Amber/Green) status per target. Where targets are qualitative (e.g. 'implement programme'), milestones serve as proxy metrics.</t>
+        </is>
+      </c>
+      <c r="P93" s="122" t="inlineStr">
+        <is>
+          <t>Sustainability / ESG / Supply Chain / Human Rights</t>
+        </is>
+      </c>
+      <c r="Q93" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R93" s="128" t="inlineStr">
+        <is>
+          <t>• Targets must be SMART (Specific, Measurable, Achievable, Relevant, Time-bound)
+• Baseline must be documented and verifiable
+• Assurers will check for cherry-picking of easy-to-achieve metrics
+• Revised targets require explanation — assurers will scrutinise downward revisions
+• Targets should align to international frameworks (SDGs, UNGP, ILO)</t>
+        </is>
+      </c>
+      <c r="S93" s="129" t="inlineStr">
+        <is>
+          <t>• Are all targets time-bound with a documented baseline?
+• Is progress against targets tracked with a consistent and auditable methodology?
+• Have any targets been revised, and if so, is the rationale documented?
+• Do targets cover the most material worker impact areas?</t>
+        </is>
+      </c>
+      <c r="T93" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S2 | Disclosure S2-5 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="130" customHeight="1" s="42">
+      <c r="A94" s="136" t="inlineStr">
+        <is>
+          <t>ESRS S2: Workers in the Value Chain</t>
+        </is>
+      </c>
+      <c r="B94" s="136" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C94" s="136" t="inlineStr">
+        <is>
+          <t>Value Chain Workers</t>
+        </is>
+      </c>
+      <c r="D94" s="137" t="inlineStr">
+        <is>
+          <t>ESRS S2-6</t>
+        </is>
+      </c>
+      <c r="E94" s="136" t="inlineStr">
+        <is>
+          <t>Characteristics of the Value Chain Workers in the Scope of the Disclosure</t>
+        </is>
+      </c>
+      <c r="F94" s="136" t="inlineStr">
+        <is>
+          <t>Disclose key characteristics of the workers in the value chain that are within scope, including categories and geographic distribution.</t>
+        </is>
+      </c>
+      <c r="G94" s="136" t="inlineStr">
+        <is>
+          <t>Mandatory (if material)</t>
+        </is>
+      </c>
+      <c r="H94" s="136" t="inlineStr">
+        <is>
+          <t>All entities reporting under S2 where value chain workers are material</t>
+        </is>
+      </c>
+      <c r="I94" s="136" t="inlineStr">
+        <is>
+          <t>Impact materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J94" s="136" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K94" s="136" t="inlineStr">
+        <is>
+          <t>Disclose: (a) characteristics of value chain workers most at risk or in scope of material impacts — including categories (e.g. agricultural workers, factory workers, homeworkers, migrant workers), geographic presence, and types of work arrangements; (b) the most significant concentration of at-risk workers; (c) the basis for identifying which categories are in scope.</t>
+        </is>
+      </c>
+      <c r="L94" s="124" t="inlineStr">
+        <is>
+          <t>• Value chain mapping and supplier tier analysis
+• Supplier register with geographic and sector data
+• At-risk worker category identification methodology
+• Human rights impact assessment (HRIA) scoping documents
+• Social audit results by worker category
+• Migrant worker identification and monitoring records
+• Saliency assessment documentation
+• ILO sector risk assessments or country risk ratings used</t>
+        </is>
+      </c>
+      <c r="M94" s="125" t="inlineStr">
+        <is>
+          <t>• Supplier mapping showing worker populations by category and location
+• HRIA or saliency assessment identifying highest-risk worker groups
+• Social audit data segmented by worker type
+• Country risk rating methodology used to prioritise scope
+• External benchmarks (e.g. Global Slavery Index) used in analysis</t>
+        </is>
+      </c>
+      <c r="N94" s="126" t="inlineStr">
+        <is>
+          <t>• Total number of workers in scope (estimated)
+• Categories of workers included (by type of work, employment status)
+• Geographic concentration of at-risk workers (top 5 countries)
+• Percentage of procurement spend in high-risk geographies (%)
+• Number of worker categories assessed for salient risks
+• Basis for scope determination (tier coverage, spend threshold, risk criteria)
+• Key sectors identified as material (agriculture, garments, electronics, etc.)</t>
+        </is>
+      </c>
+      <c r="O94" s="127" t="inlineStr">
+        <is>
+          <t>No single formula — qualitative and quantitative characterisation required. Spend in high-risk geographies % = Spend in high-risk countries / Total procurement spend × 100. Worker population estimates may be based on supplier data or sector averages where direct data is unavailable.</t>
+        </is>
+      </c>
+      <c r="P94" s="136" t="inlineStr">
+        <is>
+          <t>Supply Chain / Sustainability / Procurement / Human Rights / ESG</t>
+        </is>
+      </c>
+      <c r="Q94" s="136" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R94" s="128" t="inlineStr">
+        <is>
+          <t>• Scope must be justified — assurers check if the most salient risks are included
+• Worker categories should reflect actual supply chain structure, not generic templates
+• Geographic concentration risk should align with country-level human rights risk data
+• Estimates of worker populations must disclose methodology and uncertainty
+• Scope should evolve as supply chain mapping deepens year-on-year</t>
+        </is>
+      </c>
+      <c r="S94" s="129" t="inlineStr">
+        <is>
+          <t>• Is the scope of value chain workers identified through a structured saliency or risk assessment?
+• Are the most at-risk worker categories (e.g. migrant, informal, seasonal) explicitly included?
+• Is the geographic scope aligned to human rights country risk data?
+• Does the estimated worker population cover both tier-1 and deeper supply chain tiers?</t>
+        </is>
+      </c>
+      <c r="T94" s="136" t="inlineStr">
+        <is>
+          <t>ESRS S2 | Disclosure S2-6 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="8" customHeight="1" s="42"/>
+    <row r="96" ht="22" customHeight="1" s="42">
+      <c r="A96" s="135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ESRS S3 — Affected Communities</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="130" customHeight="1" s="42">
+      <c r="A97" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S3: Affected Communities</t>
+        </is>
+      </c>
+      <c r="B97" s="122" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C97" s="122" t="inlineStr">
+        <is>
+          <t>Affected Communities</t>
+        </is>
+      </c>
+      <c r="D97" s="123" t="inlineStr">
+        <is>
+          <t>ESRS S3-1</t>
+        </is>
+      </c>
+      <c r="E97" s="122" t="inlineStr">
+        <is>
+          <t>Policies Related to Affected Communities</t>
+        </is>
+      </c>
+      <c r="F97" s="122" t="inlineStr">
+        <is>
+          <t>Disclose the policies adopted to manage material impacts on communities affected by the organization's activities.</t>
+        </is>
+      </c>
+      <c r="G97" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (if material)</t>
+        </is>
+      </c>
+      <c r="H97" s="122" t="inlineStr">
+        <is>
+          <t>All entities in scope of CSRD where affected communities are material</t>
+        </is>
+      </c>
+      <c r="I97" s="122" t="inlineStr">
+        <is>
+          <t>Impact materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J97" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K97" s="122" t="inlineStr">
+        <is>
+          <t>Disclose: (a) policies addressing material impacts on communities affected by the organization's operations; (b) whether the policies address free, prior and informed consent (FPIC) for indigenous peoples; (c) whether land rights, displacement, and cultural heritage are addressed; (d) how community policies relate to other human rights and environmental policies.</t>
+        </is>
+      </c>
+      <c r="L97" s="124" t="inlineStr">
+        <is>
+          <t>• Community engagement and social licence policy
+• Human rights policy (community rights component)
+• Indigenous peoples rights and FPIC policy
+• Land acquisition and resettlement policy
+• Cultural heritage protection policy
+• Environmental and social impact assessment (ESIA) policy
+• Grievance mechanism policy (community-facing)
+• Local procurement and benefit-sharing policy
+• Board approval documentation for community policies</t>
+        </is>
+      </c>
+      <c r="M97" s="125" t="inlineStr">
+        <is>
+          <t>• Policy documents with approval dates and senior sign-off
+• Evidence of FPIC process documentation (where indigenous peoples present)
+• Legal compliance records for community rights obligations
+• ESIA approval documentation from regulators
+• Community agreement or social licence documentation
+• External assessment of policy adequacy vs. IFC Performance Standards or UNGP</t>
+        </is>
+      </c>
+      <c r="N97" s="126" t="inlineStr">
+        <is>
+          <t>• Number of community impact policies in place
+• Whether FPIC policy exists (yes/no) and scope of application
+• Scope of communities covered (local, indigenous, downstream)
+• Whether policies address all material impact areas identified in ESRS 3
+• Policy review frequency and last review date
+• International standards referenced (UNGP, IFC PS, ILO 169)</t>
+        </is>
+      </c>
+      <c r="O97" s="127" t="inlineStr">
+        <is>
+          <t>Policy completeness assessment against ESRS S3 requirements is qualitative. Policy coverage % = Community impact areas covered by policy / Total identified material impact areas × 100. No prescribed quantitative formula — narrative with structured checklist.</t>
+        </is>
+      </c>
+      <c r="P97" s="122" t="inlineStr">
+        <is>
+          <t>Sustainability / Community Affairs / Legal / Human Rights / ESG</t>
+        </is>
+      </c>
+      <c r="Q97" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R97" s="128" t="inlineStr">
+        <is>
+          <t>• Policies must be publicly accessible or explain why access is restricted
+• FPIC policy is essential where indigenous peoples are among affected communities
+• Assurers check alignment between stated policy and field-level practice
+• Policy scope must match identified material community impacts
+• Land and resettlement policies are high-risk — require particularly strong evidence</t>
+        </is>
+      </c>
+      <c r="S97" s="129" t="inlineStr">
+        <is>
+          <t>• Does the community policy explicitly cover indigenous peoples and FPIC requirements?
+• Are land rights, displacement and cultural heritage addressed in policy?
+• Are policies communicated to affected communities in accessible language?
+• Is there documented evidence of policy implementation at operational sites?</t>
+        </is>
+      </c>
+      <c r="T97" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S3 | Disclosure S3-1 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="130" customHeight="1" s="42">
+      <c r="A98" s="136" t="inlineStr">
+        <is>
+          <t>ESRS S3: Affected Communities</t>
+        </is>
+      </c>
+      <c r="B98" s="136" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C98" s="136" t="inlineStr">
+        <is>
+          <t>Affected Communities</t>
+        </is>
+      </c>
+      <c r="D98" s="137" t="inlineStr">
+        <is>
+          <t>ESRS S3-2</t>
+        </is>
+      </c>
+      <c r="E98" s="136" t="inlineStr">
+        <is>
+          <t>Processes for Engaging with Affected Communities about Impacts</t>
+        </is>
+      </c>
+      <c r="F98" s="136" t="inlineStr">
+        <is>
+          <t>Disclose the processes used to engage with affected communities to understand and address impacts on them.</t>
+        </is>
+      </c>
+      <c r="G98" s="136" t="inlineStr">
+        <is>
+          <t>Mandatory (if material)</t>
+        </is>
+      </c>
+      <c r="H98" s="136" t="inlineStr">
+        <is>
+          <t>All entities with material impacts on local or affected communities</t>
+        </is>
+      </c>
+      <c r="I98" s="136" t="inlineStr">
+        <is>
+          <t>Impact materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J98" s="136" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K98" s="136" t="inlineStr">
+        <is>
+          <t>Disclose: (a) whether and how the organization engages with affected communities about material impacts; (b) methods and frequency of engagement (consultation, community liaison, FPIC); (c) how engagement outputs influence decisions; (d) barriers to effective community engagement and how they are addressed.</t>
+        </is>
+      </c>
+      <c r="L98" s="124" t="inlineStr">
+        <is>
+          <t>• Community liaison programme documentation
+• Community consultation and engagement plans
+• Stakeholder engagement registers (community-specific)
+• FPIC documentation (where indigenous peoples affected)
+• Community meetings records and minutes
+• Social baseline studies
+• Community development committee records
+• Environmental and social impact assessment consultation records
+• Grievance log (community-raised issues)</t>
+        </is>
+      </c>
+      <c r="M98" s="125" t="inlineStr">
+        <is>
+          <t>• Consultation records showing community participation
+• Meeting minutes signed by community representatives
+• FPIC process documentation including consent records
+• Evidence that engagement outcomes influenced decisions
+• Social audit reports with community feedback
+• Number of engagement events and participant counts</t>
+        </is>
+      </c>
+      <c r="N98" s="126" t="inlineStr">
+        <is>
+          <t>• Number of community engagement events held
+• Number of communities engaged (distinct communities)
+• Number of community members participating in engagement
+• Types of engagement methods (consultation, co-design, advisory panels)
+• Percentage of operational sites with active community engagement plans
+• Number of community concerns raised through engagement
+• Actions taken in response to community engagement</t>
+        </is>
+      </c>
+      <c r="O98" s="127" t="inlineStr">
+        <is>
+          <t>Engagement coverage % = Sites with active engagement plan / Total operational sites × 100. Participation rate = Community members engaged / Total affected community population (estimated) × 100. Response rate = Actions taken on community concerns / Total concerns raised × 100.</t>
+        </is>
+      </c>
+      <c r="P98" s="136" t="inlineStr">
+        <is>
+          <t>Community Affairs / Sustainability / Operations / Human Rights / ESG</t>
+        </is>
+      </c>
+      <c r="Q98" s="136" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R98" s="128" t="inlineStr">
+        <is>
+          <t>• Assurers distinguish genuine two-way engagement from one-way information provision
+• FPIC requires free, prior and informed consent — all three elements must be evidenced
+• Engagement plans must be tailored to community context (language, gender, vulnerability)
+• Evidence must show engagement influenced decisions, not just occurred
+• Barriers to participation (transport, trust, language) must be acknowledged and addressed</t>
+        </is>
+      </c>
+      <c r="S98" s="129" t="inlineStr">
+        <is>
+          <t>• Are engagement processes designed with and for affected communities, or imposed?
+• Is there documented evidence that community input has influenced operational decisions?
+• Are vulnerable groups (women, youth, indigenous peoples) adequately represented?
+• Are engagement processes conducted in local languages?</t>
+        </is>
+      </c>
+      <c r="T98" s="136" t="inlineStr">
+        <is>
+          <t>ESRS S3 | Disclosure S3-2 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="130" customHeight="1" s="42">
+      <c r="A99" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S3: Affected Communities</t>
+        </is>
+      </c>
+      <c r="B99" s="122" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C99" s="122" t="inlineStr">
+        <is>
+          <t>Affected Communities</t>
+        </is>
+      </c>
+      <c r="D99" s="123" t="inlineStr">
+        <is>
+          <t>ESRS S3-3</t>
+        </is>
+      </c>
+      <c r="E99" s="122" t="inlineStr">
+        <is>
+          <t>Processes to Remediate Negative Impacts and Channels for Affected Communities to Raise Concerns</t>
+        </is>
+      </c>
+      <c r="F99" s="122" t="inlineStr">
+        <is>
+          <t>Disclose the grievance and remedy processes available to communities affected by the organization's operations.</t>
+        </is>
+      </c>
+      <c r="G99" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (if material)</t>
+        </is>
+      </c>
+      <c r="H99" s="122" t="inlineStr">
+        <is>
+          <t>All entities with material negative impacts on affected communities</t>
+        </is>
+      </c>
+      <c r="I99" s="122" t="inlineStr">
+        <is>
+          <t>Impact materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J99" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K99" s="122" t="inlineStr">
+        <is>
+          <t>Disclose: (a) processes to remediate negative impacts the organization has caused or contributed to; (b) grievance channels available to affected communities; (c) effectiveness monitoring of remedy processes; (d) number and nature of community concerns raised and resolved.</t>
+        </is>
+      </c>
+      <c r="L99" s="124" t="inlineStr">
+        <is>
+          <t>• Community grievance mechanism procedure document
+• Complaint registration and tracking system description
+• Corrective action and remedy process documentation
+• Community liaison officer (CLO) terms of reference
+• Third-party ombudsperson or mediator arrangements
+• Resettlement and compensation framework
+• Environmental incident response and community notification process
+• Annual grievance reporting to community stakeholders</t>
+        </is>
+      </c>
+      <c r="M99" s="125" t="inlineStr">
+        <is>
+          <t>• Grievance case records (anonymised) showing receipt and resolution
+• Evidence of compensation or remediation provided
+• Community satisfaction surveys post-resolution
+• Independent assessment of grievance mechanism effectiveness
+• Regulatory compliance records for community notification obligations
+• Year-on-year trend data on grievance volumes and types</t>
+        </is>
+      </c>
+      <c r="N99" s="126" t="inlineStr">
+        <is>
+          <t>• Number of community grievances received during reporting period
+• Number of grievances resolved within reporting period
+• Average grievance resolution time (days)
+• Types of community concerns (environmental, livelihood, land, health)
+• Number of escalated cases (to government, court, or external mediator)
+• Compensation paid to communities ($)
+• Grievance recurrence rate (%)</t>
+        </is>
+      </c>
+      <c r="O99" s="127" t="inlineStr">
+        <is>
+          <t>Resolution rate = Grievances resolved / Grievances received × 100. Average resolution time = Sum of resolution days / Cases resolved. Compensation amount directly reported. Recurrence rate = Issues re-raised after closure / Total closed issues × 100.</t>
+        </is>
+      </c>
+      <c r="P99" s="122" t="inlineStr">
+        <is>
+          <t>Community Affairs / Legal / Sustainability / Operations / Human Rights</t>
+        </is>
+      </c>
+      <c r="Q99" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R99" s="128" t="inlineStr">
+        <is>
+          <t>• UNGP Pillar 3 effectiveness criteria: legitimate, accessible, predictable, equitable, transparent, rights-compatible
+• Community grievance mechanisms must be independent from company control
+• Non-retaliation protections for complainants must be documented and enforced
+• Assurers will test whether communities know about and trust the mechanism
+• High-risk categories (land disputes, displacement, health impacts) require heightened attention</t>
+        </is>
+      </c>
+      <c r="S99" s="129" t="inlineStr">
+        <is>
+          <t>• Are grievance mechanisms independently managed or controlled by company operations staff?
+• Is there a documented non-retaliation policy for community complainants?
+• Can the organization show evidence of actual remediation (not just acknowledgement)?
+• Are grievance trends analysed to identify and address systemic issues?</t>
+        </is>
+      </c>
+      <c r="T99" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S3 | Disclosure S3-3 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="130" customHeight="1" s="42">
+      <c r="A100" s="136" t="inlineStr">
+        <is>
+          <t>ESRS S3: Affected Communities</t>
+        </is>
+      </c>
+      <c r="B100" s="136" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C100" s="136" t="inlineStr">
+        <is>
+          <t>Affected Communities</t>
+        </is>
+      </c>
+      <c r="D100" s="137" t="inlineStr">
+        <is>
+          <t>ESRS S3-4</t>
+        </is>
+      </c>
+      <c r="E100" s="136" t="inlineStr">
+        <is>
+          <t>Taking Action on Material Impacts on Affected Communities, and Approaches to Managing Material Risks and Opportunities</t>
+        </is>
+      </c>
+      <c r="F100" s="136" t="inlineStr">
+        <is>
+          <t>Disclose actions taken to prevent, mitigate or remediate material negative impacts on affected communities and to realise positive impacts.</t>
+        </is>
+      </c>
+      <c r="G100" s="136" t="inlineStr">
+        <is>
+          <t>Mandatory (if material)</t>
+        </is>
+      </c>
+      <c r="H100" s="136" t="inlineStr">
+        <is>
+          <t>All entities with material community impacts requiring active management</t>
+        </is>
+      </c>
+      <c r="I100" s="136" t="inlineStr">
+        <is>
+          <t>Impact materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J100" s="136" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K100" s="136" t="inlineStr">
+        <is>
+          <t>Disclose: (a) actions taken or planned to prevent, mitigate and remediate negative impacts on communities and to advance positive contributions; (b) whether actions are preventive, mitigative or remedial; (c) how the organization tracks effectiveness of actions; (d) scale and scope of actions; (e) alignment with international standards (IFC Performance Standards, UNGP).</t>
+        </is>
+      </c>
+      <c r="L100" s="124" t="inlineStr">
+        <is>
+          <t>• Community investment and social licence programme records
+• Environmental mitigation measure records (for community-affecting impacts)
+• Resettlement action plans (RAPs) and progress reports
+• Livelihood restoration programme documentation
+• Community infrastructure investments
+• Health and safety programmes for local communities
+• Partnership agreements with local NGOs or government
+• Corporate social investment (CSI) project records</t>
+        </is>
+      </c>
+      <c r="M100" s="125" t="inlineStr">
+        <is>
+          <t>• Evidence of actions completed vs. planned with timelines
+• Community impact measurements (before and after)
+• RAP or resettlement outcomes for displaced communities
+• Community satisfaction data
+• Third-party evaluation of community programmes
+• Number of beneficiaries of community investment programmes</t>
+        </is>
+      </c>
+      <c r="N100" s="126" t="inlineStr">
+        <is>
+          <t>• Total community investment ($) in reporting period
+• Number of communities receiving direct investment
+• Estimated number of community members benefiting
+• Number of resettlement or livelihood restoration cases completed
+• Number of community actions completed vs. planned
+• Investment as % of EBITDA or revenue
+• Effectiveness metrics per programme (health outcomes, income, education)</t>
+        </is>
+      </c>
+      <c r="O100" s="127" t="inlineStr">
+        <is>
+          <t>Community investment % = Community investment spend / Revenue × 100. Livelihood restoration: compare household income pre/post project against baseline. Cost-benefit of mitigation: avoided impact costs vs. mitigation investment. Number of beneficiaries is direct count from programme records.</t>
+        </is>
+      </c>
+      <c r="P100" s="136" t="inlineStr">
+        <is>
+          <t>Community Affairs / Sustainability / Operations / Government Relations / Finance</t>
+        </is>
+      </c>
+      <c r="Q100" s="136" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R100" s="128" t="inlineStr">
+        <is>
+          <t>• Actions must be demonstrably linked to identified material impacts
+• Community investment that is not linked to impact management is philanthropic — distinguish clearly
+• RAP implementation quality is a major assurance focus for extractive/infrastructure companies
+• Scale and scope must be proportionate to the severity of the impact
+• Assurers look for evidence of community co-design in programme development</t>
+        </is>
+      </c>
+      <c r="S100" s="129" t="inlineStr">
+        <is>
+          <t>• Are actions directly linked to identified material impacts on communities?
+• Is there a distinction between impact mitigation and general philanthropy?
+• Are resettlement action plans independently monitored and verified?
+• Do affected communities have meaningful input into the design of actions?</t>
+        </is>
+      </c>
+      <c r="T100" s="136" t="inlineStr">
+        <is>
+          <t>ESRS S3 | Disclosure S3-4 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="130" customHeight="1" s="42">
+      <c r="A101" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S3: Affected Communities</t>
+        </is>
+      </c>
+      <c r="B101" s="122" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C101" s="122" t="inlineStr">
+        <is>
+          <t>Affected Communities</t>
+        </is>
+      </c>
+      <c r="D101" s="123" t="inlineStr">
+        <is>
+          <t>ESRS S3-5</t>
+        </is>
+      </c>
+      <c r="E101" s="122" t="inlineStr">
+        <is>
+          <t>Targets Related to Managing Material Negative Impacts, Advancing Positive Impacts, and Managing Material Risks and Opportunities</t>
+        </is>
+      </c>
+      <c r="F101" s="122" t="inlineStr">
+        <is>
+          <t>Disclose time-bound, measurable targets related to managing impacts on affected communities.</t>
+        </is>
+      </c>
+      <c r="G101" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (if material, where targets are set)</t>
+        </is>
+      </c>
+      <c r="H101" s="122" t="inlineStr">
+        <is>
+          <t>Entities that have set community-related targets</t>
+        </is>
+      </c>
+      <c r="I101" s="122" t="inlineStr">
+        <is>
+          <t>Impact and financial materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J101" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K101" s="122" t="inlineStr">
+        <is>
+          <t>Disclose: (a) measurable, time-bound targets related to community impacts; (b) baseline values, target years, and progress made; (c) whether targets have been revised during the reporting period and reasons for revision; (d) alignment with international frameworks or commitments (e.g. ICMM 10 Principles, UN SDGs).</t>
+        </is>
+      </c>
+      <c r="L101" s="124" t="inlineStr">
+        <is>
+          <t>• Target-setting and governance documentation
+• Baseline data records for community impact metrics
+• Annual KPI tracking reports for community targets
+• Board or senior management approval of community targets
+• Benchmark data from industry peers or international standards
+• Historical trend data for baseline establishment
+• External commitments or pledges (SDG, ICMM, IFC) referenced in targets</t>
+        </is>
+      </c>
+      <c r="M101" s="125" t="inlineStr">
+        <is>
+          <t>• Progress tracking reports showing actual vs. target performance
+• Third-party verification of community target metrics
+• Board review minutes confirming target oversight
+• Explanation of target revisions (if any)
+• Beneficiary data supporting impact targets</t>
+        </is>
+      </c>
+      <c r="N101" s="126" t="inlineStr">
+        <is>
+          <t>• Number of community impact targets set
+• Baseline year and value for each target
+• Target value and year for each commitment
+• Actual performance in reporting period
+• Number of targets achieved, on track, or missed
+• Progress % towards target for each KPI
+• International framework alignment (SDG goals, ICMM principles)</t>
+        </is>
+      </c>
+      <c r="O101" s="127" t="inlineStr">
+        <is>
+          <t>Progress % = (Current value − Baseline) / (Target − Baseline) × 100. Where targets are qualitative milestones, track against milestone completion schedule. Aggregate target achievement rate = Targets achieved / Total targets × 100.</t>
+        </is>
+      </c>
+      <c r="P101" s="122" t="inlineStr">
+        <is>
+          <t>Sustainability / ESG / Community Affairs / Government Relations</t>
+        </is>
+      </c>
+      <c r="Q101" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R101" s="128" t="inlineStr">
+        <is>
+          <t>• Targets must be SMART with documented baselines
+• Assurers will test whether targets are ambitious or merely codify business as usual
+• Downward revisions must be explained transparently
+• Targets should cover the most material community impact areas
+• Community involvement in target-setting improves credibility and social licence</t>
+        </is>
+      </c>
+      <c r="S101" s="129" t="inlineStr">
+        <is>
+          <t>• Are community impact targets set with documented baselines and time horizons?
+• Do targets cover the most material impacts (land, health, livelihood, culture)?
+• Has the organization involved affected communities in setting targets?
+• Is progress against targets independently verified?</t>
+        </is>
+      </c>
+      <c r="T101" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S3 | Disclosure S3-5 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="8" customHeight="1" s="42"/>
+    <row r="103" ht="22" customHeight="1" s="42">
+      <c r="A103" s="135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ESRS S4 — Consumers and End-Users</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="130" customHeight="1" s="42">
+      <c r="A104" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S4: Consumers and End-Users</t>
+        </is>
+      </c>
+      <c r="B104" s="122" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C104" s="122" t="inlineStr">
+        <is>
+          <t>Consumers and End-Users</t>
+        </is>
+      </c>
+      <c r="D104" s="123" t="inlineStr">
+        <is>
+          <t>ESRS S4-1</t>
+        </is>
+      </c>
+      <c r="E104" s="122" t="inlineStr">
+        <is>
+          <t>Policies Related to Consumers and End-Users</t>
+        </is>
+      </c>
+      <c r="F104" s="122" t="inlineStr">
+        <is>
+          <t>Disclose the policies adopted to manage the organization's material impacts on consumers and end-users of its products and services.</t>
+        </is>
+      </c>
+      <c r="G104" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (if material)</t>
+        </is>
+      </c>
+      <c r="H104" s="122" t="inlineStr">
+        <is>
+          <t>All entities in scope of CSRD where consumer impacts are material</t>
+        </is>
+      </c>
+      <c r="I104" s="122" t="inlineStr">
+        <is>
+          <t>Impact materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J104" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K104" s="122" t="inlineStr">
+        <is>
+          <t>Disclose: (a) policies addressing the organization's material impacts on consumers and end-users; (b) whether policies address consumer health and safety, data protection, responsible marketing, and access to products/services; (c) how these policies align with legal requirements and international consumer protection standards.</t>
+        </is>
+      </c>
+      <c r="L104" s="124" t="inlineStr">
+        <is>
+          <t>• Consumer health and safety policy
+• Responsible marketing and advertising policy
+• Data privacy and data protection policy (GDPR aligned)
+• Product labelling and transparency policy
+• Customer complaints and redress policy
+• Vulnerable consumer policy (children, elderly, low-income)
+• Accessibility policy for products/services
+• Product liability and recall policy
+• Board approval records for consumer-related policies</t>
+        </is>
+      </c>
+      <c r="M104" s="125" t="inlineStr">
+        <is>
+          <t>• Policy documents with version history and senior approval
+• Regulatory compliance records (consumer protection laws, GDPR)
+• Marketing code compliance sign-off
+• Data protection impact assessments (DPIAs)
+• Product safety test records
+• Accessibility audit reports
+• Customer ombudsman service designation (where applicable)</t>
+        </is>
+      </c>
+      <c r="N104" s="126" t="inlineStr">
+        <is>
+          <t>• Number of consumer protection policies in place
+• Whether data protection policy is GDPR-compliant (yes/no)
+• Whether vulnerable consumer policy exists (yes/no)
+• Policy scope (geographic, product, channel coverage)
+• International standards referenced (OECD Consumer Guidelines, ISO 31000)
+• Policy review frequency and last update date
+• Number of regulatory consumer protection obligations addressed by policies</t>
+        </is>
+      </c>
+      <c r="O104" s="127" t="inlineStr">
+        <is>
+          <t>Policy completeness is qualitative. Coverage % = Consumer impact areas with policy / Total material consumer impact areas × 100. Regulatory compliance rate = Consumer protection regulatory requirements met / Total applicable requirements × 100.</t>
+        </is>
+      </c>
+      <c r="P104" s="122" t="inlineStr">
+        <is>
+          <t>Marketing / Legal / Data Privacy / Product / Sustainability / ESG</t>
+        </is>
+      </c>
+      <c r="Q104" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R104" s="128" t="inlineStr">
+        <is>
+          <t>• Policies must align with applicable consumer protection laws in all operating jurisdictions
+• GDPR and data privacy policies are an assurance focus for all digital businesses
+• Responsible marketing policies must address both content and targeting practices
+• Vulnerable consumer provisions are increasingly scrutinised by regulators and assurers
+• Policy gaps vs. identified material consumer impacts must be explicitly acknowledged</t>
+        </is>
+      </c>
+      <c r="S104" s="129" t="inlineStr">
+        <is>
+          <t>• Do consumer policies address all identified material impacts (safety, data, marketing, access)?
+• Are there specific provisions for vulnerable consumer groups?
+• Are policies aligned with all applicable consumer protection legislation?
+• Are consumer-facing policies publicly available and clearly communicated?</t>
+        </is>
+      </c>
+      <c r="T104" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S4 | Disclosure S4-1 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="130" customHeight="1" s="42">
+      <c r="A105" s="136" t="inlineStr">
+        <is>
+          <t>ESRS S4: Consumers and End-Users</t>
+        </is>
+      </c>
+      <c r="B105" s="136" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C105" s="136" t="inlineStr">
+        <is>
+          <t>Consumers and End-Users</t>
+        </is>
+      </c>
+      <c r="D105" s="137" t="inlineStr">
+        <is>
+          <t>ESRS S4-2</t>
+        </is>
+      </c>
+      <c r="E105" s="136" t="inlineStr">
+        <is>
+          <t>Processes for Engaging with Consumers and End-Users about Impacts</t>
+        </is>
+      </c>
+      <c r="F105" s="136" t="inlineStr">
+        <is>
+          <t>Disclose the processes through which the organization engages with consumers and end-users to understand and manage material impacts on them.</t>
+        </is>
+      </c>
+      <c r="G105" s="136" t="inlineStr">
+        <is>
+          <t>Mandatory (if material)</t>
+        </is>
+      </c>
+      <c r="H105" s="136" t="inlineStr">
+        <is>
+          <t>All entities with material consumer impacts requiring engagement</t>
+        </is>
+      </c>
+      <c r="I105" s="136" t="inlineStr">
+        <is>
+          <t>Impact materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J105" s="136" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K105" s="136" t="inlineStr">
+        <is>
+          <t>Disclose: (a) whether and how the organization engages with consumers and end-users on material impacts; (b) types of engagement (surveys, focus groups, consumer panels, digital feedback); (c) how consumer insights influence product development, marketing, and service delivery; (d) whether consumers can access information needed to make informed choices.</t>
+        </is>
+      </c>
+      <c r="L105" s="124" t="inlineStr">
+        <is>
+          <t>• Customer satisfaction survey methodology and results
+• Consumer research and focus group records
+• Consumer advisory panel terms of reference and minutes
+• Product feedback mechanism documentation
+• Digital engagement data (app ratings, reviews, complaints portal)
+• Consumer disclosure/labelling audit records
+• Annual consumer NPS or CSAT benchmarking reports
+• Consumer co-creation programme records</t>
+        </is>
+      </c>
+      <c r="M105" s="125" t="inlineStr">
+        <is>
+          <t>• Survey results with statistical significance data
+• Evidence that consumer feedback influenced product or policy changes
+• Consumer panel participation records
+• Digital feedback volume and resolution rates
+• Third-party consumer satisfaction benchmarks
+• Year-on-year trend in consumer complaint volumes and types</t>
+        </is>
+      </c>
+      <c r="N105" s="126" t="inlineStr">
+        <is>
+          <t>• Number of consumer engagement events/surveys conducted
+• Number of consumers engaged (respondents, panel members)
+• Net Promoter Score (NPS) or CSAT score
+• Consumer complaint volume by category
+• Percentage of consumer complaints resolved within SLA
+• Number of product changes made in response to consumer feedback
+• Consumer disclosure completeness score (labelling audit outcome)</t>
+        </is>
+      </c>
+      <c r="O105" s="127" t="inlineStr">
+        <is>
+          <t>NPS = % Promoters − % Detractors. CSAT = Satisfied respondents / Total respondents × 100. Complaint resolution rate = Complaints resolved within SLA / Total complaints × 100. Consumer feedback to action rate = Product changes driven by consumer insight / Total product changes × 100.</t>
+        </is>
+      </c>
+      <c r="P105" s="136" t="inlineStr">
+        <is>
+          <t>Marketing / Customer Experience / Product / Legal / Sustainability</t>
+        </is>
+      </c>
+      <c r="Q105" s="136" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R105" s="128" t="inlineStr">
+        <is>
+          <t>• Assurers distinguish between genuine consumer insight processes and compliance-only disclosure
+• Consumer engagement must extend beyond satisfied customers to capture complaint patterns
+• Engagement with vulnerable consumers (children, elderly, disabled) requires special care
+• Evidence that engagement outputs influence decisions is critical
+• Data from engagement must be aggregated and representative, not cherry-picked</t>
+        </is>
+      </c>
+      <c r="S105" s="129" t="inlineStr">
+        <is>
+          <t>• Is consumer engagement structured to capture diverse perspectives, not just satisfied customers?
+• Is there documented evidence that consumer insights have driven product or policy changes?
+• Are vulnerable consumer groups specifically included in engagement processes?
+• Are consumer engagement processes compliant with data protection regulations?</t>
+        </is>
+      </c>
+      <c r="T105" s="136" t="inlineStr">
+        <is>
+          <t>ESRS S4 | Disclosure S4-2 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="130" customHeight="1" s="42">
+      <c r="A106" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S4: Consumers and End-Users</t>
+        </is>
+      </c>
+      <c r="B106" s="122" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C106" s="122" t="inlineStr">
+        <is>
+          <t>Consumers and End-Users</t>
+        </is>
+      </c>
+      <c r="D106" s="123" t="inlineStr">
+        <is>
+          <t>ESRS S4-3</t>
+        </is>
+      </c>
+      <c r="E106" s="122" t="inlineStr">
+        <is>
+          <t>Processes to Remediate Negative Impacts and Channels for Consumers and End-Users to Raise Concerns</t>
+        </is>
+      </c>
+      <c r="F106" s="122" t="inlineStr">
+        <is>
+          <t>Disclose the grievance and remedy processes available to consumers to raise concerns about negative impacts.</t>
+        </is>
+      </c>
+      <c r="G106" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (if material)</t>
+        </is>
+      </c>
+      <c r="H106" s="122" t="inlineStr">
+        <is>
+          <t>All entities with material negative impacts on consumers</t>
+        </is>
+      </c>
+      <c r="I106" s="122" t="inlineStr">
+        <is>
+          <t>Impact materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J106" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K106" s="122" t="inlineStr">
+        <is>
+          <t>Disclose: (a) processes for providing remedy to consumers and end-users harmed by the organization's products or services; (b) complaint and redress channels available (ombudsman, helpline, returns policy, compensation scheme); (c) how the effectiveness of these channels is monitored; (d) number and nature of consumer complaints received and resolved.</t>
+        </is>
+      </c>
+      <c r="L106" s="124" t="inlineStr">
+        <is>
+          <t>• Consumer complaints handling procedure
+• Product recall and safety notification process
+• Refund, return, and compensation policy
+• Ombudsman or alternative dispute resolution (ADR) scheme membership
+• Data breach notification procedure
+• Product liability claim management process
+• Consumer helpline and digital support channel documentation
+• Regulatory complaint referral procedure (FCA, consumer protection bodies)</t>
+        </is>
+      </c>
+      <c r="M106" s="125" t="inlineStr">
+        <is>
+          <t>• Complaint volume reports by category and channel
+• Evidence of compensation provided to harmed consumers
+• Product recall effectiveness records
+• Regulatory body complaint statistics (where published)
+• Customer satisfaction scores post-resolution
+• Legal claim settlement records
+• ADR scheme annual reporting</t>
+        </is>
+      </c>
+      <c r="N106" s="126" t="inlineStr">
+        <is>
+          <t>• Total consumer complaints received in reporting period
+• Complaints by category (safety, billing, service, data breach, etc.)
+• Complaint resolution rate within SLA (%)
+• Average resolution time (days)
+• Number of product recalls and consumers notified
+• Compensation paid to consumers ($)
+• Data subject requests received and resolved (GDPR DSARs)
+• Regulatory enforcement actions related to consumer protection</t>
+        </is>
+      </c>
+      <c r="O106" s="127" t="inlineStr">
+        <is>
+          <t>Complaint resolution rate = Resolved within SLA / Total complaints × 100. Average resolution time = Total resolution days / Complaints resolved. Recall coverage rate = Consumers notified of recall / Total product at risk in market × 100. DSAR fulfilment rate = DSARs completed on time / Total DSARs received × 100.</t>
+        </is>
+      </c>
+      <c r="P106" s="122" t="inlineStr">
+        <is>
+          <t>Customer Experience / Legal / Compliance / Product Safety / Data Privacy</t>
+        </is>
+      </c>
+      <c r="Q106" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R106" s="128" t="inlineStr">
+        <is>
+          <t>• Consumer remedy channels must comply with applicable consumer protection law in all jurisdictions
+• ADR scheme membership and referral rates are an assurance focus in financial and utility sectors
+• Product recall effectiveness (coverage rate) is a key metric for physical product companies
+• GDPR data breach notification timelines must be documented and verifiable
+• Vulnerable consumer outcomes must be separately monitored within complaint data</t>
+        </is>
+      </c>
+      <c r="S106" s="129" t="inlineStr">
+        <is>
+          <t>• Does the organization belong to recognised ADR or ombudsman schemes in all key markets?
+• Are complaint volumes and types trended to identify systemic product or service failures?
+• Are product recall and safety notification processes tested and independently reviewed?
+• Are vulnerable consumer complaints and outcomes separately tracked?</t>
+        </is>
+      </c>
+      <c r="T106" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S4 | Disclosure S4-3 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="130" customHeight="1" s="42">
+      <c r="A107" s="136" t="inlineStr">
+        <is>
+          <t>ESRS S4: Consumers and End-Users</t>
+        </is>
+      </c>
+      <c r="B107" s="136" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C107" s="136" t="inlineStr">
+        <is>
+          <t>Consumers and End-Users</t>
+        </is>
+      </c>
+      <c r="D107" s="137" t="inlineStr">
+        <is>
+          <t>ESRS S4-4</t>
+        </is>
+      </c>
+      <c r="E107" s="136" t="inlineStr">
+        <is>
+          <t>Taking Action on Material Impacts on Consumers and End-Users, and Approaches to Managing Material Risks and Opportunities</t>
+        </is>
+      </c>
+      <c r="F107" s="136" t="inlineStr">
+        <is>
+          <t>Disclose actions taken or planned to address material negative impacts on consumers and to capture positive impact opportunities.</t>
+        </is>
+      </c>
+      <c r="G107" s="136" t="inlineStr">
+        <is>
+          <t>Mandatory (if material)</t>
+        </is>
+      </c>
+      <c r="H107" s="136" t="inlineStr">
+        <is>
+          <t>All entities with material consumer impacts requiring active management</t>
+        </is>
+      </c>
+      <c r="I107" s="136" t="inlineStr">
+        <is>
+          <t>Impact materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J107" s="136" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K107" s="136" t="inlineStr">
+        <is>
+          <t>Disclose: (a) actions taken or planned to address material negative impacts on consumers and end-users and to prevent recurrence; (b) whether actions are preventive, mitigative or remedial; (c) how actions are tracked and effectiveness monitored; (d) investment in consumer-benefiting initiatives (accessibility, affordability, sustainable products).</t>
+        </is>
+      </c>
+      <c r="L107" s="124" t="inlineStr">
+        <is>
+          <t>• Product safety improvement action plans
+• Digital accessibility enhancement programme documentation
+• Responsible AI and algorithmic fairness initiatives
+• Sustainable product development pipeline
+• Affordability and financial inclusion programme records
+• Data privacy enhancement actions (privacy by design implementation)
+• Vulnerable consumer protection programme
+• Consumer education and empowerment initiatives
+• Regulatory remediation plans (where enforcement action received)</t>
+        </is>
+      </c>
+      <c r="M107" s="125" t="inlineStr">
+        <is>
+          <t>• Evidence of completed vs. planned actions with timelines
+• Product safety improvement metrics (defect rates, recall rates)
+• Accessibility audit before and after improvement actions
+• Consumer satisfaction change following interventions
+• Third-party certification of product sustainability claims
+• Regulatory correspondence confirming remediation accepted</t>
+        </is>
+      </c>
+      <c r="N107" s="126" t="inlineStr">
+        <is>
+          <t>• Number of consumer protection actions implemented in period
+• Product safety improvement metrics (defect rate reduction %)
+• Number of products/services with enhanced accessibility features
+• Number of vulnerable consumers supported through dedicated programmes
+• Investment in responsible product development ($)
+• Change in consumer complaint volumes year-on-year (%)
+• Number of regulatory violations related to consumer protection</t>
+        </is>
+      </c>
+      <c r="O107" s="127" t="inlineStr">
+        <is>
+          <t>Defect rate = Defective units / Total units produced × 100. Complaint reduction = (Current complaints − Prior year complaints) / Prior year complaints × 100. Investment in consumer protection % = Consumer protection spend / Total revenue × 100. Accessibility coverage = Products with accessibility features / Total product range × 100.</t>
+        </is>
+      </c>
+      <c r="P107" s="136" t="inlineStr">
+        <is>
+          <t>Product / Marketing / Legal / Customer Experience / Sustainability / ESG</t>
+        </is>
+      </c>
+      <c r="Q107" s="136" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R107" s="128" t="inlineStr">
+        <is>
+          <t>• Actions must be demonstrably linked to identified material consumer impacts
+• Product safety improvements must include root cause analysis
+• Responsible marketing actions must address both content and targeting (especially for minors)
+• Assurers look for evidence of independent testing of consumer safety claims
+• Vulnerable consumer actions require specific, not generic, evidence of effectiveness</t>
+        </is>
+      </c>
+      <c r="S107" s="129" t="inlineStr">
+        <is>
+          <t>• Are product safety actions documented with root cause analysis and effectiveness monitoring?
+• Are there specific actions targeting the most material consumer impact areas?
+• Are vulnerable consumer protection actions independently evaluated?
+• Is investment in responsible product development quantified and tracked?</t>
+        </is>
+      </c>
+      <c r="T107" s="136" t="inlineStr">
+        <is>
+          <t>ESRS S4 | Disclosure S4-4 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="130" customHeight="1" s="42">
+      <c r="A108" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S4: Consumers and End-Users</t>
+        </is>
+      </c>
+      <c r="B108" s="122" t="inlineStr">
+        <is>
+          <t>ESRS Social</t>
+        </is>
+      </c>
+      <c r="C108" s="122" t="inlineStr">
+        <is>
+          <t>Consumers and End-Users</t>
+        </is>
+      </c>
+      <c r="D108" s="123" t="inlineStr">
+        <is>
+          <t>ESRS S4-5</t>
+        </is>
+      </c>
+      <c r="E108" s="122" t="inlineStr">
+        <is>
+          <t>Targets Related to Managing Material Negative Impacts, Advancing Positive Impacts, and Managing Material Risks and Opportunities</t>
+        </is>
+      </c>
+      <c r="F108" s="122" t="inlineStr">
+        <is>
+          <t>Disclose measurable targets related to managing impacts on consumers and end-users.</t>
+        </is>
+      </c>
+      <c r="G108" s="122" t="inlineStr">
+        <is>
+          <t>Mandatory (if material, where targets are set)</t>
+        </is>
+      </c>
+      <c r="H108" s="122" t="inlineStr">
+        <is>
+          <t>Entities that have set consumer-related sustainability targets</t>
+        </is>
+      </c>
+      <c r="I108" s="122" t="inlineStr">
+        <is>
+          <t>Impact and financial materiality per ESRS 1</t>
+        </is>
+      </c>
+      <c r="J108" s="122" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K108" s="122" t="inlineStr">
+        <is>
+          <t>Disclose: (a) time-bound, measurable targets related to material consumer and end-user impacts; (b) baseline values and target years; (c) progress made during the reporting period; (d) alignment with industry commitments or regulatory requirements.</t>
+        </is>
+      </c>
+      <c r="L108" s="124" t="inlineStr">
+        <is>
+          <t>• Target-setting methodology and governance documentation
+• Baseline data records for each consumer impact metric
+• Annual target performance tracking reports
+• Board or senior management approval documentation for consumer targets
+• Industry benchmark data supporting target ambition
+• Regulatory or certification standards referenced in targets
+• Historical trend data for baseline establishment</t>
+        </is>
+      </c>
+      <c r="M108" s="125" t="inlineStr">
+        <is>
+          <t>• Progress reports showing actual vs. target performance
+• Third-party verification of consumer target metrics
+• Board review minutes confirming oversight of consumer targets
+• Explanation of any target revisions
+• Consumer satisfaction data supporting impact targets</t>
+        </is>
+      </c>
+      <c r="N108" s="126" t="inlineStr">
+        <is>
+          <t>• Number of consumer impact targets set
+• Baseline year and value for each target
+• Target value and year for each metric
+• Actual performance in reporting period vs. target
+• Number of targets achieved, on track, or missed
+• Progress % towards each target
+• Target categories (safety, data privacy, affordability, accessibility)</t>
+        </is>
+      </c>
+      <c r="O108" s="127" t="inlineStr">
+        <is>
+          <t>Progress % = (Current value − Baseline) / (Target − Baseline) × 100. Track each target independently. Aggregate target achievement rate = Targets on track or achieved / Total targets × 100. Where targets are qualitative milestones, track against milestone completion schedule.</t>
+        </is>
+      </c>
+      <c r="P108" s="122" t="inlineStr">
+        <is>
+          <t>Sustainability / ESG / Marketing / Legal / Product / Customer Experience</t>
+        </is>
+      </c>
+      <c r="Q108" s="122" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="R108" s="128" t="inlineStr">
+        <is>
+          <t>• Consumer impact targets must be proportionate to the scale of material impacts
+• Targets should not merely codify current performance — ambition must be demonstrated
+• Assurers will check that targets address the highest priority consumer impacts
+• Data quality for consumer metrics (NPS, complaint rates, safety data) must be robust
+• Industry benchmark comparisons strengthen target credibility</t>
+        </is>
+      </c>
+      <c r="S108" s="129" t="inlineStr">
+        <is>
+          <t>• Are consumer impact targets aligned to the most material identified consumer risks?
+• Is there documented evidence of target ambition vs. business-as-usual trajectory?
+• Are targets independently verified or linked to certified standards?
+• Do targets cover both negative impact reduction and positive impact advancement?</t>
+        </is>
+      </c>
+      <c r="T108" s="122" t="inlineStr">
+        <is>
+          <t>ESRS S4 | Disclosure S4-5 | ESRS Commission Delegated Regulation (EU) 2023/2772 | efrag.org</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="15">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A5:T5"/>
     <mergeCell ref="A45:T45"/>
     <mergeCell ref="A27:T27"/>
+    <mergeCell ref="A103:T103"/>
+    <mergeCell ref="A88:T88"/>
     <mergeCell ref="A34:T34"/>
     <mergeCell ref="A40:T40"/>
     <mergeCell ref="A21:T21"/>
     <mergeCell ref="A64:T64"/>
     <mergeCell ref="A59:T59"/>
+    <mergeCell ref="A81:T81"/>
+    <mergeCell ref="A96:T96"/>
     <mergeCell ref="A2:T2"/>
     <mergeCell ref="A52:T52"/>
   </mergeCells>
